--- a/data/conferences.xlsx
+++ b/data/conferences.xlsx
@@ -594,6 +594,12 @@
           <t>not_yet_announced</t>
         </is>
       </c>
+      <c r="P2" t="inlineStr">
+        <is>
+          <t>2026-07-22 19:07 UTC</t>
+        </is>
+      </c>
+      <c r="R2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -654,6 +660,12 @@
           <t>not_yet_announced</t>
         </is>
       </c>
+      <c r="P3" t="inlineStr">
+        <is>
+          <t>2026-07-22 19:07 UTC</t>
+        </is>
+      </c>
+      <c r="R3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -714,6 +726,12 @@
           <t>not_yet_announced</t>
         </is>
       </c>
+      <c r="P4" t="inlineStr">
+        <is>
+          <t>2026-07-22 19:07 UTC</t>
+        </is>
+      </c>
+      <c r="R4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -774,6 +792,12 @@
           <t>not_yet_announced</t>
         </is>
       </c>
+      <c r="P5" t="inlineStr">
+        <is>
+          <t>2026-07-22 19:07 UTC</t>
+        </is>
+      </c>
+      <c r="R5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -834,6 +858,12 @@
           <t>not_yet_announced</t>
         </is>
       </c>
+      <c r="P6" t="inlineStr">
+        <is>
+          <t>2026-07-22 19:07 UTC</t>
+        </is>
+      </c>
+      <c r="R6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -894,6 +924,12 @@
           <t>not_yet_announced</t>
         </is>
       </c>
+      <c r="P7" t="inlineStr">
+        <is>
+          <t>2026-07-22 19:07 UTC</t>
+        </is>
+      </c>
+      <c r="R7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -954,6 +990,12 @@
           <t>not_yet_announced</t>
         </is>
       </c>
+      <c r="P8" t="inlineStr">
+        <is>
+          <t>2026-07-22 19:07 UTC</t>
+        </is>
+      </c>
+      <c r="R8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -1014,6 +1056,12 @@
           <t>not_yet_announced</t>
         </is>
       </c>
+      <c r="P9" t="inlineStr">
+        <is>
+          <t>2026-07-22 19:07 UTC</t>
+        </is>
+      </c>
+      <c r="R9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -1069,9 +1117,39 @@
           <t>2026-09-10</t>
         </is>
       </c>
+      <c r="M10" t="inlineStr">
+        <is>
+          <t>September 28, 2026</t>
+        </is>
+      </c>
       <c r="N10" t="inlineStr">
         <is>
-          <t>not_yet_announced</t>
+          <t>confirmed</t>
+        </is>
+      </c>
+      <c r="O10" t="inlineStr">
+        <is>
+          <t>https://chi2027.acm.org/authors/workshops/</t>
+        </is>
+      </c>
+      <c r="P10" t="inlineStr">
+        <is>
+          <t>2026-07-22 19:07 UTC</t>
+        </is>
+      </c>
+      <c r="Q10" t="inlineStr">
+        <is>
+          <t>2026-07-22 18:58 UTC</t>
+        </is>
+      </c>
+      <c r="R10" t="inlineStr">
+        <is>
+          <t>https://chi2027.acm.org/authors/workshops/</t>
+        </is>
+      </c>
+      <c r="S10" t="inlineStr">
+        <is>
+          <t>extracted from official site</t>
         </is>
       </c>
     </row>
@@ -1134,6 +1212,12 @@
           <t>not_yet_announced</t>
         </is>
       </c>
+      <c r="P11" t="inlineStr">
+        <is>
+          <t>2026-07-22 19:07 UTC</t>
+        </is>
+      </c>
+      <c r="R11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
@@ -1189,9 +1273,39 @@
           <t>2025-05-13</t>
         </is>
       </c>
+      <c r="M12" t="inlineStr">
+        <is>
+          <t>April 10, 2026</t>
+        </is>
+      </c>
       <c r="N12" t="inlineStr">
         <is>
-          <t>not_yet_announced</t>
+          <t>confirmed</t>
+        </is>
+      </c>
+      <c r="O12" t="inlineStr">
+        <is>
+          <t>https://cscw.acm.org/2026/workshops.html</t>
+        </is>
+      </c>
+      <c r="P12" t="inlineStr">
+        <is>
+          <t>2026-07-22 19:07 UTC</t>
+        </is>
+      </c>
+      <c r="Q12" t="inlineStr">
+        <is>
+          <t>2026-07-22 18:58 UTC</t>
+        </is>
+      </c>
+      <c r="R12" t="inlineStr">
+        <is>
+          <t>https://cscw.acm.org/2026/workshops.html</t>
+        </is>
+      </c>
+      <c r="S12" t="inlineStr">
+        <is>
+          <t>extracted from official site</t>
         </is>
       </c>
     </row>
@@ -1249,9 +1363,39 @@
           <t>2025-11-13</t>
         </is>
       </c>
+      <c r="M13" t="inlineStr">
+        <is>
+          <t>Nov 03, 2025</t>
+        </is>
+      </c>
       <c r="N13" t="inlineStr">
         <is>
-          <t>not_yet_announced</t>
+          <t>confirmed</t>
+        </is>
+      </c>
+      <c r="O13" t="inlineStr">
+        <is>
+          <t>https://cvpr.thecvf.com/Conferences/2026/CallForWorkshops</t>
+        </is>
+      </c>
+      <c r="P13" t="inlineStr">
+        <is>
+          <t>2026-07-22 19:07 UTC</t>
+        </is>
+      </c>
+      <c r="Q13" t="inlineStr">
+        <is>
+          <t>2026-07-22 18:58 UTC</t>
+        </is>
+      </c>
+      <c r="R13" t="inlineStr">
+        <is>
+          <t>https://cvpr.thecvf.com/Conferences/2026/CallForWorkshops</t>
+        </is>
+      </c>
+      <c r="S13" t="inlineStr">
+        <is>
+          <t>extracted from official site</t>
         </is>
       </c>
     </row>
@@ -1309,9 +1453,39 @@
           <t>2025-11-18</t>
         </is>
       </c>
+      <c r="M14" t="inlineStr">
+        <is>
+          <t>Apr 29, 2026</t>
+        </is>
+      </c>
       <c r="N14" t="inlineStr">
         <is>
-          <t>not_yet_announced</t>
+          <t>confirmed</t>
+        </is>
+      </c>
+      <c r="O14" t="inlineStr">
+        <is>
+          <t>https://dac.com/2026/workshop-call-for-proposals</t>
+        </is>
+      </c>
+      <c r="P14" t="inlineStr">
+        <is>
+          <t>2026-07-22 19:07 UTC</t>
+        </is>
+      </c>
+      <c r="Q14" t="inlineStr">
+        <is>
+          <t>2026-07-22 18:58 UTC</t>
+        </is>
+      </c>
+      <c r="R14" t="inlineStr">
+        <is>
+          <t>https://dac.com/2026/workshop-call-for-proposals</t>
+        </is>
+      </c>
+      <c r="S14" t="inlineStr">
+        <is>
+          <t>extracted from official site</t>
         </is>
       </c>
     </row>
@@ -1374,6 +1548,12 @@
           <t>not_yet_announced</t>
         </is>
       </c>
+      <c r="P15" t="inlineStr">
+        <is>
+          <t>2026-07-22 19:07 UTC</t>
+        </is>
+      </c>
+      <c r="R15" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
@@ -1434,6 +1614,12 @@
           <t>not_yet_announced</t>
         </is>
       </c>
+      <c r="P16" t="inlineStr">
+        <is>
+          <t>2026-07-22 19:07 UTC</t>
+        </is>
+      </c>
+      <c r="R16" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
@@ -1494,6 +1680,12 @@
           <t>not_yet_announced</t>
         </is>
       </c>
+      <c r="P17" t="inlineStr">
+        <is>
+          <t>2026-07-22 19:07 UTC</t>
+        </is>
+      </c>
+      <c r="R17" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
@@ -1549,9 +1741,39 @@
           <t>2025-12-02</t>
         </is>
       </c>
+      <c r="M18" t="inlineStr">
+        <is>
+          <t>November 10, 2025</t>
+        </is>
+      </c>
       <c r="N18" t="inlineStr">
         <is>
-          <t>not_yet_announced</t>
+          <t>confirmed</t>
+        </is>
+      </c>
+      <c r="O18" t="inlineStr">
+        <is>
+          <t>https://conf.researchr.org/track/fm-2026/fm-2026-workshops</t>
+        </is>
+      </c>
+      <c r="P18" t="inlineStr">
+        <is>
+          <t>2026-07-22 19:07 UTC</t>
+        </is>
+      </c>
+      <c r="Q18" t="inlineStr">
+        <is>
+          <t>2026-07-22 18:58 UTC</t>
+        </is>
+      </c>
+      <c r="R18" t="inlineStr">
+        <is>
+          <t>https://conf.researchr.org/track/fm-2026/fm-2026-workshops</t>
+        </is>
+      </c>
+      <c r="S18" t="inlineStr">
+        <is>
+          <t>extracted from official site</t>
         </is>
       </c>
     </row>
@@ -1614,6 +1836,12 @@
           <t>not_yet_announced</t>
         </is>
       </c>
+      <c r="P19" t="inlineStr">
+        <is>
+          <t>2026-07-22 19:07 UTC</t>
+        </is>
+      </c>
+      <c r="R19" t="inlineStr"/>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
@@ -1674,6 +1902,12 @@
           <t>not_yet_announced</t>
         </is>
       </c>
+      <c r="P20" t="inlineStr">
+        <is>
+          <t>2026-07-22 19:07 UTC</t>
+        </is>
+      </c>
+      <c r="R20" t="inlineStr"/>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
@@ -1736,7 +1970,7 @@
       </c>
       <c r="P21" t="inlineStr">
         <is>
-          <t>2026-07-22 18:19 UTC</t>
+          <t>2026-07-22 19:07 UTC</t>
         </is>
       </c>
       <c r="R21" t="inlineStr"/>
@@ -1795,9 +2029,39 @@
           <t>2026-01-29</t>
         </is>
       </c>
+      <c r="M22" t="inlineStr">
+        <is>
+          <t>December 5, 2025</t>
+        </is>
+      </c>
       <c r="N22" t="inlineStr">
         <is>
-          <t>not_yet_announced</t>
+          <t>confirmed</t>
+        </is>
+      </c>
+      <c r="O22" t="inlineStr">
+        <is>
+          <t>https://hpdc.sci.utah.edu/2026/</t>
+        </is>
+      </c>
+      <c r="P22" t="inlineStr">
+        <is>
+          <t>2026-07-22 19:07 UTC</t>
+        </is>
+      </c>
+      <c r="Q22" t="inlineStr">
+        <is>
+          <t>2026-07-22 18:58 UTC</t>
+        </is>
+      </c>
+      <c r="R22" t="inlineStr">
+        <is>
+          <t>https://hpdc.sci.utah.edu/2026/</t>
+        </is>
+      </c>
+      <c r="S22" t="inlineStr">
+        <is>
+          <t>extracted from official site</t>
         </is>
       </c>
     </row>
@@ -1855,9 +2119,39 @@
           <t>2025-03-08</t>
         </is>
       </c>
+      <c r="M23" t="inlineStr">
+        <is>
+          <t>Mar 13, 2025</t>
+        </is>
+      </c>
       <c r="N23" t="inlineStr">
         <is>
-          <t>not_yet_announced</t>
+          <t>confirmed</t>
+        </is>
+      </c>
+      <c r="O23" t="inlineStr">
+        <is>
+          <t>https://iccv.thecvf.com/Conferences/2025/CallForWorkshops</t>
+        </is>
+      </c>
+      <c r="P23" t="inlineStr">
+        <is>
+          <t>2026-07-22 19:07 UTC</t>
+        </is>
+      </c>
+      <c r="Q23" t="inlineStr">
+        <is>
+          <t>2026-07-22 18:58 UTC</t>
+        </is>
+      </c>
+      <c r="R23" t="inlineStr">
+        <is>
+          <t>https://iccv.thecvf.com/Conferences/2025/CallForWorkshops</t>
+        </is>
+      </c>
+      <c r="S23" t="inlineStr">
+        <is>
+          <t>extracted from official site</t>
         </is>
       </c>
     </row>
@@ -1920,6 +2214,12 @@
           <t>not_yet_announced</t>
         </is>
       </c>
+      <c r="P24" t="inlineStr">
+        <is>
+          <t>2026-07-22 19:07 UTC</t>
+        </is>
+      </c>
+      <c r="R24" t="inlineStr"/>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
@@ -1970,9 +2270,39 @@
           <t>2025-09-24</t>
         </is>
       </c>
+      <c r="M25" t="inlineStr">
+        <is>
+          <t>10 October 2025</t>
+        </is>
+      </c>
       <c r="N25" t="inlineStr">
         <is>
-          <t>not_yet_announced</t>
+          <t>confirmed</t>
+        </is>
+      </c>
+      <c r="O25" t="inlineStr">
+        <is>
+          <t>https://iclr.cc/Conferences/2026/CallForWorkshops</t>
+        </is>
+      </c>
+      <c r="P25" t="inlineStr">
+        <is>
+          <t>2026-07-22 19:07 UTC</t>
+        </is>
+      </c>
+      <c r="Q25" t="inlineStr">
+        <is>
+          <t>2026-07-22 18:58 UTC</t>
+        </is>
+      </c>
+      <c r="R25" t="inlineStr">
+        <is>
+          <t>https://iclr.cc/Conferences/2026/CallForWorkshops</t>
+        </is>
+      </c>
+      <c r="S25" t="inlineStr">
+        <is>
+          <t>extracted from official site</t>
         </is>
       </c>
     </row>
@@ -2030,9 +2360,39 @@
           <t>2026-01-29</t>
         </is>
       </c>
+      <c r="M26" t="inlineStr">
+        <is>
+          <t>February 13, 2026</t>
+        </is>
+      </c>
       <c r="N26" t="inlineStr">
         <is>
-          <t>not_yet_announced</t>
+          <t>confirmed</t>
+        </is>
+      </c>
+      <c r="O26" t="inlineStr">
+        <is>
+          <t>https://icml.cc/Conferences/2026/CallForWorkshops</t>
+        </is>
+      </c>
+      <c r="P26" t="inlineStr">
+        <is>
+          <t>2026-07-22 19:07 UTC</t>
+        </is>
+      </c>
+      <c r="Q26" t="inlineStr">
+        <is>
+          <t>2026-07-22 18:58 UTC</t>
+        </is>
+      </c>
+      <c r="R26" t="inlineStr">
+        <is>
+          <t>https://icml.cc/Conferences/2026/CallForWorkshops</t>
+        </is>
+      </c>
+      <c r="S26" t="inlineStr">
+        <is>
+          <t>extracted from official site</t>
         </is>
       </c>
     </row>
@@ -2090,9 +2450,39 @@
           <t>2026-06-30</t>
         </is>
       </c>
+      <c r="M27" t="inlineStr">
+        <is>
+          <t>4 July 2026</t>
+        </is>
+      </c>
       <c r="N27" t="inlineStr">
         <is>
-          <t>not_yet_announced</t>
+          <t>confirmed</t>
+        </is>
+      </c>
+      <c r="O27" t="inlineStr">
+        <is>
+          <t>https://conf.researchr.org/track/icse-2027/icse-2027-workshops</t>
+        </is>
+      </c>
+      <c r="P27" t="inlineStr">
+        <is>
+          <t>2026-07-22 19:07 UTC</t>
+        </is>
+      </c>
+      <c r="Q27" t="inlineStr">
+        <is>
+          <t>2026-07-22 18:58 UTC</t>
+        </is>
+      </c>
+      <c r="R27" t="inlineStr">
+        <is>
+          <t>https://conf.researchr.org/track/icse-2027/icse-2027-workshops</t>
+        </is>
+      </c>
+      <c r="S27" t="inlineStr">
+        <is>
+          <t>extracted from official site</t>
         </is>
       </c>
     </row>
@@ -2150,9 +2540,39 @@
           <t>2026-03-31</t>
         </is>
       </c>
+      <c r="M28" t="inlineStr">
+        <is>
+          <t>July 30, 2026</t>
+        </is>
+      </c>
       <c r="N28" t="inlineStr">
         <is>
-          <t>not_yet_announced</t>
+          <t>confirmed</t>
+        </is>
+      </c>
+      <c r="O28" t="inlineStr">
+        <is>
+          <t>https://ieeevis.org/year/2026/info/call-participation/workshops</t>
+        </is>
+      </c>
+      <c r="P28" t="inlineStr">
+        <is>
+          <t>2026-07-22 19:07 UTC</t>
+        </is>
+      </c>
+      <c r="Q28" t="inlineStr">
+        <is>
+          <t>2026-07-22 18:58 UTC</t>
+        </is>
+      </c>
+      <c r="R28" t="inlineStr">
+        <is>
+          <t>https://ieeevis.org/year/2026/info/call-participation/workshops</t>
+        </is>
+      </c>
+      <c r="S28" t="inlineStr">
+        <is>
+          <t>extracted from official site</t>
         </is>
       </c>
     </row>
@@ -2215,6 +2635,12 @@
           <t>not_yet_announced</t>
         </is>
       </c>
+      <c r="P29" t="inlineStr">
+        <is>
+          <t>2026-07-22 19:07 UTC</t>
+        </is>
+      </c>
+      <c r="R29" t="inlineStr"/>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
@@ -2275,6 +2701,12 @@
           <t>not_yet_announced</t>
         </is>
       </c>
+      <c r="P30" t="inlineStr">
+        <is>
+          <t>2026-07-22 19:07 UTC</t>
+        </is>
+      </c>
+      <c r="R30" t="inlineStr"/>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
@@ -2330,9 +2762,39 @@
           <t>2025-11-10</t>
         </is>
       </c>
+      <c r="M31" t="inlineStr">
+        <is>
+          <t>Jan 9, 2026</t>
+        </is>
+      </c>
       <c r="N31" t="inlineStr">
         <is>
-          <t>not_yet_announced</t>
+          <t>confirmed</t>
+        </is>
+      </c>
+      <c r="O31" t="inlineStr">
+        <is>
+          <t>https://iscaconf.org/isca2026/</t>
+        </is>
+      </c>
+      <c r="P31" t="inlineStr">
+        <is>
+          <t>2026-07-22 19:07 UTC</t>
+        </is>
+      </c>
+      <c r="Q31" t="inlineStr">
+        <is>
+          <t>2026-07-22 18:58 UTC</t>
+        </is>
+      </c>
+      <c r="R31" t="inlineStr">
+        <is>
+          <t>https://iscaconf.org/isca2026/</t>
+        </is>
+      </c>
+      <c r="S31" t="inlineStr">
+        <is>
+          <t>extracted from official site</t>
         </is>
       </c>
     </row>
@@ -2390,9 +2852,39 @@
           <t>2026-01-29</t>
         </is>
       </c>
+      <c r="M32" t="inlineStr">
+        <is>
+          <t>Sat 17 Jan 2026</t>
+        </is>
+      </c>
       <c r="N32" t="inlineStr">
         <is>
-          <t>not_yet_announced</t>
+          <t>confirmed</t>
+        </is>
+      </c>
+      <c r="O32" t="inlineStr">
+        <is>
+          <t>https://conf.researchr.org/track/issta-2026/splash-issta-2026-workshops</t>
+        </is>
+      </c>
+      <c r="P32" t="inlineStr">
+        <is>
+          <t>2026-07-22 19:07 UTC</t>
+        </is>
+      </c>
+      <c r="Q32" t="inlineStr">
+        <is>
+          <t>2026-07-22 18:58 UTC</t>
+        </is>
+      </c>
+      <c r="R32" t="inlineStr">
+        <is>
+          <t>https://conf.researchr.org/track/issta-2026/splash-issta-2026-workshops</t>
+        </is>
+      </c>
+      <c r="S32" t="inlineStr">
+        <is>
+          <t>extracted from official site</t>
         </is>
       </c>
     </row>
@@ -2455,6 +2947,12 @@
           <t>not_yet_announced</t>
         </is>
       </c>
+      <c r="P33" t="inlineStr">
+        <is>
+          <t>2026-07-22 19:07 UTC</t>
+        </is>
+      </c>
+      <c r="R33" t="inlineStr"/>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
@@ -2510,9 +3008,39 @@
           <t>2026-04-07</t>
         </is>
       </c>
+      <c r="M34" t="inlineStr">
+        <is>
+          <t>May 22, 2026</t>
+        </is>
+      </c>
       <c r="N34" t="inlineStr">
         <is>
-          <t>not_yet_announced</t>
+          <t>confirmed</t>
+        </is>
+      </c>
+      <c r="O34" t="inlineStr">
+        <is>
+          <t>https://microarch.org/micro59/</t>
+        </is>
+      </c>
+      <c r="P34" t="inlineStr">
+        <is>
+          <t>2026-07-22 19:07 UTC</t>
+        </is>
+      </c>
+      <c r="Q34" t="inlineStr">
+        <is>
+          <t>2026-07-22 18:58 UTC</t>
+        </is>
+      </c>
+      <c r="R34" t="inlineStr">
+        <is>
+          <t>https://microarch.org/micro59/</t>
+        </is>
+      </c>
+      <c r="S34" t="inlineStr">
+        <is>
+          <t>extracted from official site</t>
         </is>
       </c>
     </row>
@@ -2575,6 +3103,12 @@
           <t>not_yet_announced</t>
         </is>
       </c>
+      <c r="P35" t="inlineStr">
+        <is>
+          <t>2026-07-22 19:07 UTC</t>
+        </is>
+      </c>
+      <c r="R35" t="inlineStr"/>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
@@ -2635,6 +3169,12 @@
           <t>not_yet_announced</t>
         </is>
       </c>
+      <c r="P36" t="inlineStr">
+        <is>
+          <t>2026-07-22 19:07 UTC</t>
+        </is>
+      </c>
+      <c r="R36" t="inlineStr"/>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
@@ -2690,9 +3230,39 @@
           <t>2026-05-07</t>
         </is>
       </c>
+      <c r="M37" t="inlineStr">
+        <is>
+          <t>June 06, 2026</t>
+        </is>
+      </c>
       <c r="N37" t="inlineStr">
         <is>
-          <t>not_yet_announced</t>
+          <t>confirmed</t>
+        </is>
+      </c>
+      <c r="O37" t="inlineStr">
+        <is>
+          <t>https://neurips.cc/Conferences/2026/CallForWorkshops</t>
+        </is>
+      </c>
+      <c r="P37" t="inlineStr">
+        <is>
+          <t>2026-07-22 19:07 UTC</t>
+        </is>
+      </c>
+      <c r="Q37" t="inlineStr">
+        <is>
+          <t>2026-07-22 18:58 UTC</t>
+        </is>
+      </c>
+      <c r="R37" t="inlineStr">
+        <is>
+          <t>https://neurips.cc/Conferences/2026/CallForWorkshops</t>
+        </is>
+      </c>
+      <c r="S37" t="inlineStr">
+        <is>
+          <t>extracted from official site</t>
         </is>
       </c>
     </row>
@@ -2755,6 +3325,12 @@
           <t>not_yet_announced</t>
         </is>
       </c>
+      <c r="P38" t="inlineStr">
+        <is>
+          <t>2026-07-22 19:07 UTC</t>
+        </is>
+      </c>
+      <c r="R38" t="inlineStr"/>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
@@ -2810,9 +3386,39 @@
           <t>2025-10-10</t>
         </is>
       </c>
+      <c r="M39" t="inlineStr">
+        <is>
+          <t>Sat 17 Jan 2026</t>
+        </is>
+      </c>
       <c r="N39" t="inlineStr">
         <is>
-          <t>not_yet_announced</t>
+          <t>confirmed</t>
+        </is>
+      </c>
+      <c r="O39" t="inlineStr">
+        <is>
+          <t>https://2026.splashcon.org/track/splash-issta-2026-workshops</t>
+        </is>
+      </c>
+      <c r="P39" t="inlineStr">
+        <is>
+          <t>2026-07-22 19:07 UTC</t>
+        </is>
+      </c>
+      <c r="Q39" t="inlineStr">
+        <is>
+          <t>2026-07-22 18:58 UTC</t>
+        </is>
+      </c>
+      <c r="R39" t="inlineStr">
+        <is>
+          <t>https://2026.splashcon.org/track/splash-issta-2026-workshops</t>
+        </is>
+      </c>
+      <c r="S39" t="inlineStr">
+        <is>
+          <t>extracted from official site</t>
         </is>
       </c>
     </row>
@@ -2875,6 +3481,12 @@
           <t>not_yet_announced</t>
         </is>
       </c>
+      <c r="P40" t="inlineStr">
+        <is>
+          <t>2026-07-22 19:07 UTC</t>
+        </is>
+      </c>
+      <c r="R40" t="inlineStr"/>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
@@ -2930,9 +3542,39 @@
           <t>2025-11-13</t>
         </is>
       </c>
+      <c r="M41" t="inlineStr">
+        <is>
+          <t>Mon 24 Nov 2025</t>
+        </is>
+      </c>
       <c r="N41" t="inlineStr">
         <is>
-          <t>not_yet_announced</t>
+          <t>confirmed</t>
+        </is>
+      </c>
+      <c r="O41" t="inlineStr">
+        <is>
+          <t>https://pldi26.sigplan.org/track/pldi-2026-PLDI-Workshops</t>
+        </is>
+      </c>
+      <c r="P41" t="inlineStr">
+        <is>
+          <t>2026-07-22 19:07 UTC</t>
+        </is>
+      </c>
+      <c r="Q41" t="inlineStr">
+        <is>
+          <t>2026-07-22 18:58 UTC</t>
+        </is>
+      </c>
+      <c r="R41" t="inlineStr">
+        <is>
+          <t>https://pldi26.sigplan.org/track/pldi-2026-PLDI-Workshops</t>
+        </is>
+      </c>
+      <c r="S41" t="inlineStr">
+        <is>
+          <t>extracted from official site</t>
         </is>
       </c>
     </row>
@@ -2985,9 +3627,39 @@
           <t>2026-07-09</t>
         </is>
       </c>
+      <c r="M42" t="inlineStr">
+        <is>
+          <t>24 July 2026</t>
+        </is>
+      </c>
       <c r="N42" t="inlineStr">
         <is>
-          <t>not_yet_announced</t>
+          <t>confirmed</t>
+        </is>
+      </c>
+      <c r="O42" t="inlineStr">
+        <is>
+          <t>https://popl27.sigplan.org/track/POPL-2027-workshops-and-co-located-events</t>
+        </is>
+      </c>
+      <c r="P42" t="inlineStr">
+        <is>
+          <t>2026-07-22 19:07 UTC</t>
+        </is>
+      </c>
+      <c r="Q42" t="inlineStr">
+        <is>
+          <t>2026-07-22 18:58 UTC</t>
+        </is>
+      </c>
+      <c r="R42" t="inlineStr">
+        <is>
+          <t>https://popl27.sigplan.org/track/POPL-2027-workshops-and-co-located-events</t>
+        </is>
+      </c>
+      <c r="S42" t="inlineStr">
+        <is>
+          <t>extracted from official site</t>
         </is>
       </c>
     </row>
@@ -3052,7 +3724,7 @@
       </c>
       <c r="P43" t="inlineStr">
         <is>
-          <t>2026-07-22 18:19 UTC</t>
+          <t>2026-07-22 19:07 UTC</t>
         </is>
       </c>
       <c r="R43" t="inlineStr"/>
@@ -3116,6 +3788,12 @@
           <t>not_yet_announced</t>
         </is>
       </c>
+      <c r="P44" t="inlineStr">
+        <is>
+          <t>2026-07-22 19:07 UTC</t>
+        </is>
+      </c>
+      <c r="R44" t="inlineStr"/>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
@@ -3176,6 +3854,12 @@
           <t>not_yet_announced</t>
         </is>
       </c>
+      <c r="P45" t="inlineStr">
+        <is>
+          <t>2026-07-22 19:07 UTC</t>
+        </is>
+      </c>
+      <c r="R45" t="inlineStr"/>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
@@ -3231,9 +3915,39 @@
           <t>2026-02-06</t>
         </is>
       </c>
+      <c r="M46" t="inlineStr">
+        <is>
+          <t>January 21, 2026</t>
+        </is>
+      </c>
       <c r="N46" t="inlineStr">
         <is>
-          <t>not_yet_announced</t>
+          <t>confirmed</t>
+        </is>
+      </c>
+      <c r="O46" t="inlineStr">
+        <is>
+          <t>https://conferences.sigcomm.org/sigcomm/2026/</t>
+        </is>
+      </c>
+      <c r="P46" t="inlineStr">
+        <is>
+          <t>2026-07-22 19:07 UTC</t>
+        </is>
+      </c>
+      <c r="Q46" t="inlineStr">
+        <is>
+          <t>2026-07-22 18:58 UTC</t>
+        </is>
+      </c>
+      <c r="R46" t="inlineStr">
+        <is>
+          <t>https://conferences.sigcomm.org/sigcomm/2026/</t>
+        </is>
+      </c>
+      <c r="S46" t="inlineStr">
+        <is>
+          <t>extracted from official site</t>
         </is>
       </c>
     </row>
@@ -3296,6 +4010,12 @@
           <t>not_yet_announced</t>
         </is>
       </c>
+      <c r="P47" t="inlineStr">
+        <is>
+          <t>2026-07-22 19:07 UTC</t>
+        </is>
+      </c>
+      <c r="R47" t="inlineStr"/>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
@@ -3356,6 +4076,12 @@
           <t>not_yet_announced</t>
         </is>
       </c>
+      <c r="P48" t="inlineStr">
+        <is>
+          <t>2026-07-22 19:07 UTC</t>
+        </is>
+      </c>
+      <c r="R48" t="inlineStr"/>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
@@ -3416,6 +4142,12 @@
           <t>not_yet_announced</t>
         </is>
       </c>
+      <c r="P49" t="inlineStr">
+        <is>
+          <t>2026-07-22 19:07 UTC</t>
+        </is>
+      </c>
+      <c r="R49" t="inlineStr"/>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
@@ -3471,9 +4203,39 @@
           <t>2026-06-11</t>
         </is>
       </c>
+      <c r="M50" t="inlineStr">
+        <is>
+          <t>April 29, 2025</t>
+        </is>
+      </c>
       <c r="N50" t="inlineStr">
         <is>
-          <t>not_yet_announced</t>
+          <t>confirmed</t>
+        </is>
+      </c>
+      <c r="O50" t="inlineStr">
+        <is>
+          <t>https://sigops.org/s/conferences/atc/2026/index.html</t>
+        </is>
+      </c>
+      <c r="P50" t="inlineStr">
+        <is>
+          <t>2026-07-22 19:07 UTC</t>
+        </is>
+      </c>
+      <c r="Q50" t="inlineStr">
+        <is>
+          <t>2026-07-22 19:04 UTC</t>
+        </is>
+      </c>
+      <c r="R50" t="inlineStr">
+        <is>
+          <t>https://sigops.org/s/conferences/atc/2026/index.html</t>
+        </is>
+      </c>
+      <c r="S50" t="inlineStr">
+        <is>
+          <t>extracted from official site</t>
         </is>
       </c>
     </row>
@@ -3536,6 +4298,12 @@
           <t>not_yet_announced</t>
         </is>
       </c>
+      <c r="P51" t="inlineStr">
+        <is>
+          <t>2026-07-22 19:07 UTC</t>
+        </is>
+      </c>
+      <c r="R51" t="inlineStr"/>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
@@ -3596,6 +4364,12 @@
           <t>not_yet_announced</t>
         </is>
       </c>
+      <c r="P52" t="inlineStr">
+        <is>
+          <t>2026-07-22 19:07 UTC</t>
+        </is>
+      </c>
+      <c r="R52" t="inlineStr"/>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
@@ -3656,6 +4430,12 @@
           <t>not_yet_announced</t>
         </is>
       </c>
+      <c r="P53" t="inlineStr">
+        <is>
+          <t>2026-07-22 19:07 UTC</t>
+        </is>
+      </c>
+      <c r="R53" t="inlineStr"/>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
@@ -3716,6 +4496,12 @@
           <t>not_yet_announced</t>
         </is>
       </c>
+      <c r="P54" t="inlineStr">
+        <is>
+          <t>2026-07-22 19:07 UTC</t>
+        </is>
+      </c>
+      <c r="R54" t="inlineStr"/>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
@@ -3771,9 +4557,39 @@
           <t>2026-02-01</t>
         </is>
       </c>
+      <c r="M55" t="inlineStr">
+        <is>
+          <t>2026-03-07</t>
+        </is>
+      </c>
       <c r="N55" t="inlineStr">
         <is>
-          <t>not_yet_announced</t>
+          <t>confirmed</t>
+        </is>
+      </c>
+      <c r="O55" t="inlineStr">
+        <is>
+          <t>https://www.ubicomp.org/ubicomp-iswc-2026/workshop-cfp/</t>
+        </is>
+      </c>
+      <c r="P55" t="inlineStr">
+        <is>
+          <t>2026-07-22 19:07 UTC</t>
+        </is>
+      </c>
+      <c r="Q55" t="inlineStr">
+        <is>
+          <t>2026-07-22 18:58 UTC</t>
+        </is>
+      </c>
+      <c r="R55" t="inlineStr">
+        <is>
+          <t>https://www.ubicomp.org/ubicomp-iswc-2026/workshop-cfp/</t>
+        </is>
+      </c>
+      <c r="S55" t="inlineStr">
+        <is>
+          <t>extracted from official site</t>
         </is>
       </c>
     </row>
@@ -3831,9 +4647,39 @@
           <t>2026-03-31</t>
         </is>
       </c>
+      <c r="M56" t="inlineStr">
+        <is>
+          <t>Jul 10, 2026</t>
+        </is>
+      </c>
       <c r="N56" t="inlineStr">
         <is>
-          <t>not_yet_announced</t>
+          <t>confirmed</t>
+        </is>
+      </c>
+      <c r="O56" t="inlineStr">
+        <is>
+          <t>https://uist.acm.org/2026/</t>
+        </is>
+      </c>
+      <c r="P56" t="inlineStr">
+        <is>
+          <t>2026-07-22 19:07 UTC</t>
+        </is>
+      </c>
+      <c r="Q56" t="inlineStr">
+        <is>
+          <t>2026-07-22 18:58 UTC</t>
+        </is>
+      </c>
+      <c r="R56" t="inlineStr">
+        <is>
+          <t>https://uist.acm.org/2026/</t>
+        </is>
+      </c>
+      <c r="S56" t="inlineStr">
+        <is>
+          <t>extracted from official site</t>
         </is>
       </c>
     </row>
@@ -3896,6 +4742,12 @@
           <t>not_yet_announced</t>
         </is>
       </c>
+      <c r="P57" t="inlineStr">
+        <is>
+          <t>2026-07-22 19:07 UTC</t>
+        </is>
+      </c>
+      <c r="R57" t="inlineStr"/>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
@@ -3956,6 +4808,12 @@
           <t>not_yet_announced</t>
         </is>
       </c>
+      <c r="P58" t="inlineStr">
+        <is>
+          <t>2026-07-22 19:07 UTC</t>
+        </is>
+      </c>
+      <c r="R58" t="inlineStr"/>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
@@ -4016,6 +4874,12 @@
           <t>not_yet_announced</t>
         </is>
       </c>
+      <c r="P59" t="inlineStr">
+        <is>
+          <t>2026-07-22 19:07 UTC</t>
+        </is>
+      </c>
+      <c r="R59" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -4028,7 +4892,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E1"/>
+  <dimension ref="A1:E46"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -4058,6 +4922,1111 @@
         </is>
       </c>
     </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>chi</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>workshop_proposal_deadline</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>September 28, 2026</t>
+        </is>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>2026-07-22 18:58 UTC</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>chi</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>workshop_proposal_status</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>not_yet_announced</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>confirmed</t>
+        </is>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>2026-07-22 18:58 UTC</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>cscw</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>workshop_proposal_deadline</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>April 10, 2026</t>
+        </is>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>2026-07-22 18:58 UTC</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>cscw</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>workshop_proposal_status</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>not_yet_announced</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>confirmed</t>
+        </is>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>2026-07-22 18:58 UTC</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>cvpr</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>workshop_proposal_deadline</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>Nov 03, 2025</t>
+        </is>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>2026-07-22 18:58 UTC</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>cvpr</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>workshop_proposal_status</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>not_yet_announced</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>confirmed</t>
+        </is>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>2026-07-22 18:58 UTC</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>dac</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>workshop_proposal_deadline</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>Apr 29, 2026</t>
+        </is>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>2026-07-22 18:58 UTC</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>dac</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>workshop_proposal_status</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>not_yet_announced</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>confirmed</t>
+        </is>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>2026-07-22 18:58 UTC</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>fm</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>workshop_proposal_deadline</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>November 10, 2025</t>
+        </is>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>2026-07-22 18:58 UTC</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>fm</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>workshop_proposal_status</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>not_yet_announced</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>confirmed</t>
+        </is>
+      </c>
+      <c r="E11" t="inlineStr">
+        <is>
+          <t>2026-07-22 18:58 UTC</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>hpdc</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>workshop_proposal_deadline</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>December 5, 2025</t>
+        </is>
+      </c>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t>2026-07-22 18:58 UTC</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>hpdc</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>workshop_proposal_status</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>not_yet_announced</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>confirmed</t>
+        </is>
+      </c>
+      <c r="E13" t="inlineStr">
+        <is>
+          <t>2026-07-22 18:58 UTC</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>iccv</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>workshop_proposal_deadline</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>Mar 13, 2025</t>
+        </is>
+      </c>
+      <c r="E14" t="inlineStr">
+        <is>
+          <t>2026-07-22 18:58 UTC</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>iccv</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>workshop_proposal_status</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>not_yet_announced</t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>confirmed</t>
+        </is>
+      </c>
+      <c r="E15" t="inlineStr">
+        <is>
+          <t>2026-07-22 18:58 UTC</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>iclr</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>workshop_proposal_deadline</t>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>10 October 2025</t>
+        </is>
+      </c>
+      <c r="E16" t="inlineStr">
+        <is>
+          <t>2026-07-22 18:58 UTC</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>iclr</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>workshop_proposal_status</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>not_yet_announced</t>
+        </is>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>confirmed</t>
+        </is>
+      </c>
+      <c r="E17" t="inlineStr">
+        <is>
+          <t>2026-07-22 18:58 UTC</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>icml</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>workshop_proposal_deadline</t>
+        </is>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>February 13, 2026</t>
+        </is>
+      </c>
+      <c r="E18" t="inlineStr">
+        <is>
+          <t>2026-07-22 18:58 UTC</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>icml</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>workshop_proposal_status</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>not_yet_announced</t>
+        </is>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>confirmed</t>
+        </is>
+      </c>
+      <c r="E19" t="inlineStr">
+        <is>
+          <t>2026-07-22 18:58 UTC</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>icse</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>workshop_proposal_deadline</t>
+        </is>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>4 July 2026</t>
+        </is>
+      </c>
+      <c r="E20" t="inlineStr">
+        <is>
+          <t>2026-07-22 18:58 UTC</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>icse</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>workshop_proposal_status</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>not_yet_announced</t>
+        </is>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>confirmed</t>
+        </is>
+      </c>
+      <c r="E21" t="inlineStr">
+        <is>
+          <t>2026-07-22 18:58 UTC</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>ieeevis</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>workshop_proposal_deadline</t>
+        </is>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>July 30, 2026</t>
+        </is>
+      </c>
+      <c r="E22" t="inlineStr">
+        <is>
+          <t>2026-07-22 18:58 UTC</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>ieeevis</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>workshop_proposal_status</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>not_yet_announced</t>
+        </is>
+      </c>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>confirmed</t>
+        </is>
+      </c>
+      <c r="E23" t="inlineStr">
+        <is>
+          <t>2026-07-22 18:58 UTC</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>isca</t>
+        </is>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>workshop_proposal_deadline</t>
+        </is>
+      </c>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t>Jan 9, 2026</t>
+        </is>
+      </c>
+      <c r="E24" t="inlineStr">
+        <is>
+          <t>2026-07-22 18:58 UTC</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>isca</t>
+        </is>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>workshop_proposal_status</t>
+        </is>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>not_yet_announced</t>
+        </is>
+      </c>
+      <c r="D25" t="inlineStr">
+        <is>
+          <t>confirmed</t>
+        </is>
+      </c>
+      <c r="E25" t="inlineStr">
+        <is>
+          <t>2026-07-22 18:58 UTC</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>issta</t>
+        </is>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>workshop_proposal_deadline</t>
+        </is>
+      </c>
+      <c r="D26" t="inlineStr">
+        <is>
+          <t>Sat 17 Jan 2026</t>
+        </is>
+      </c>
+      <c r="E26" t="inlineStr">
+        <is>
+          <t>2026-07-22 18:58 UTC</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>issta</t>
+        </is>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>workshop_proposal_status</t>
+        </is>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>not_yet_announced</t>
+        </is>
+      </c>
+      <c r="D27" t="inlineStr">
+        <is>
+          <t>confirmed</t>
+        </is>
+      </c>
+      <c r="E27" t="inlineStr">
+        <is>
+          <t>2026-07-22 18:58 UTC</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>micro</t>
+        </is>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>workshop_proposal_deadline</t>
+        </is>
+      </c>
+      <c r="D28" t="inlineStr">
+        <is>
+          <t>May 22, 2026</t>
+        </is>
+      </c>
+      <c r="E28" t="inlineStr">
+        <is>
+          <t>2026-07-22 18:58 UTC</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>micro</t>
+        </is>
+      </c>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>workshop_proposal_status</t>
+        </is>
+      </c>
+      <c r="C29" t="inlineStr">
+        <is>
+          <t>not_yet_announced</t>
+        </is>
+      </c>
+      <c r="D29" t="inlineStr">
+        <is>
+          <t>confirmed</t>
+        </is>
+      </c>
+      <c r="E29" t="inlineStr">
+        <is>
+          <t>2026-07-22 18:58 UTC</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>neurips</t>
+        </is>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>workshop_proposal_deadline</t>
+        </is>
+      </c>
+      <c r="D30" t="inlineStr">
+        <is>
+          <t>June 06, 2026</t>
+        </is>
+      </c>
+      <c r="E30" t="inlineStr">
+        <is>
+          <t>2026-07-22 18:58 UTC</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>neurips</t>
+        </is>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>workshop_proposal_status</t>
+        </is>
+      </c>
+      <c r="C31" t="inlineStr">
+        <is>
+          <t>not_yet_announced</t>
+        </is>
+      </c>
+      <c r="D31" t="inlineStr">
+        <is>
+          <t>confirmed</t>
+        </is>
+      </c>
+      <c r="E31" t="inlineStr">
+        <is>
+          <t>2026-07-22 18:58 UTC</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="inlineStr">
+        <is>
+          <t>oopsla</t>
+        </is>
+      </c>
+      <c r="B32" t="inlineStr">
+        <is>
+          <t>workshop_proposal_deadline</t>
+        </is>
+      </c>
+      <c r="D32" t="inlineStr">
+        <is>
+          <t>Sat 17 Jan 2026</t>
+        </is>
+      </c>
+      <c r="E32" t="inlineStr">
+        <is>
+          <t>2026-07-22 18:58 UTC</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="inlineStr">
+        <is>
+          <t>oopsla</t>
+        </is>
+      </c>
+      <c r="B33" t="inlineStr">
+        <is>
+          <t>workshop_proposal_status</t>
+        </is>
+      </c>
+      <c r="C33" t="inlineStr">
+        <is>
+          <t>not_yet_announced</t>
+        </is>
+      </c>
+      <c r="D33" t="inlineStr">
+        <is>
+          <t>confirmed</t>
+        </is>
+      </c>
+      <c r="E33" t="inlineStr">
+        <is>
+          <t>2026-07-22 18:58 UTC</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="inlineStr">
+        <is>
+          <t>pldi</t>
+        </is>
+      </c>
+      <c r="B34" t="inlineStr">
+        <is>
+          <t>workshop_proposal_deadline</t>
+        </is>
+      </c>
+      <c r="D34" t="inlineStr">
+        <is>
+          <t>Mon 24 Nov 2025</t>
+        </is>
+      </c>
+      <c r="E34" t="inlineStr">
+        <is>
+          <t>2026-07-22 18:58 UTC</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="inlineStr">
+        <is>
+          <t>pldi</t>
+        </is>
+      </c>
+      <c r="B35" t="inlineStr">
+        <is>
+          <t>workshop_proposal_status</t>
+        </is>
+      </c>
+      <c r="C35" t="inlineStr">
+        <is>
+          <t>not_yet_announced</t>
+        </is>
+      </c>
+      <c r="D35" t="inlineStr">
+        <is>
+          <t>confirmed</t>
+        </is>
+      </c>
+      <c r="E35" t="inlineStr">
+        <is>
+          <t>2026-07-22 18:58 UTC</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="inlineStr">
+        <is>
+          <t>popl</t>
+        </is>
+      </c>
+      <c r="B36" t="inlineStr">
+        <is>
+          <t>workshop_proposal_deadline</t>
+        </is>
+      </c>
+      <c r="D36" t="inlineStr">
+        <is>
+          <t>24 July 2026</t>
+        </is>
+      </c>
+      <c r="E36" t="inlineStr">
+        <is>
+          <t>2026-07-22 18:58 UTC</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="inlineStr">
+        <is>
+          <t>popl</t>
+        </is>
+      </c>
+      <c r="B37" t="inlineStr">
+        <is>
+          <t>workshop_proposal_status</t>
+        </is>
+      </c>
+      <c r="C37" t="inlineStr">
+        <is>
+          <t>not_yet_announced</t>
+        </is>
+      </c>
+      <c r="D37" t="inlineStr">
+        <is>
+          <t>confirmed</t>
+        </is>
+      </c>
+      <c r="E37" t="inlineStr">
+        <is>
+          <t>2026-07-22 18:58 UTC</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="inlineStr">
+        <is>
+          <t>sigcomm</t>
+        </is>
+      </c>
+      <c r="B38" t="inlineStr">
+        <is>
+          <t>workshop_proposal_deadline</t>
+        </is>
+      </c>
+      <c r="D38" t="inlineStr">
+        <is>
+          <t>January 21, 2026</t>
+        </is>
+      </c>
+      <c r="E38" t="inlineStr">
+        <is>
+          <t>2026-07-22 18:58 UTC</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="inlineStr">
+        <is>
+          <t>sigcomm</t>
+        </is>
+      </c>
+      <c r="B39" t="inlineStr">
+        <is>
+          <t>workshop_proposal_status</t>
+        </is>
+      </c>
+      <c r="C39" t="inlineStr">
+        <is>
+          <t>not_yet_announced</t>
+        </is>
+      </c>
+      <c r="D39" t="inlineStr">
+        <is>
+          <t>confirmed</t>
+        </is>
+      </c>
+      <c r="E39" t="inlineStr">
+        <is>
+          <t>2026-07-22 18:58 UTC</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="inlineStr">
+        <is>
+          <t>sigopsatc</t>
+        </is>
+      </c>
+      <c r="B40" t="inlineStr">
+        <is>
+          <t>workshop_proposal_deadline</t>
+        </is>
+      </c>
+      <c r="D40" t="inlineStr">
+        <is>
+          <t>August 1, 2025</t>
+        </is>
+      </c>
+      <c r="E40" t="inlineStr">
+        <is>
+          <t>2026-07-22 18:58 UTC</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="inlineStr">
+        <is>
+          <t>sigopsatc</t>
+        </is>
+      </c>
+      <c r="B41" t="inlineStr">
+        <is>
+          <t>workshop_proposal_status</t>
+        </is>
+      </c>
+      <c r="C41" t="inlineStr">
+        <is>
+          <t>not_yet_announced</t>
+        </is>
+      </c>
+      <c r="D41" t="inlineStr">
+        <is>
+          <t>confirmed</t>
+        </is>
+      </c>
+      <c r="E41" t="inlineStr">
+        <is>
+          <t>2026-07-22 18:58 UTC</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="inlineStr">
+        <is>
+          <t>ubicompiswc</t>
+        </is>
+      </c>
+      <c r="B42" t="inlineStr">
+        <is>
+          <t>workshop_proposal_deadline</t>
+        </is>
+      </c>
+      <c r="D42" t="inlineStr">
+        <is>
+          <t>2026-03-07</t>
+        </is>
+      </c>
+      <c r="E42" t="inlineStr">
+        <is>
+          <t>2026-07-22 18:58 UTC</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="inlineStr">
+        <is>
+          <t>ubicompiswc</t>
+        </is>
+      </c>
+      <c r="B43" t="inlineStr">
+        <is>
+          <t>workshop_proposal_status</t>
+        </is>
+      </c>
+      <c r="C43" t="inlineStr">
+        <is>
+          <t>not_yet_announced</t>
+        </is>
+      </c>
+      <c r="D43" t="inlineStr">
+        <is>
+          <t>confirmed</t>
+        </is>
+      </c>
+      <c r="E43" t="inlineStr">
+        <is>
+          <t>2026-07-22 18:58 UTC</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="inlineStr">
+        <is>
+          <t>uist</t>
+        </is>
+      </c>
+      <c r="B44" t="inlineStr">
+        <is>
+          <t>workshop_proposal_deadline</t>
+        </is>
+      </c>
+      <c r="D44" t="inlineStr">
+        <is>
+          <t>Jul 10, 2026</t>
+        </is>
+      </c>
+      <c r="E44" t="inlineStr">
+        <is>
+          <t>2026-07-22 18:58 UTC</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="inlineStr">
+        <is>
+          <t>uist</t>
+        </is>
+      </c>
+      <c r="B45" t="inlineStr">
+        <is>
+          <t>workshop_proposal_status</t>
+        </is>
+      </c>
+      <c r="C45" t="inlineStr">
+        <is>
+          <t>not_yet_announced</t>
+        </is>
+      </c>
+      <c r="D45" t="inlineStr">
+        <is>
+          <t>confirmed</t>
+        </is>
+      </c>
+      <c r="E45" t="inlineStr">
+        <is>
+          <t>2026-07-22 18:58 UTC</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="inlineStr">
+        <is>
+          <t>sigopsatc</t>
+        </is>
+      </c>
+      <c r="B46" t="inlineStr">
+        <is>
+          <t>workshop_proposal_deadline</t>
+        </is>
+      </c>
+      <c r="C46" t="inlineStr">
+        <is>
+          <t>August 1, 2025</t>
+        </is>
+      </c>
+      <c r="D46" t="inlineStr">
+        <is>
+          <t>April 29, 2025</t>
+        </is>
+      </c>
+      <c r="E46" t="inlineStr">
+        <is>
+          <t>2026-07-22 19:04 UTC</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/conferences.xlsx
+++ b/data/conferences.xlsx
@@ -596,7 +596,7 @@
       </c>
       <c r="P2" t="inlineStr">
         <is>
-          <t>2026-07-22 19:07 UTC</t>
+          <t>2026-07-22 19:12 UTC</t>
         </is>
       </c>
       <c r="R2" t="inlineStr"/>
@@ -662,7 +662,7 @@
       </c>
       <c r="P3" t="inlineStr">
         <is>
-          <t>2026-07-22 19:07 UTC</t>
+          <t>2026-07-22 19:12 UTC</t>
         </is>
       </c>
       <c r="R3" t="inlineStr"/>
@@ -728,7 +728,7 @@
       </c>
       <c r="P4" t="inlineStr">
         <is>
-          <t>2026-07-22 19:07 UTC</t>
+          <t>2026-07-22 19:12 UTC</t>
         </is>
       </c>
       <c r="R4" t="inlineStr"/>
@@ -794,7 +794,7 @@
       </c>
       <c r="P5" t="inlineStr">
         <is>
-          <t>2026-07-22 19:07 UTC</t>
+          <t>2026-07-22 19:12 UTC</t>
         </is>
       </c>
       <c r="R5" t="inlineStr"/>
@@ -860,7 +860,7 @@
       </c>
       <c r="P6" t="inlineStr">
         <is>
-          <t>2026-07-22 19:07 UTC</t>
+          <t>2026-07-22 19:12 UTC</t>
         </is>
       </c>
       <c r="R6" t="inlineStr"/>
@@ -926,7 +926,7 @@
       </c>
       <c r="P7" t="inlineStr">
         <is>
-          <t>2026-07-22 19:07 UTC</t>
+          <t>2026-07-22 19:12 UTC</t>
         </is>
       </c>
       <c r="R7" t="inlineStr"/>
@@ -992,7 +992,7 @@
       </c>
       <c r="P8" t="inlineStr">
         <is>
-          <t>2026-07-22 19:07 UTC</t>
+          <t>2026-07-22 19:12 UTC</t>
         </is>
       </c>
       <c r="R8" t="inlineStr"/>
@@ -1058,7 +1058,7 @@
       </c>
       <c r="P9" t="inlineStr">
         <is>
-          <t>2026-07-22 19:07 UTC</t>
+          <t>2026-07-22 19:12 UTC</t>
         </is>
       </c>
       <c r="R9" t="inlineStr"/>
@@ -1134,7 +1134,7 @@
       </c>
       <c r="P10" t="inlineStr">
         <is>
-          <t>2026-07-22 19:07 UTC</t>
+          <t>2026-07-22 19:12 UTC</t>
         </is>
       </c>
       <c r="Q10" t="inlineStr">
@@ -1214,7 +1214,7 @@
       </c>
       <c r="P11" t="inlineStr">
         <is>
-          <t>2026-07-22 19:07 UTC</t>
+          <t>2026-07-22 19:12 UTC</t>
         </is>
       </c>
       <c r="R11" t="inlineStr"/>
@@ -1290,7 +1290,7 @@
       </c>
       <c r="P12" t="inlineStr">
         <is>
-          <t>2026-07-22 19:07 UTC</t>
+          <t>2026-07-22 19:12 UTC</t>
         </is>
       </c>
       <c r="Q12" t="inlineStr">
@@ -1380,7 +1380,7 @@
       </c>
       <c r="P13" t="inlineStr">
         <is>
-          <t>2026-07-22 19:07 UTC</t>
+          <t>2026-07-22 19:12 UTC</t>
         </is>
       </c>
       <c r="Q13" t="inlineStr">
@@ -1470,7 +1470,7 @@
       </c>
       <c r="P14" t="inlineStr">
         <is>
-          <t>2026-07-22 19:07 UTC</t>
+          <t>2026-07-22 19:12 UTC</t>
         </is>
       </c>
       <c r="Q14" t="inlineStr">
@@ -1550,7 +1550,7 @@
       </c>
       <c r="P15" t="inlineStr">
         <is>
-          <t>2026-07-22 19:07 UTC</t>
+          <t>2026-07-22 19:12 UTC</t>
         </is>
       </c>
       <c r="R15" t="inlineStr"/>
@@ -1616,7 +1616,7 @@
       </c>
       <c r="P16" t="inlineStr">
         <is>
-          <t>2026-07-22 19:07 UTC</t>
+          <t>2026-07-22 19:12 UTC</t>
         </is>
       </c>
       <c r="R16" t="inlineStr"/>
@@ -1682,7 +1682,7 @@
       </c>
       <c r="P17" t="inlineStr">
         <is>
-          <t>2026-07-22 19:07 UTC</t>
+          <t>2026-07-22 19:12 UTC</t>
         </is>
       </c>
       <c r="R17" t="inlineStr"/>
@@ -1758,7 +1758,7 @@
       </c>
       <c r="P18" t="inlineStr">
         <is>
-          <t>2026-07-22 19:07 UTC</t>
+          <t>2026-07-22 19:12 UTC</t>
         </is>
       </c>
       <c r="Q18" t="inlineStr">
@@ -1838,7 +1838,7 @@
       </c>
       <c r="P19" t="inlineStr">
         <is>
-          <t>2026-07-22 19:07 UTC</t>
+          <t>2026-07-22 19:12 UTC</t>
         </is>
       </c>
       <c r="R19" t="inlineStr"/>
@@ -1904,7 +1904,7 @@
       </c>
       <c r="P20" t="inlineStr">
         <is>
-          <t>2026-07-22 19:07 UTC</t>
+          <t>2026-07-22 19:12 UTC</t>
         </is>
       </c>
       <c r="R20" t="inlineStr"/>
@@ -1970,7 +1970,7 @@
       </c>
       <c r="P21" t="inlineStr">
         <is>
-          <t>2026-07-22 19:07 UTC</t>
+          <t>2026-07-22 19:12 UTC</t>
         </is>
       </c>
       <c r="R21" t="inlineStr"/>
@@ -2046,7 +2046,7 @@
       </c>
       <c r="P22" t="inlineStr">
         <is>
-          <t>2026-07-22 19:07 UTC</t>
+          <t>2026-07-22 19:12 UTC</t>
         </is>
       </c>
       <c r="Q22" t="inlineStr">
@@ -2136,7 +2136,7 @@
       </c>
       <c r="P23" t="inlineStr">
         <is>
-          <t>2026-07-22 19:07 UTC</t>
+          <t>2026-07-22 19:12 UTC</t>
         </is>
       </c>
       <c r="Q23" t="inlineStr">
@@ -2216,7 +2216,7 @@
       </c>
       <c r="P24" t="inlineStr">
         <is>
-          <t>2026-07-22 19:07 UTC</t>
+          <t>2026-07-22 19:12 UTC</t>
         </is>
       </c>
       <c r="R24" t="inlineStr"/>
@@ -2287,7 +2287,7 @@
       </c>
       <c r="P25" t="inlineStr">
         <is>
-          <t>2026-07-22 19:07 UTC</t>
+          <t>2026-07-22 19:12 UTC</t>
         </is>
       </c>
       <c r="Q25" t="inlineStr">
@@ -2377,7 +2377,7 @@
       </c>
       <c r="P26" t="inlineStr">
         <is>
-          <t>2026-07-22 19:07 UTC</t>
+          <t>2026-07-22 19:12 UTC</t>
         </is>
       </c>
       <c r="Q26" t="inlineStr">
@@ -2467,7 +2467,7 @@
       </c>
       <c r="P27" t="inlineStr">
         <is>
-          <t>2026-07-22 19:07 UTC</t>
+          <t>2026-07-22 19:12 UTC</t>
         </is>
       </c>
       <c r="Q27" t="inlineStr">
@@ -2557,7 +2557,7 @@
       </c>
       <c r="P28" t="inlineStr">
         <is>
-          <t>2026-07-22 19:07 UTC</t>
+          <t>2026-07-22 19:12 UTC</t>
         </is>
       </c>
       <c r="Q28" t="inlineStr">
@@ -2637,7 +2637,7 @@
       </c>
       <c r="P29" t="inlineStr">
         <is>
-          <t>2026-07-22 19:07 UTC</t>
+          <t>2026-07-22 19:12 UTC</t>
         </is>
       </c>
       <c r="R29" t="inlineStr"/>
@@ -2703,7 +2703,7 @@
       </c>
       <c r="P30" t="inlineStr">
         <is>
-          <t>2026-07-22 19:07 UTC</t>
+          <t>2026-07-22 19:12 UTC</t>
         </is>
       </c>
       <c r="R30" t="inlineStr"/>
@@ -2779,7 +2779,7 @@
       </c>
       <c r="P31" t="inlineStr">
         <is>
-          <t>2026-07-22 19:07 UTC</t>
+          <t>2026-07-22 19:12 UTC</t>
         </is>
       </c>
       <c r="Q31" t="inlineStr">
@@ -2869,7 +2869,7 @@
       </c>
       <c r="P32" t="inlineStr">
         <is>
-          <t>2026-07-22 19:07 UTC</t>
+          <t>2026-07-22 19:12 UTC</t>
         </is>
       </c>
       <c r="Q32" t="inlineStr">
@@ -2949,7 +2949,7 @@
       </c>
       <c r="P33" t="inlineStr">
         <is>
-          <t>2026-07-22 19:07 UTC</t>
+          <t>2026-07-22 19:12 UTC</t>
         </is>
       </c>
       <c r="R33" t="inlineStr"/>
@@ -3025,7 +3025,7 @@
       </c>
       <c r="P34" t="inlineStr">
         <is>
-          <t>2026-07-22 19:07 UTC</t>
+          <t>2026-07-22 19:12 UTC</t>
         </is>
       </c>
       <c r="Q34" t="inlineStr">
@@ -3105,7 +3105,7 @@
       </c>
       <c r="P35" t="inlineStr">
         <is>
-          <t>2026-07-22 19:07 UTC</t>
+          <t>2026-07-22 19:12 UTC</t>
         </is>
       </c>
       <c r="R35" t="inlineStr"/>
@@ -3171,7 +3171,7 @@
       </c>
       <c r="P36" t="inlineStr">
         <is>
-          <t>2026-07-22 19:07 UTC</t>
+          <t>2026-07-22 19:12 UTC</t>
         </is>
       </c>
       <c r="R36" t="inlineStr"/>
@@ -3247,7 +3247,7 @@
       </c>
       <c r="P37" t="inlineStr">
         <is>
-          <t>2026-07-22 19:07 UTC</t>
+          <t>2026-07-22 19:12 UTC</t>
         </is>
       </c>
       <c r="Q37" t="inlineStr">
@@ -3327,7 +3327,7 @@
       </c>
       <c r="P38" t="inlineStr">
         <is>
-          <t>2026-07-22 19:07 UTC</t>
+          <t>2026-07-22 19:12 UTC</t>
         </is>
       </c>
       <c r="R38" t="inlineStr"/>
@@ -3403,7 +3403,7 @@
       </c>
       <c r="P39" t="inlineStr">
         <is>
-          <t>2026-07-22 19:07 UTC</t>
+          <t>2026-07-22 19:12 UTC</t>
         </is>
       </c>
       <c r="Q39" t="inlineStr">
@@ -3483,7 +3483,7 @@
       </c>
       <c r="P40" t="inlineStr">
         <is>
-          <t>2026-07-22 19:07 UTC</t>
+          <t>2026-07-22 19:12 UTC</t>
         </is>
       </c>
       <c r="R40" t="inlineStr"/>
@@ -3559,7 +3559,7 @@
       </c>
       <c r="P41" t="inlineStr">
         <is>
-          <t>2026-07-22 19:07 UTC</t>
+          <t>2026-07-22 19:12 UTC</t>
         </is>
       </c>
       <c r="Q41" t="inlineStr">
@@ -3644,7 +3644,7 @@
       </c>
       <c r="P42" t="inlineStr">
         <is>
-          <t>2026-07-22 19:07 UTC</t>
+          <t>2026-07-22 19:12 UTC</t>
         </is>
       </c>
       <c r="Q42" t="inlineStr">
@@ -3724,7 +3724,7 @@
       </c>
       <c r="P43" t="inlineStr">
         <is>
-          <t>2026-07-22 19:07 UTC</t>
+          <t>2026-07-22 19:12 UTC</t>
         </is>
       </c>
       <c r="R43" t="inlineStr"/>
@@ -3790,7 +3790,7 @@
       </c>
       <c r="P44" t="inlineStr">
         <is>
-          <t>2026-07-22 19:07 UTC</t>
+          <t>2026-07-22 19:12 UTC</t>
         </is>
       </c>
       <c r="R44" t="inlineStr"/>
@@ -3856,7 +3856,7 @@
       </c>
       <c r="P45" t="inlineStr">
         <is>
-          <t>2026-07-22 19:07 UTC</t>
+          <t>2026-07-22 19:12 UTC</t>
         </is>
       </c>
       <c r="R45" t="inlineStr"/>
@@ -3932,7 +3932,7 @@
       </c>
       <c r="P46" t="inlineStr">
         <is>
-          <t>2026-07-22 19:07 UTC</t>
+          <t>2026-07-22 19:12 UTC</t>
         </is>
       </c>
       <c r="Q46" t="inlineStr">
@@ -4012,7 +4012,7 @@
       </c>
       <c r="P47" t="inlineStr">
         <is>
-          <t>2026-07-22 19:07 UTC</t>
+          <t>2026-07-22 19:12 UTC</t>
         </is>
       </c>
       <c r="R47" t="inlineStr"/>
@@ -4078,7 +4078,7 @@
       </c>
       <c r="P48" t="inlineStr">
         <is>
-          <t>2026-07-22 19:07 UTC</t>
+          <t>2026-07-22 19:12 UTC</t>
         </is>
       </c>
       <c r="R48" t="inlineStr"/>
@@ -4144,7 +4144,7 @@
       </c>
       <c r="P49" t="inlineStr">
         <is>
-          <t>2026-07-22 19:07 UTC</t>
+          <t>2026-07-22 19:12 UTC</t>
         </is>
       </c>
       <c r="R49" t="inlineStr"/>
@@ -4220,7 +4220,7 @@
       </c>
       <c r="P50" t="inlineStr">
         <is>
-          <t>2026-07-22 19:07 UTC</t>
+          <t>2026-07-22 19:12 UTC</t>
         </is>
       </c>
       <c r="Q50" t="inlineStr">
@@ -4300,7 +4300,7 @@
       </c>
       <c r="P51" t="inlineStr">
         <is>
-          <t>2026-07-22 19:07 UTC</t>
+          <t>2026-07-22 19:12 UTC</t>
         </is>
       </c>
       <c r="R51" t="inlineStr"/>
@@ -4366,7 +4366,7 @@
       </c>
       <c r="P52" t="inlineStr">
         <is>
-          <t>2026-07-22 19:07 UTC</t>
+          <t>2026-07-22 19:12 UTC</t>
         </is>
       </c>
       <c r="R52" t="inlineStr"/>
@@ -4432,7 +4432,7 @@
       </c>
       <c r="P53" t="inlineStr">
         <is>
-          <t>2026-07-22 19:07 UTC</t>
+          <t>2026-07-22 19:12 UTC</t>
         </is>
       </c>
       <c r="R53" t="inlineStr"/>
@@ -4498,7 +4498,7 @@
       </c>
       <c r="P54" t="inlineStr">
         <is>
-          <t>2026-07-22 19:07 UTC</t>
+          <t>2026-07-22 19:12 UTC</t>
         </is>
       </c>
       <c r="R54" t="inlineStr"/>
@@ -4574,7 +4574,7 @@
       </c>
       <c r="P55" t="inlineStr">
         <is>
-          <t>2026-07-22 19:07 UTC</t>
+          <t>2026-07-22 19:12 UTC</t>
         </is>
       </c>
       <c r="Q55" t="inlineStr">
@@ -4664,7 +4664,7 @@
       </c>
       <c r="P56" t="inlineStr">
         <is>
-          <t>2026-07-22 19:07 UTC</t>
+          <t>2026-07-22 19:12 UTC</t>
         </is>
       </c>
       <c r="Q56" t="inlineStr">
@@ -4744,7 +4744,7 @@
       </c>
       <c r="P57" t="inlineStr">
         <is>
-          <t>2026-07-22 19:07 UTC</t>
+          <t>2026-07-22 19:12 UTC</t>
         </is>
       </c>
       <c r="R57" t="inlineStr"/>
@@ -4810,7 +4810,7 @@
       </c>
       <c r="P58" t="inlineStr">
         <is>
-          <t>2026-07-22 19:07 UTC</t>
+          <t>2026-07-22 19:12 UTC</t>
         </is>
       </c>
       <c r="R58" t="inlineStr"/>
@@ -4876,7 +4876,7 @@
       </c>
       <c r="P59" t="inlineStr">
         <is>
-          <t>2026-07-22 19:07 UTC</t>
+          <t>2026-07-22 19:12 UTC</t>
         </is>
       </c>
       <c r="R59" t="inlineStr"/>

--- a/data/conferences.xlsx
+++ b/data/conferences.xlsx
@@ -414,7 +414,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:S59"/>
+  <dimension ref="A1:R59"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="20" customWidth="1" min="1" max="1"/>
@@ -435,7 +435,6 @@
     <col width="20" customWidth="1" min="16" max="16"/>
     <col width="20" customWidth="1" min="17" max="17"/>
     <col width="20" customWidth="1" min="18" max="18"/>
-    <col width="20" customWidth="1" min="19" max="19"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -481,55 +480,50 @@
       </c>
       <c r="I1" t="inlineStr">
         <is>
-          <t>date_start</t>
+          <t>date</t>
         </is>
       </c>
       <c r="J1" t="inlineStr">
         <is>
-          <t>date_end</t>
+          <t>official_url</t>
         </is>
       </c>
       <c r="K1" t="inlineStr">
         <is>
-          <t>official_url</t>
+          <t>main_cfp_deadline</t>
         </is>
       </c>
       <c r="L1" t="inlineStr">
         <is>
-          <t>main_cfp_deadline</t>
+          <t>workshop_proposal_deadline</t>
         </is>
       </c>
       <c r="M1" t="inlineStr">
         <is>
-          <t>workshop_proposal_deadline</t>
+          <t>workshop_proposal_status</t>
         </is>
       </c>
       <c r="N1" t="inlineStr">
         <is>
-          <t>workshop_proposal_status</t>
+          <t>workshop_page_url</t>
         </is>
       </c>
       <c r="O1" t="inlineStr">
         <is>
-          <t>workshop_page_url</t>
+          <t>last_checked_at</t>
         </is>
       </c>
       <c r="P1" t="inlineStr">
         <is>
-          <t>last_checked_at</t>
+          <t>last_changed_at</t>
         </is>
       </c>
       <c r="Q1" t="inlineStr">
         <is>
-          <t>last_changed_at</t>
+          <t>source_url</t>
         </is>
       </c>
       <c r="R1" t="inlineStr">
-        <is>
-          <t>source_url</t>
-        </is>
-      </c>
-      <c r="S1" t="inlineStr">
         <is>
           <t>notes</t>
         </is>
@@ -576,30 +570,29 @@
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>February 16-23, 2027</t>
+          <t>02.16-02.23</t>
+        </is>
+      </c>
+      <c r="J2" t="inlineStr">
+        <is>
+          <t>https://aaai.org/conference/aaai/aaai-27/</t>
         </is>
       </c>
       <c r="K2" t="inlineStr">
         <is>
-          <t>https://aaai.org/conference/aaai/aaai-27/</t>
-        </is>
-      </c>
-      <c r="L2" t="inlineStr">
-        <is>
           <t>2026-07-28</t>
         </is>
       </c>
-      <c r="N2" t="inlineStr">
-        <is>
-          <t>not_yet_announced</t>
-        </is>
-      </c>
-      <c r="P2" t="inlineStr">
-        <is>
-          <t>2026-07-22 19:07 UTC</t>
-        </is>
-      </c>
-      <c r="R2" t="inlineStr"/>
+      <c r="M2" t="inlineStr">
+        <is>
+          <t>not_yet_announced</t>
+        </is>
+      </c>
+      <c r="O2" t="inlineStr">
+        <is>
+          <t>2026-07-22 19:22 UTC</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -642,30 +635,29 @@
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>August 17-22, 2027</t>
+          <t>08.17-08.22</t>
+        </is>
+      </c>
+      <c r="J3" t="inlineStr">
+        <is>
+          <t>https://2027.aclweb.org/</t>
         </is>
       </c>
       <c r="K3" t="inlineStr">
         <is>
-          <t>https://2027.aclweb.org/</t>
-        </is>
-      </c>
-      <c r="L3" t="inlineStr">
-        <is>
-          <t>TBD</t>
-        </is>
-      </c>
-      <c r="N3" t="inlineStr">
-        <is>
-          <t>not_yet_announced</t>
-        </is>
-      </c>
-      <c r="P3" t="inlineStr">
-        <is>
-          <t>2026-07-22 19:07 UTC</t>
-        </is>
-      </c>
-      <c r="R3" t="inlineStr"/>
+          <t>TBD</t>
+        </is>
+      </c>
+      <c r="M3" t="inlineStr">
+        <is>
+          <t>not_yet_announced</t>
+        </is>
+      </c>
+      <c r="O3" t="inlineStr">
+        <is>
+          <t>2026-07-22 19:22 UTC</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -684,54 +676,37 @@
         </is>
       </c>
       <c r="D4" t="n">
-        <v>2026</v>
+        <v>2027</v>
       </c>
       <c r="E4" t="inlineStr">
         <is>
           <t>CG</t>
         </is>
       </c>
-      <c r="F4" t="inlineStr">
-        <is>
-          <t>Rio de Janeiro</t>
-        </is>
-      </c>
-      <c r="G4" t="inlineStr">
-        <is>
-          <t>Brazil</t>
-        </is>
-      </c>
-      <c r="H4" t="inlineStr">
-        <is>
-          <t>Latin America</t>
-        </is>
-      </c>
+      <c r="F4" t="inlineStr"/>
+      <c r="G4" t="inlineStr"/>
+      <c r="H4" t="inlineStr"/>
       <c r="I4" t="inlineStr">
         <is>
-          <t>November 10-14, 2026</t>
-        </is>
-      </c>
+          <t>TBD</t>
+        </is>
+      </c>
+      <c r="J4" t="inlineStr"/>
       <c r="K4" t="inlineStr">
         <is>
-          <t>https://2026.acmmm.org/</t>
-        </is>
-      </c>
-      <c r="L4" t="inlineStr">
-        <is>
-          <t>2026-04-01</t>
-        </is>
-      </c>
-      <c r="N4" t="inlineStr">
-        <is>
-          <t>not_yet_announced</t>
-        </is>
-      </c>
-      <c r="P4" t="inlineStr">
-        <is>
-          <t>2026-07-22 19:07 UTC</t>
-        </is>
-      </c>
-      <c r="R4" t="inlineStr"/>
+          <t>TBD</t>
+        </is>
+      </c>
+      <c r="M4" t="inlineStr">
+        <is>
+          <t>not_yet_announced</t>
+        </is>
+      </c>
+      <c r="O4" t="inlineStr">
+        <is>
+          <t>2026-07-22 19:22 UTC</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -750,54 +725,37 @@
         </is>
       </c>
       <c r="D5" t="n">
-        <v>2026</v>
+        <v>2027</v>
       </c>
       <c r="E5" t="inlineStr">
         <is>
           <t>CG</t>
         </is>
       </c>
-      <c r="F5" t="inlineStr">
-        <is>
-          <t>Los Angeles, California</t>
-        </is>
-      </c>
-      <c r="G5" t="inlineStr">
-        <is>
-          <t>USA</t>
-        </is>
-      </c>
-      <c r="H5" t="inlineStr">
-        <is>
-          <t>North America</t>
-        </is>
-      </c>
+      <c r="F5" t="inlineStr"/>
+      <c r="G5" t="inlineStr"/>
+      <c r="H5" t="inlineStr"/>
       <c r="I5" t="inlineStr">
         <is>
-          <t>July 19 - 23, 2026</t>
-        </is>
-      </c>
+          <t>TBD</t>
+        </is>
+      </c>
+      <c r="J5" t="inlineStr"/>
       <c r="K5" t="inlineStr">
         <is>
-          <t>https://s2026.siggraph.org/</t>
-        </is>
-      </c>
-      <c r="L5" t="inlineStr">
-        <is>
-          <t>2026-01-22</t>
-        </is>
-      </c>
-      <c r="N5" t="inlineStr">
-        <is>
-          <t>not_yet_announced</t>
-        </is>
-      </c>
-      <c r="P5" t="inlineStr">
-        <is>
-          <t>2026-07-22 19:07 UTC</t>
-        </is>
-      </c>
-      <c r="R5" t="inlineStr"/>
+          <t>TBD</t>
+        </is>
+      </c>
+      <c r="M5" t="inlineStr">
+        <is>
+          <t>not_yet_announced</t>
+        </is>
+      </c>
+      <c r="O5" t="inlineStr">
+        <is>
+          <t>2026-07-22 19:22 UTC</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -816,54 +774,37 @@
         </is>
       </c>
       <c r="D6" t="n">
-        <v>2026</v>
+        <v>2027</v>
       </c>
       <c r="E6" t="inlineStr">
         <is>
           <t>SE</t>
         </is>
       </c>
-      <c r="F6" t="inlineStr">
-        <is>
-          <t>Munich</t>
-        </is>
-      </c>
-      <c r="G6" t="inlineStr">
-        <is>
-          <t>Germany</t>
-        </is>
-      </c>
-      <c r="H6" t="inlineStr">
-        <is>
-          <t>Europe</t>
-        </is>
-      </c>
+      <c r="F6" t="inlineStr"/>
+      <c r="G6" t="inlineStr"/>
+      <c r="H6" t="inlineStr"/>
       <c r="I6" t="inlineStr">
         <is>
-          <t>October 12 - 16, 2026</t>
-        </is>
-      </c>
+          <t>TBD</t>
+        </is>
+      </c>
+      <c r="J6" t="inlineStr"/>
       <c r="K6" t="inlineStr">
         <is>
-          <t>https://conf.researchr.org/home/ase-2026</t>
-        </is>
-      </c>
-      <c r="L6" t="inlineStr">
-        <is>
-          <t>2026-03-26</t>
-        </is>
-      </c>
-      <c r="N6" t="inlineStr">
-        <is>
-          <t>not_yet_announced</t>
-        </is>
-      </c>
-      <c r="P6" t="inlineStr">
-        <is>
-          <t>2026-07-22 19:07 UTC</t>
-        </is>
-      </c>
-      <c r="R6" t="inlineStr"/>
+          <t>TBD</t>
+        </is>
+      </c>
+      <c r="M6" t="inlineStr">
+        <is>
+          <t>not_yet_announced</t>
+        </is>
+      </c>
+      <c r="O6" t="inlineStr">
+        <is>
+          <t>2026-07-22 19:22 UTC</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -906,30 +847,29 @@
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>April 11-15, 2027</t>
+          <t>04.11-04.15</t>
+        </is>
+      </c>
+      <c r="J7" t="inlineStr">
+        <is>
+          <t>https://www.asplos-conference.org/asplos2027/cfp/</t>
         </is>
       </c>
       <c r="K7" t="inlineStr">
         <is>
-          <t>https://www.asplos-conference.org/asplos2027/cfp/</t>
-        </is>
-      </c>
-      <c r="L7" t="inlineStr">
-        <is>
           <t>2026-04-15</t>
         </is>
       </c>
-      <c r="N7" t="inlineStr">
-        <is>
-          <t>not_yet_announced</t>
-        </is>
-      </c>
-      <c r="P7" t="inlineStr">
-        <is>
-          <t>2026-07-22 19:07 UTC</t>
-        </is>
-      </c>
-      <c r="R7" t="inlineStr"/>
+      <c r="M7" t="inlineStr">
+        <is>
+          <t>not_yet_announced</t>
+        </is>
+      </c>
+      <c r="O7" t="inlineStr">
+        <is>
+          <t>2026-07-22 19:22 UTC</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -948,54 +888,37 @@
         </is>
       </c>
       <c r="D8" t="n">
-        <v>2026</v>
+        <v>2027</v>
       </c>
       <c r="E8" t="inlineStr">
         <is>
           <t>CT</t>
         </is>
       </c>
-      <c r="F8" t="inlineStr">
-        <is>
-          <t>Lisbon</t>
-        </is>
-      </c>
-      <c r="G8" t="inlineStr">
-        <is>
-          <t>Portugal</t>
-        </is>
-      </c>
-      <c r="H8" t="inlineStr">
-        <is>
-          <t>Europe</t>
-        </is>
-      </c>
+      <c r="F8" t="inlineStr"/>
+      <c r="G8" t="inlineStr"/>
+      <c r="H8" t="inlineStr"/>
       <c r="I8" t="inlineStr">
         <is>
-          <t>July 26-29, 2026</t>
-        </is>
-      </c>
+          <t>TBD</t>
+        </is>
+      </c>
+      <c r="J8" t="inlineStr"/>
       <c r="K8" t="inlineStr">
         <is>
-          <t>https://conferences.i-cav.org/2026/</t>
-        </is>
-      </c>
-      <c r="L8" t="inlineStr">
-        <is>
-          <t>2026-01-28</t>
-        </is>
-      </c>
-      <c r="N8" t="inlineStr">
-        <is>
-          <t>not_yet_announced</t>
-        </is>
-      </c>
-      <c r="P8" t="inlineStr">
-        <is>
-          <t>2026-07-22 19:07 UTC</t>
-        </is>
-      </c>
-      <c r="R8" t="inlineStr"/>
+          <t>TBD</t>
+        </is>
+      </c>
+      <c r="M8" t="inlineStr">
+        <is>
+          <t>not_yet_announced</t>
+        </is>
+      </c>
+      <c r="O8" t="inlineStr">
+        <is>
+          <t>2026-07-22 19:22 UTC</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -1014,54 +937,37 @@
         </is>
       </c>
       <c r="D9" t="n">
-        <v>2026</v>
+        <v>2027</v>
       </c>
       <c r="E9" t="inlineStr">
         <is>
           <t>SC</t>
         </is>
       </c>
-      <c r="F9" t="inlineStr">
-        <is>
-          <t>World Forum, Hague</t>
-        </is>
-      </c>
-      <c r="G9" t="inlineStr">
-        <is>
-          <t>Netherlands</t>
-        </is>
-      </c>
-      <c r="H9" t="inlineStr">
-        <is>
-          <t>Europe</t>
-        </is>
-      </c>
+      <c r="F9" t="inlineStr"/>
+      <c r="G9" t="inlineStr"/>
+      <c r="H9" t="inlineStr"/>
       <c r="I9" t="inlineStr">
         <is>
-          <t>November 15-19, 2026</t>
-        </is>
-      </c>
+          <t>TBD</t>
+        </is>
+      </c>
+      <c r="J9" t="inlineStr"/>
       <c r="K9" t="inlineStr">
         <is>
-          <t>https://www.sigsac.org/ccs/CCS2026/</t>
-        </is>
-      </c>
-      <c r="L9" t="inlineStr">
-        <is>
-          <t>2026-01-14</t>
-        </is>
-      </c>
-      <c r="N9" t="inlineStr">
-        <is>
-          <t>not_yet_announced</t>
-        </is>
-      </c>
-      <c r="P9" t="inlineStr">
-        <is>
-          <t>2026-07-22 19:07 UTC</t>
-        </is>
-      </c>
-      <c r="R9" t="inlineStr"/>
+          <t>TBD</t>
+        </is>
+      </c>
+      <c r="M9" t="inlineStr">
+        <is>
+          <t>not_yet_announced</t>
+        </is>
+      </c>
+      <c r="O9" t="inlineStr">
+        <is>
+          <t>2026-07-22 19:22 UTC</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -1104,50 +1010,50 @@
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>May 10 - 14, 2027</t>
+          <t>05.10-05.14</t>
+        </is>
+      </c>
+      <c r="J10" t="inlineStr">
+        <is>
+          <t>https://chi2027.acm.org/</t>
         </is>
       </c>
       <c r="K10" t="inlineStr">
         <is>
-          <t>https://chi2027.acm.org/</t>
+          <t>2026-09-10</t>
         </is>
       </c>
       <c r="L10" t="inlineStr">
         <is>
-          <t>2026-09-10</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="M10" t="inlineStr">
         <is>
-          <t>September 28, 2026</t>
+          <t>confirmed</t>
         </is>
       </c>
       <c r="N10" t="inlineStr">
         <is>
-          <t>confirmed</t>
+          <t>https://chi2027.acm.org/authors/workshops/</t>
         </is>
       </c>
       <c r="O10" t="inlineStr">
         <is>
+          <t>2026-07-22 19:22 UTC</t>
+        </is>
+      </c>
+      <c r="P10" t="inlineStr">
+        <is>
+          <t>2026-07-22 19:22 UTC</t>
+        </is>
+      </c>
+      <c r="Q10" t="inlineStr">
+        <is>
           <t>https://chi2027.acm.org/authors/workshops/</t>
         </is>
       </c>
-      <c r="P10" t="inlineStr">
-        <is>
-          <t>2026-07-22 19:07 UTC</t>
-        </is>
-      </c>
-      <c r="Q10" t="inlineStr">
-        <is>
-          <t>2026-07-22 18:58 UTC</t>
-        </is>
-      </c>
       <c r="R10" t="inlineStr">
-        <is>
-          <t>https://chi2027.acm.org/authors/workshops/</t>
-        </is>
-      </c>
-      <c r="S10" t="inlineStr">
         <is>
           <t>extracted from official site</t>
         </is>
@@ -1170,54 +1076,37 @@
         </is>
       </c>
       <c r="D11" t="n">
-        <v>2026</v>
+        <v>2027</v>
       </c>
       <c r="E11" t="inlineStr">
         <is>
           <t>SC</t>
         </is>
       </c>
-      <c r="F11" t="inlineStr">
-        <is>
-          <t>Santa Barbara</t>
-        </is>
-      </c>
-      <c r="G11" t="inlineStr">
-        <is>
-          <t>USA</t>
-        </is>
-      </c>
-      <c r="H11" t="inlineStr">
-        <is>
-          <t>North America</t>
-        </is>
-      </c>
+      <c r="F11" t="inlineStr"/>
+      <c r="G11" t="inlineStr"/>
+      <c r="H11" t="inlineStr"/>
       <c r="I11" t="inlineStr">
         <is>
-          <t>August 17-20, 2026</t>
-        </is>
-      </c>
+          <t>TBD</t>
+        </is>
+      </c>
+      <c r="J11" t="inlineStr"/>
       <c r="K11" t="inlineStr">
         <is>
-          <t>https://crypto.iacr.org/2026/</t>
-        </is>
-      </c>
-      <c r="L11" t="inlineStr">
-        <is>
-          <t>2026-02-12</t>
-        </is>
-      </c>
-      <c r="N11" t="inlineStr">
-        <is>
-          <t>not_yet_announced</t>
-        </is>
-      </c>
-      <c r="P11" t="inlineStr">
-        <is>
-          <t>2026-07-22 19:07 UTC</t>
-        </is>
-      </c>
-      <c r="R11" t="inlineStr"/>
+          <t>TBD</t>
+        </is>
+      </c>
+      <c r="M11" t="inlineStr">
+        <is>
+          <t>not_yet_announced</t>
+        </is>
+      </c>
+      <c r="O11" t="inlineStr">
+        <is>
+          <t>2026-07-22 19:22 UTC</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
@@ -1236,76 +1125,45 @@
         </is>
       </c>
       <c r="D12" t="n">
-        <v>2026</v>
+        <v>2027</v>
       </c>
       <c r="E12" t="inlineStr">
         <is>
           <t>HI</t>
         </is>
       </c>
-      <c r="F12" t="inlineStr">
-        <is>
-          <t>Salt Lake City, Utah</t>
-        </is>
-      </c>
-      <c r="G12" t="inlineStr">
-        <is>
-          <t>USA</t>
-        </is>
-      </c>
-      <c r="H12" t="inlineStr">
-        <is>
-          <t>North America</t>
-        </is>
-      </c>
+      <c r="F12" t="inlineStr"/>
+      <c r="G12" t="inlineStr"/>
+      <c r="H12" t="inlineStr"/>
       <c r="I12" t="inlineStr">
         <is>
-          <t>October 10-14, 2026</t>
-        </is>
-      </c>
+          <t>TBD</t>
+        </is>
+      </c>
+      <c r="J12" t="inlineStr"/>
       <c r="K12" t="inlineStr">
         <is>
-          <t>https://cscw.acm.org/2026/</t>
-        </is>
-      </c>
-      <c r="L12" t="inlineStr">
-        <is>
-          <t>2025-05-13</t>
+          <t>TBD</t>
         </is>
       </c>
       <c r="M12" t="inlineStr">
         <is>
-          <t>April 10, 2026</t>
-        </is>
-      </c>
-      <c r="N12" t="inlineStr">
-        <is>
-          <t>confirmed</t>
+          <t>not_yet_announced</t>
         </is>
       </c>
       <c r="O12" t="inlineStr">
         <is>
-          <t>https://cscw.acm.org/2026/workshops.html</t>
+          <t>2026-07-22 19:22 UTC</t>
         </is>
       </c>
       <c r="P12" t="inlineStr">
         <is>
-          <t>2026-07-22 19:07 UTC</t>
-        </is>
-      </c>
-      <c r="Q12" t="inlineStr">
-        <is>
-          <t>2026-07-22 18:58 UTC</t>
+          <t>2026-07-22 19:22 UTC</t>
         </is>
       </c>
       <c r="R12" t="inlineStr">
         <is>
-          <t>https://cscw.acm.org/2026/workshops.html</t>
-        </is>
-      </c>
-      <c r="S12" t="inlineStr">
-        <is>
-          <t>extracted from official site</t>
+          <t>需要人工核实官网（未配置搜索API做兜底）</t>
         </is>
       </c>
     </row>
@@ -1326,76 +1184,45 @@
         </is>
       </c>
       <c r="D13" t="n">
-        <v>2026</v>
+        <v>2027</v>
       </c>
       <c r="E13" t="inlineStr">
         <is>
           <t>AI</t>
         </is>
       </c>
-      <c r="F13" t="inlineStr">
-        <is>
-          <t>Denver, Colorado</t>
-        </is>
-      </c>
-      <c r="G13" t="inlineStr">
-        <is>
-          <t>United States</t>
-        </is>
-      </c>
-      <c r="H13" t="inlineStr">
-        <is>
-          <t>North America</t>
-        </is>
-      </c>
+      <c r="F13" t="inlineStr"/>
+      <c r="G13" t="inlineStr"/>
+      <c r="H13" t="inlineStr"/>
       <c r="I13" t="inlineStr">
         <is>
-          <t>June 3-7, 2026</t>
-        </is>
-      </c>
+          <t>TBD</t>
+        </is>
+      </c>
+      <c r="J13" t="inlineStr"/>
       <c r="K13" t="inlineStr">
         <is>
-          <t>https://cvpr.thecvf.com/Conferences/2026</t>
-        </is>
-      </c>
-      <c r="L13" t="inlineStr">
-        <is>
-          <t>2025-11-13</t>
+          <t>TBD</t>
         </is>
       </c>
       <c r="M13" t="inlineStr">
         <is>
-          <t>Nov 03, 2025</t>
-        </is>
-      </c>
-      <c r="N13" t="inlineStr">
-        <is>
-          <t>confirmed</t>
+          <t>not_yet_announced</t>
         </is>
       </c>
       <c r="O13" t="inlineStr">
         <is>
-          <t>https://cvpr.thecvf.com/Conferences/2026/CallForWorkshops</t>
+          <t>2026-07-22 19:22 UTC</t>
         </is>
       </c>
       <c r="P13" t="inlineStr">
         <is>
-          <t>2026-07-22 19:07 UTC</t>
-        </is>
-      </c>
-      <c r="Q13" t="inlineStr">
-        <is>
-          <t>2026-07-22 18:58 UTC</t>
+          <t>2026-07-22 19:22 UTC</t>
         </is>
       </c>
       <c r="R13" t="inlineStr">
         <is>
-          <t>https://cvpr.thecvf.com/Conferences/2026/CallForWorkshops</t>
-        </is>
-      </c>
-      <c r="S13" t="inlineStr">
-        <is>
-          <t>extracted from official site</t>
+          <t>需要人工核实官网（未配置搜索API做兜底）</t>
         </is>
       </c>
     </row>
@@ -1416,76 +1243,45 @@
         </is>
       </c>
       <c r="D14" t="n">
-        <v>2026</v>
+        <v>2027</v>
       </c>
       <c r="E14" t="inlineStr">
         <is>
           <t>DS</t>
         </is>
       </c>
-      <c r="F14" t="inlineStr">
-        <is>
-          <t>Long Beach, CA</t>
-        </is>
-      </c>
-      <c r="G14" t="inlineStr">
-        <is>
-          <t>USA</t>
-        </is>
-      </c>
-      <c r="H14" t="inlineStr">
-        <is>
-          <t>North America</t>
-        </is>
-      </c>
+      <c r="F14" t="inlineStr"/>
+      <c r="G14" t="inlineStr"/>
+      <c r="H14" t="inlineStr"/>
       <c r="I14" t="inlineStr">
         <is>
-          <t>July 26-29, 2026</t>
-        </is>
-      </c>
+          <t>TBD</t>
+        </is>
+      </c>
+      <c r="J14" t="inlineStr"/>
       <c r="K14" t="inlineStr">
         <is>
-          <t>https://dac.com/2026/call-for-contributions</t>
-        </is>
-      </c>
-      <c r="L14" t="inlineStr">
-        <is>
-          <t>2025-11-18</t>
+          <t>TBD</t>
         </is>
       </c>
       <c r="M14" t="inlineStr">
         <is>
-          <t>Apr 29, 2026</t>
-        </is>
-      </c>
-      <c r="N14" t="inlineStr">
-        <is>
-          <t>confirmed</t>
+          <t>not_yet_announced</t>
         </is>
       </c>
       <c r="O14" t="inlineStr">
         <is>
-          <t>https://dac.com/2026/workshop-call-for-proposals</t>
+          <t>2026-07-22 19:22 UTC</t>
         </is>
       </c>
       <c r="P14" t="inlineStr">
         <is>
-          <t>2026-07-22 19:07 UTC</t>
-        </is>
-      </c>
-      <c r="Q14" t="inlineStr">
-        <is>
-          <t>2026-07-22 18:58 UTC</t>
+          <t>2026-07-22 19:22 UTC</t>
         </is>
       </c>
       <c r="R14" t="inlineStr">
         <is>
-          <t>https://dac.com/2026/workshop-call-for-proposals</t>
-        </is>
-      </c>
-      <c r="S14" t="inlineStr">
-        <is>
-          <t>extracted from official site</t>
+          <t>需要人工核实官网（未配置搜索API做兜底）</t>
         </is>
       </c>
     </row>
@@ -1530,30 +1326,29 @@
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>April 11-15, 2027</t>
+          <t>04.11-04.15</t>
+        </is>
+      </c>
+      <c r="J15" t="inlineStr">
+        <is>
+          <t>https://eurocrypt.iacr.org/2027/</t>
         </is>
       </c>
       <c r="K15" t="inlineStr">
         <is>
-          <t>https://eurocrypt.iacr.org/2027/</t>
-        </is>
-      </c>
-      <c r="L15" t="inlineStr">
-        <is>
           <t>2026-09-17</t>
         </is>
       </c>
-      <c r="N15" t="inlineStr">
-        <is>
-          <t>not_yet_announced</t>
-        </is>
-      </c>
-      <c r="P15" t="inlineStr">
-        <is>
-          <t>2026-07-22 19:07 UTC</t>
-        </is>
-      </c>
-      <c r="R15" t="inlineStr"/>
+      <c r="M15" t="inlineStr">
+        <is>
+          <t>not_yet_announced</t>
+        </is>
+      </c>
+      <c r="O15" t="inlineStr">
+        <is>
+          <t>2026-07-22 19:22 UTC</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
@@ -1596,30 +1391,29 @@
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>April 19-24, 2027</t>
+          <t>04.19-04.24</t>
+        </is>
+      </c>
+      <c r="J16" t="inlineStr">
+        <is>
+          <t>https://2027.eurosys.org/</t>
         </is>
       </c>
       <c r="K16" t="inlineStr">
         <is>
-          <t>https://2027.eurosys.org/</t>
-        </is>
-      </c>
-      <c r="L16" t="inlineStr">
-        <is>
           <t>2026-05-14</t>
         </is>
       </c>
-      <c r="N16" t="inlineStr">
-        <is>
-          <t>not_yet_announced</t>
-        </is>
-      </c>
-      <c r="P16" t="inlineStr">
-        <is>
-          <t>2026-07-22 19:07 UTC</t>
-        </is>
-      </c>
-      <c r="R16" t="inlineStr"/>
+      <c r="M16" t="inlineStr">
+        <is>
+          <t>not_yet_announced</t>
+        </is>
+      </c>
+      <c r="O16" t="inlineStr">
+        <is>
+          <t>2026-07-22 19:22 UTC</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
@@ -1662,30 +1456,29 @@
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>FEBRUARY 23-25, 2027</t>
+          <t>02.23-02.25</t>
+        </is>
+      </c>
+      <c r="J17" t="inlineStr">
+        <is>
+          <t>https://www.usenix.org/conference/fast27</t>
         </is>
       </c>
       <c r="K17" t="inlineStr">
         <is>
-          <t>https://www.usenix.org/conference/fast27</t>
-        </is>
-      </c>
-      <c r="L17" t="inlineStr">
-        <is>
           <t>2026-03-17</t>
         </is>
       </c>
-      <c r="N17" t="inlineStr">
-        <is>
-          <t>not_yet_announced</t>
-        </is>
-      </c>
-      <c r="P17" t="inlineStr">
-        <is>
-          <t>2026-07-22 19:07 UTC</t>
-        </is>
-      </c>
-      <c r="R17" t="inlineStr"/>
+      <c r="M17" t="inlineStr">
+        <is>
+          <t>not_yet_announced</t>
+        </is>
+      </c>
+      <c r="O17" t="inlineStr">
+        <is>
+          <t>2026-07-22 19:22 UTC</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
@@ -1704,76 +1497,45 @@
         </is>
       </c>
       <c r="D18" t="n">
-        <v>2026</v>
+        <v>2027</v>
       </c>
       <c r="E18" t="inlineStr">
         <is>
           <t>SE</t>
         </is>
       </c>
-      <c r="F18" t="inlineStr">
-        <is>
-          <t>Tokyo</t>
-        </is>
-      </c>
-      <c r="G18" t="inlineStr">
-        <is>
-          <t>Japan</t>
-        </is>
-      </c>
-      <c r="H18" t="inlineStr">
-        <is>
-          <t>Asia</t>
-        </is>
-      </c>
+      <c r="F18" t="inlineStr"/>
+      <c r="G18" t="inlineStr"/>
+      <c r="H18" t="inlineStr"/>
       <c r="I18" t="inlineStr">
         <is>
-          <t>May 18-22, 2026</t>
-        </is>
-      </c>
+          <t>TBD</t>
+        </is>
+      </c>
+      <c r="J18" t="inlineStr"/>
       <c r="K18" t="inlineStr">
         <is>
-          <t>https://conf.researchr.org/home/fm-2026</t>
-        </is>
-      </c>
-      <c r="L18" t="inlineStr">
-        <is>
-          <t>2025-12-02</t>
+          <t>TBD</t>
         </is>
       </c>
       <c r="M18" t="inlineStr">
         <is>
-          <t>November 10, 2025</t>
-        </is>
-      </c>
-      <c r="N18" t="inlineStr">
-        <is>
-          <t>confirmed</t>
+          <t>not_yet_announced</t>
         </is>
       </c>
       <c r="O18" t="inlineStr">
         <is>
-          <t>https://conf.researchr.org/track/fm-2026/fm-2026-workshops</t>
+          <t>2026-07-22 19:22 UTC</t>
         </is>
       </c>
       <c r="P18" t="inlineStr">
         <is>
-          <t>2026-07-22 19:07 UTC</t>
-        </is>
-      </c>
-      <c r="Q18" t="inlineStr">
-        <is>
-          <t>2026-07-22 18:58 UTC</t>
+          <t>2026-07-22 19:22 UTC</t>
         </is>
       </c>
       <c r="R18" t="inlineStr">
         <is>
-          <t>https://conf.researchr.org/track/fm-2026/fm-2026-workshops</t>
-        </is>
-      </c>
-      <c r="S18" t="inlineStr">
-        <is>
-          <t>extracted from official site</t>
+          <t>需要人工核实官网（未配置搜索API做兜底）</t>
         </is>
       </c>
     </row>
@@ -1794,53 +1556,37 @@
         </is>
       </c>
       <c r="D19" t="n">
-        <v>2026</v>
+        <v>2027</v>
       </c>
       <c r="E19" t="inlineStr">
         <is>
           <t>CT</t>
         </is>
       </c>
-      <c r="F19" t="inlineStr">
-        <is>
-          <t>New York City, NY</t>
-        </is>
-      </c>
-      <c r="G19" t="inlineStr">
-        <is>
-          <t>USA</t>
-        </is>
-      </c>
-      <c r="H19" t="inlineStr">
-        <is>
-          <t>North America</t>
-        </is>
-      </c>
+      <c r="F19" t="inlineStr"/>
+      <c r="G19" t="inlineStr"/>
+      <c r="H19" t="inlineStr"/>
       <c r="I19" t="inlineStr">
         <is>
-          <t>November 8-11, 2026</t>
-        </is>
-      </c>
+          <t>TBD</t>
+        </is>
+      </c>
+      <c r="J19" t="inlineStr"/>
       <c r="K19" t="inlineStr">
         <is>
-          <t>https://sanjeevkhanna.org/FOCS2026_CFP.html</t>
-        </is>
-      </c>
-      <c r="L19" t="inlineStr">
-        <is>
-          <t>2026-04-01</t>
-        </is>
-      </c>
-      <c r="N19" t="inlineStr">
-        <is>
-          <t>not_yet_announced</t>
-        </is>
-      </c>
-      <c r="P19" t="inlineStr">
-        <is>
-          <t>2026-07-22 19:07 UTC</t>
-        </is>
-      </c>
+          <t>TBD</t>
+        </is>
+      </c>
+      <c r="L19" t="inlineStr"/>
+      <c r="M19" t="inlineStr">
+        <is>
+          <t>not_yet_announced</t>
+        </is>
+      </c>
+      <c r="N19" t="inlineStr"/>
+      <c r="O19" t="inlineStr"/>
+      <c r="P19" t="inlineStr"/>
+      <c r="Q19" t="inlineStr"/>
       <c r="R19" t="inlineStr"/>
     </row>
     <row r="20">
@@ -1884,30 +1630,29 @@
       </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t>July 12-16, 2027</t>
+          <t>07.12-07.16</t>
+        </is>
+      </c>
+      <c r="J20" t="inlineStr">
+        <is>
+          <t>https://conf.researchr.org/home/fse-2027</t>
         </is>
       </c>
       <c r="K20" t="inlineStr">
         <is>
-          <t>https://conf.researchr.org/home/fse-2027</t>
-        </is>
-      </c>
-      <c r="L20" t="inlineStr">
-        <is>
           <t>2026-10-02</t>
         </is>
       </c>
-      <c r="N20" t="inlineStr">
-        <is>
-          <t>not_yet_announced</t>
-        </is>
-      </c>
-      <c r="P20" t="inlineStr">
-        <is>
-          <t>2026-07-22 19:07 UTC</t>
-        </is>
-      </c>
-      <c r="R20" t="inlineStr"/>
+      <c r="M20" t="inlineStr">
+        <is>
+          <t>not_yet_announced</t>
+        </is>
+      </c>
+      <c r="O20" t="inlineStr">
+        <is>
+          <t>2026-07-22 19:22 UTC</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
@@ -1950,30 +1695,29 @@
       </c>
       <c r="I21" t="inlineStr">
         <is>
-          <t>Jan 30-Feb 3, 2027</t>
+          <t>01.30-02.03</t>
+        </is>
+      </c>
+      <c r="J21" t="inlineStr">
+        <is>
+          <t>https://conf.researchr.org/home/hpca-2027</t>
         </is>
       </c>
       <c r="K21" t="inlineStr">
         <is>
-          <t>https://conf.researchr.org/home/hpca-2027</t>
-        </is>
-      </c>
-      <c r="L21" t="inlineStr">
-        <is>
           <t>2026-07-31</t>
         </is>
       </c>
-      <c r="N21" t="inlineStr">
-        <is>
-          <t>not_yet_announced</t>
-        </is>
-      </c>
-      <c r="P21" t="inlineStr">
-        <is>
-          <t>2026-07-22 19:07 UTC</t>
-        </is>
-      </c>
-      <c r="R21" t="inlineStr"/>
+      <c r="M21" t="inlineStr">
+        <is>
+          <t>not_yet_announced</t>
+        </is>
+      </c>
+      <c r="O21" t="inlineStr">
+        <is>
+          <t>2026-07-22 19:22 UTC</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
@@ -1992,76 +1736,45 @@
         </is>
       </c>
       <c r="D22" t="n">
-        <v>2026</v>
+        <v>2027</v>
       </c>
       <c r="E22" t="inlineStr">
         <is>
           <t>DS</t>
         </is>
       </c>
-      <c r="F22" t="inlineStr">
-        <is>
-          <t>Cleveland, OH</t>
-        </is>
-      </c>
-      <c r="G22" t="inlineStr">
-        <is>
-          <t>USA</t>
-        </is>
-      </c>
-      <c r="H22" t="inlineStr">
-        <is>
-          <t>North America</t>
-        </is>
-      </c>
+      <c r="F22" t="inlineStr"/>
+      <c r="G22" t="inlineStr"/>
+      <c r="H22" t="inlineStr"/>
       <c r="I22" t="inlineStr">
         <is>
-          <t>July 13-16, 2026</t>
-        </is>
-      </c>
+          <t>TBD</t>
+        </is>
+      </c>
+      <c r="J22" t="inlineStr"/>
       <c r="K22" t="inlineStr">
         <is>
-          <t>https://hpdc.sci.utah.edu/2026/</t>
-        </is>
-      </c>
-      <c r="L22" t="inlineStr">
-        <is>
-          <t>2026-01-29</t>
+          <t>TBD</t>
         </is>
       </c>
       <c r="M22" t="inlineStr">
         <is>
-          <t>December 5, 2025</t>
-        </is>
-      </c>
-      <c r="N22" t="inlineStr">
-        <is>
-          <t>confirmed</t>
+          <t>not_yet_announced</t>
         </is>
       </c>
       <c r="O22" t="inlineStr">
         <is>
-          <t>https://hpdc.sci.utah.edu/2026/</t>
+          <t>2026-07-22 19:22 UTC</t>
         </is>
       </c>
       <c r="P22" t="inlineStr">
         <is>
-          <t>2026-07-22 19:07 UTC</t>
-        </is>
-      </c>
-      <c r="Q22" t="inlineStr">
-        <is>
-          <t>2026-07-22 18:58 UTC</t>
+          <t>2026-07-22 19:22 UTC</t>
         </is>
       </c>
       <c r="R22" t="inlineStr">
         <is>
-          <t>https://hpdc.sci.utah.edu/2026/</t>
-        </is>
-      </c>
-      <c r="S22" t="inlineStr">
-        <is>
-          <t>extracted from official site</t>
+          <t>需要人工核实官网（未配置搜索API做兜底）</t>
         </is>
       </c>
     </row>
@@ -2082,76 +1795,45 @@
         </is>
       </c>
       <c r="D23" t="n">
-        <v>2025</v>
+        <v>2027</v>
       </c>
       <c r="E23" t="inlineStr">
         <is>
           <t>AI</t>
         </is>
       </c>
-      <c r="F23" t="inlineStr">
-        <is>
-          <t>Honolulu, Hawaii</t>
-        </is>
-      </c>
-      <c r="G23" t="inlineStr">
-        <is>
-          <t>USA</t>
-        </is>
-      </c>
-      <c r="H23" t="inlineStr">
-        <is>
-          <t>North America</t>
-        </is>
-      </c>
+      <c r="F23" t="inlineStr"/>
+      <c r="G23" t="inlineStr"/>
+      <c r="H23" t="inlineStr"/>
       <c r="I23" t="inlineStr">
         <is>
-          <t>October 19-25, 2025</t>
-        </is>
-      </c>
+          <t>TBD</t>
+        </is>
+      </c>
+      <c r="J23" t="inlineStr"/>
       <c r="K23" t="inlineStr">
         <is>
-          <t>https://iccv.thecvf.com/Conferences/2025</t>
-        </is>
-      </c>
-      <c r="L23" t="inlineStr">
-        <is>
-          <t>2025-03-08</t>
+          <t>TBD</t>
         </is>
       </c>
       <c r="M23" t="inlineStr">
         <is>
-          <t>Mar 13, 2025</t>
-        </is>
-      </c>
-      <c r="N23" t="inlineStr">
-        <is>
-          <t>confirmed</t>
+          <t>not_yet_announced</t>
         </is>
       </c>
       <c r="O23" t="inlineStr">
         <is>
-          <t>https://iccv.thecvf.com/Conferences/2025/CallForWorkshops</t>
+          <t>2026-07-22 19:22 UTC</t>
         </is>
       </c>
       <c r="P23" t="inlineStr">
         <is>
-          <t>2026-07-22 19:07 UTC</t>
-        </is>
-      </c>
-      <c r="Q23" t="inlineStr">
-        <is>
-          <t>2026-07-22 18:58 UTC</t>
+          <t>2026-07-22 19:22 UTC</t>
         </is>
       </c>
       <c r="R23" t="inlineStr">
         <is>
-          <t>https://iccv.thecvf.com/Conferences/2025/CallForWorkshops</t>
-        </is>
-      </c>
-      <c r="S23" t="inlineStr">
-        <is>
-          <t>extracted from official site</t>
+          <t>需要人工核实官网（未配置搜索API做兜底）</t>
         </is>
       </c>
     </row>
@@ -2196,30 +1878,29 @@
       </c>
       <c r="I24" t="inlineStr">
         <is>
-          <t>May 17-21, 2027</t>
+          <t>05.17-05.21</t>
+        </is>
+      </c>
+      <c r="J24" t="inlineStr">
+        <is>
+          <t>https://icde2027.github.io/</t>
         </is>
       </c>
       <c r="K24" t="inlineStr">
         <is>
-          <t>https://icde2027.github.io/</t>
-        </is>
-      </c>
-      <c r="L24" t="inlineStr">
-        <is>
           <t>2026-06-11</t>
         </is>
       </c>
-      <c r="N24" t="inlineStr">
-        <is>
-          <t>not_yet_announced</t>
-        </is>
-      </c>
-      <c r="P24" t="inlineStr">
-        <is>
-          <t>2026-07-22 19:07 UTC</t>
-        </is>
-      </c>
-      <c r="R24" t="inlineStr"/>
+      <c r="M24" t="inlineStr">
+        <is>
+          <t>not_yet_announced</t>
+        </is>
+      </c>
+      <c r="O24" t="inlineStr">
+        <is>
+          <t>2026-07-22 19:22 UTC</t>
+        </is>
+      </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
@@ -2238,71 +1919,45 @@
         </is>
       </c>
       <c r="D25" t="n">
-        <v>2026</v>
+        <v>2027</v>
       </c>
       <c r="E25" t="inlineStr">
         <is>
           <t>AI</t>
         </is>
       </c>
-      <c r="F25" t="inlineStr">
-        <is>
-          <t>Brazil</t>
-        </is>
-      </c>
-      <c r="H25" t="inlineStr">
-        <is>
-          <t>Other</t>
-        </is>
-      </c>
+      <c r="F25" t="inlineStr"/>
+      <c r="G25" t="inlineStr"/>
+      <c r="H25" t="inlineStr"/>
       <c r="I25" t="inlineStr">
         <is>
-          <t>May 01-05, 2026</t>
-        </is>
-      </c>
+          <t>TBD</t>
+        </is>
+      </c>
+      <c r="J25" t="inlineStr"/>
       <c r="K25" t="inlineStr">
         <is>
-          <t>https://iclr.cc/Conferences/2026</t>
-        </is>
-      </c>
-      <c r="L25" t="inlineStr">
-        <is>
-          <t>2025-09-24</t>
+          <t>TBD</t>
         </is>
       </c>
       <c r="M25" t="inlineStr">
         <is>
-          <t>10 October 2025</t>
-        </is>
-      </c>
-      <c r="N25" t="inlineStr">
-        <is>
-          <t>confirmed</t>
+          <t>not_yet_announced</t>
         </is>
       </c>
       <c r="O25" t="inlineStr">
         <is>
-          <t>https://iclr.cc/Conferences/2026/CallForWorkshops</t>
+          <t>2026-07-22 19:22 UTC</t>
         </is>
       </c>
       <c r="P25" t="inlineStr">
         <is>
-          <t>2026-07-22 19:07 UTC</t>
-        </is>
-      </c>
-      <c r="Q25" t="inlineStr">
-        <is>
-          <t>2026-07-22 18:58 UTC</t>
+          <t>2026-07-22 19:22 UTC</t>
         </is>
       </c>
       <c r="R25" t="inlineStr">
         <is>
-          <t>https://iclr.cc/Conferences/2026/CallForWorkshops</t>
-        </is>
-      </c>
-      <c r="S25" t="inlineStr">
-        <is>
-          <t>extracted from official site</t>
+          <t>需要人工核实官网（未配置搜索API做兜底）</t>
         </is>
       </c>
     </row>
@@ -2323,76 +1978,45 @@
         </is>
       </c>
       <c r="D26" t="n">
-        <v>2026</v>
+        <v>2027</v>
       </c>
       <c r="E26" t="inlineStr">
         <is>
           <t>AI</t>
         </is>
       </c>
-      <c r="F26" t="inlineStr">
-        <is>
-          <t>Seoul</t>
-        </is>
-      </c>
-      <c r="G26" t="inlineStr">
-        <is>
-          <t>Korea</t>
-        </is>
-      </c>
-      <c r="H26" t="inlineStr">
-        <is>
-          <t>Asia</t>
-        </is>
-      </c>
+      <c r="F26" t="inlineStr"/>
+      <c r="G26" t="inlineStr"/>
+      <c r="H26" t="inlineStr"/>
       <c r="I26" t="inlineStr">
         <is>
-          <t>July 6-12, 2026</t>
-        </is>
-      </c>
+          <t>TBD</t>
+        </is>
+      </c>
+      <c r="J26" t="inlineStr"/>
       <c r="K26" t="inlineStr">
         <is>
-          <t>https://icml.cc/Conferences/2026</t>
-        </is>
-      </c>
-      <c r="L26" t="inlineStr">
-        <is>
-          <t>2026-01-29</t>
+          <t>TBD</t>
         </is>
       </c>
       <c r="M26" t="inlineStr">
         <is>
-          <t>February 13, 2026</t>
-        </is>
-      </c>
-      <c r="N26" t="inlineStr">
-        <is>
-          <t>confirmed</t>
+          <t>not_yet_announced</t>
         </is>
       </c>
       <c r="O26" t="inlineStr">
         <is>
-          <t>https://icml.cc/Conferences/2026/CallForWorkshops</t>
+          <t>2026-07-22 19:22 UTC</t>
         </is>
       </c>
       <c r="P26" t="inlineStr">
         <is>
-          <t>2026-07-22 19:07 UTC</t>
-        </is>
-      </c>
-      <c r="Q26" t="inlineStr">
-        <is>
-          <t>2026-07-22 18:58 UTC</t>
+          <t>2026-07-22 19:22 UTC</t>
         </is>
       </c>
       <c r="R26" t="inlineStr">
         <is>
-          <t>https://icml.cc/Conferences/2026/CallForWorkshops</t>
-        </is>
-      </c>
-      <c r="S26" t="inlineStr">
-        <is>
-          <t>extracted from official site</t>
+          <t>需要人工核实官网（未配置搜索API做兜底）</t>
         </is>
       </c>
     </row>
@@ -2437,50 +2061,50 @@
       </c>
       <c r="I27" t="inlineStr">
         <is>
-          <t>April 25-May 01, 2027</t>
+          <t>04.25-05.01</t>
+        </is>
+      </c>
+      <c r="J27" t="inlineStr">
+        <is>
+          <t>https://conf.researchr.org/home/icse-2027</t>
         </is>
       </c>
       <c r="K27" t="inlineStr">
         <is>
-          <t>https://conf.researchr.org/home/icse-2027</t>
+          <t>2026-06-30</t>
         </is>
       </c>
       <c r="L27" t="inlineStr">
         <is>
-          <t>2026-06-30</t>
+          <t>2026-07-04</t>
         </is>
       </c>
       <c r="M27" t="inlineStr">
         <is>
-          <t>4 July 2026</t>
+          <t>confirmed</t>
         </is>
       </c>
       <c r="N27" t="inlineStr">
         <is>
-          <t>confirmed</t>
+          <t>https://conf.researchr.org/track/icse-2027/icse-2027-workshops</t>
         </is>
       </c>
       <c r="O27" t="inlineStr">
         <is>
+          <t>2026-07-22 19:22 UTC</t>
+        </is>
+      </c>
+      <c r="P27" t="inlineStr">
+        <is>
+          <t>2026-07-22 19:22 UTC</t>
+        </is>
+      </c>
+      <c r="Q27" t="inlineStr">
+        <is>
           <t>https://conf.researchr.org/track/icse-2027/icse-2027-workshops</t>
         </is>
       </c>
-      <c r="P27" t="inlineStr">
-        <is>
-          <t>2026-07-22 19:07 UTC</t>
-        </is>
-      </c>
-      <c r="Q27" t="inlineStr">
-        <is>
-          <t>2026-07-22 18:58 UTC</t>
-        </is>
-      </c>
       <c r="R27" t="inlineStr">
-        <is>
-          <t>https://conf.researchr.org/track/icse-2027/icse-2027-workshops</t>
-        </is>
-      </c>
-      <c r="S27" t="inlineStr">
         <is>
           <t>extracted from official site</t>
         </is>
@@ -2503,76 +2127,45 @@
         </is>
       </c>
       <c r="D28" t="n">
-        <v>2026</v>
+        <v>2027</v>
       </c>
       <c r="E28" t="inlineStr">
         <is>
           <t>CG</t>
         </is>
       </c>
-      <c r="F28" t="inlineStr">
-        <is>
-          <t>Boston, Massachusetts</t>
-        </is>
-      </c>
-      <c r="G28" t="inlineStr">
-        <is>
-          <t>USA</t>
-        </is>
-      </c>
-      <c r="H28" t="inlineStr">
-        <is>
-          <t>North America</t>
-        </is>
-      </c>
+      <c r="F28" t="inlineStr"/>
+      <c r="G28" t="inlineStr"/>
+      <c r="H28" t="inlineStr"/>
       <c r="I28" t="inlineStr">
         <is>
-          <t>November 9-13, 2026</t>
-        </is>
-      </c>
+          <t>TBD</t>
+        </is>
+      </c>
+      <c r="J28" t="inlineStr"/>
       <c r="K28" t="inlineStr">
         <is>
-          <t>https://ieeevis.org/year/2026/welcome</t>
-        </is>
-      </c>
-      <c r="L28" t="inlineStr">
-        <is>
-          <t>2026-03-31</t>
+          <t>TBD</t>
         </is>
       </c>
       <c r="M28" t="inlineStr">
         <is>
-          <t>July 30, 2026</t>
-        </is>
-      </c>
-      <c r="N28" t="inlineStr">
-        <is>
-          <t>confirmed</t>
+          <t>not_yet_announced</t>
         </is>
       </c>
       <c r="O28" t="inlineStr">
         <is>
-          <t>https://ieeevis.org/year/2026/info/call-participation/workshops</t>
+          <t>2026-07-22 19:22 UTC</t>
         </is>
       </c>
       <c r="P28" t="inlineStr">
         <is>
-          <t>2026-07-22 19:07 UTC</t>
-        </is>
-      </c>
-      <c r="Q28" t="inlineStr">
-        <is>
-          <t>2026-07-22 18:58 UTC</t>
+          <t>2026-07-22 19:22 UTC</t>
         </is>
       </c>
       <c r="R28" t="inlineStr">
         <is>
-          <t>https://ieeevis.org/year/2026/info/call-participation/workshops</t>
-        </is>
-      </c>
-      <c r="S28" t="inlineStr">
-        <is>
-          <t>extracted from official site</t>
+          <t>需要人工核实官网（未配置搜索API做兜底）</t>
         </is>
       </c>
     </row>
@@ -2617,30 +2210,29 @@
       </c>
       <c r="I29" t="inlineStr">
         <is>
-          <t>February 27 - March 3, 2027</t>
+          <t>02.27-03.03</t>
+        </is>
+      </c>
+      <c r="J29" t="inlineStr">
+        <is>
+          <t>https://ieeevr.org/2027/</t>
         </is>
       </c>
       <c r="K29" t="inlineStr">
         <is>
-          <t>https://ieeevr.org/2027/</t>
-        </is>
-      </c>
-      <c r="L29" t="inlineStr">
-        <is>
           <t>2026-08-31</t>
         </is>
       </c>
-      <c r="N29" t="inlineStr">
-        <is>
-          <t>not_yet_announced</t>
-        </is>
-      </c>
-      <c r="P29" t="inlineStr">
-        <is>
-          <t>2026-07-22 19:07 UTC</t>
-        </is>
-      </c>
-      <c r="R29" t="inlineStr"/>
+      <c r="M29" t="inlineStr">
+        <is>
+          <t>not_yet_announced</t>
+        </is>
+      </c>
+      <c r="O29" t="inlineStr">
+        <is>
+          <t>2026-07-22 19:22 UTC</t>
+        </is>
+      </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
@@ -2683,30 +2275,29 @@
       </c>
       <c r="I30" t="inlineStr">
         <is>
-          <t>May 24 - 27, 2027</t>
+          <t>05.24-05.27</t>
+        </is>
+      </c>
+      <c r="J30" t="inlineStr">
+        <is>
+          <t>https://infocom2027.ieee-infocom.org/</t>
         </is>
       </c>
       <c r="K30" t="inlineStr">
         <is>
-          <t>https://infocom2027.ieee-infocom.org/</t>
-        </is>
-      </c>
-      <c r="L30" t="inlineStr">
-        <is>
           <t>2026-07-31</t>
         </is>
       </c>
-      <c r="N30" t="inlineStr">
-        <is>
-          <t>not_yet_announced</t>
-        </is>
-      </c>
-      <c r="P30" t="inlineStr">
-        <is>
-          <t>2026-07-22 19:07 UTC</t>
-        </is>
-      </c>
-      <c r="R30" t="inlineStr"/>
+      <c r="M30" t="inlineStr">
+        <is>
+          <t>not_yet_announced</t>
+        </is>
+      </c>
+      <c r="O30" t="inlineStr">
+        <is>
+          <t>2026-07-22 19:22 UTC</t>
+        </is>
+      </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
@@ -2725,76 +2316,45 @@
         </is>
       </c>
       <c r="D31" t="n">
-        <v>2026</v>
+        <v>2027</v>
       </c>
       <c r="E31" t="inlineStr">
         <is>
           <t>DS</t>
         </is>
       </c>
-      <c r="F31" t="inlineStr">
-        <is>
-          <t>Raleigh</t>
-        </is>
-      </c>
-      <c r="G31" t="inlineStr">
-        <is>
-          <t>USA</t>
-        </is>
-      </c>
-      <c r="H31" t="inlineStr">
-        <is>
-          <t>North America</t>
-        </is>
-      </c>
+      <c r="F31" t="inlineStr"/>
+      <c r="G31" t="inlineStr"/>
+      <c r="H31" t="inlineStr"/>
       <c r="I31" t="inlineStr">
         <is>
-          <t>June 27-July 1, 2026</t>
-        </is>
-      </c>
+          <t>TBD</t>
+        </is>
+      </c>
+      <c r="J31" t="inlineStr"/>
       <c r="K31" t="inlineStr">
         <is>
-          <t>https://iscaconf.org/isca2026/</t>
-        </is>
-      </c>
-      <c r="L31" t="inlineStr">
-        <is>
-          <t>2025-11-10</t>
+          <t>TBD</t>
         </is>
       </c>
       <c r="M31" t="inlineStr">
         <is>
-          <t>Jan 9, 2026</t>
-        </is>
-      </c>
-      <c r="N31" t="inlineStr">
-        <is>
-          <t>confirmed</t>
+          <t>not_yet_announced</t>
         </is>
       </c>
       <c r="O31" t="inlineStr">
         <is>
-          <t>https://iscaconf.org/isca2026/</t>
+          <t>2026-07-22 19:22 UTC</t>
         </is>
       </c>
       <c r="P31" t="inlineStr">
         <is>
-          <t>2026-07-22 19:07 UTC</t>
-        </is>
-      </c>
-      <c r="Q31" t="inlineStr">
-        <is>
-          <t>2026-07-22 18:58 UTC</t>
+          <t>2026-07-22 19:22 UTC</t>
         </is>
       </c>
       <c r="R31" t="inlineStr">
         <is>
-          <t>https://iscaconf.org/isca2026/</t>
-        </is>
-      </c>
-      <c r="S31" t="inlineStr">
-        <is>
-          <t>extracted from official site</t>
+          <t>需要人工核实官网（未配置搜索API做兜底）</t>
         </is>
       </c>
     </row>
@@ -2815,76 +2375,45 @@
         </is>
       </c>
       <c r="D32" t="n">
-        <v>2026</v>
+        <v>2027</v>
       </c>
       <c r="E32" t="inlineStr">
         <is>
           <t>SE</t>
         </is>
       </c>
-      <c r="F32" t="inlineStr">
-        <is>
-          <t>Oakland, California</t>
-        </is>
-      </c>
-      <c r="G32" t="inlineStr">
-        <is>
-          <t>United States</t>
-        </is>
-      </c>
-      <c r="H32" t="inlineStr">
-        <is>
-          <t>North America</t>
-        </is>
-      </c>
+      <c r="F32" t="inlineStr"/>
+      <c r="G32" t="inlineStr"/>
+      <c r="H32" t="inlineStr"/>
       <c r="I32" t="inlineStr">
         <is>
-          <t>October 3-9, 2026</t>
-        </is>
-      </c>
+          <t>TBD</t>
+        </is>
+      </c>
+      <c r="J32" t="inlineStr"/>
       <c r="K32" t="inlineStr">
         <is>
-          <t>https://conf.researchr.org/home/issta-2026</t>
-        </is>
-      </c>
-      <c r="L32" t="inlineStr">
-        <is>
-          <t>2026-01-29</t>
+          <t>TBD</t>
         </is>
       </c>
       <c r="M32" t="inlineStr">
         <is>
-          <t>Sat 17 Jan 2026</t>
-        </is>
-      </c>
-      <c r="N32" t="inlineStr">
-        <is>
-          <t>confirmed</t>
+          <t>not_yet_announced</t>
         </is>
       </c>
       <c r="O32" t="inlineStr">
         <is>
-          <t>https://conf.researchr.org/track/issta-2026/splash-issta-2026-workshops</t>
+          <t>2026-07-22 19:22 UTC</t>
         </is>
       </c>
       <c r="P32" t="inlineStr">
         <is>
-          <t>2026-07-22 19:07 UTC</t>
-        </is>
-      </c>
-      <c r="Q32" t="inlineStr">
-        <is>
-          <t>2026-07-22 18:58 UTC</t>
+          <t>2026-07-22 19:22 UTC</t>
         </is>
       </c>
       <c r="R32" t="inlineStr">
         <is>
-          <t>https://conf.researchr.org/track/issta-2026/splash-issta-2026-workshops</t>
-        </is>
-      </c>
-      <c r="S32" t="inlineStr">
-        <is>
-          <t>extracted from official site</t>
+          <t>需要人工核实官网（未配置搜索API做兜底）</t>
         </is>
       </c>
     </row>
@@ -2905,54 +2434,37 @@
         </is>
       </c>
       <c r="D33" t="n">
-        <v>2026</v>
+        <v>2027</v>
       </c>
       <c r="E33" t="inlineStr">
         <is>
           <t>CT</t>
         </is>
       </c>
-      <c r="F33" t="inlineStr">
-        <is>
-          <t>Lisbon</t>
-        </is>
-      </c>
-      <c r="G33" t="inlineStr">
-        <is>
-          <t>Portugal</t>
-        </is>
-      </c>
-      <c r="H33" t="inlineStr">
-        <is>
-          <t>Europe</t>
-        </is>
-      </c>
+      <c r="F33" t="inlineStr"/>
+      <c r="G33" t="inlineStr"/>
+      <c r="H33" t="inlineStr"/>
       <c r="I33" t="inlineStr">
         <is>
-          <t>July 20-23, 2026</t>
-        </is>
-      </c>
+          <t>TBD</t>
+        </is>
+      </c>
+      <c r="J33" t="inlineStr"/>
       <c r="K33" t="inlineStr">
         <is>
-          <t>https://lics.siglog.org/lics26/</t>
-        </is>
-      </c>
-      <c r="L33" t="inlineStr">
-        <is>
-          <t>2026-01-22</t>
-        </is>
-      </c>
-      <c r="N33" t="inlineStr">
-        <is>
-          <t>not_yet_announced</t>
-        </is>
-      </c>
-      <c r="P33" t="inlineStr">
-        <is>
-          <t>2026-07-22 19:07 UTC</t>
-        </is>
-      </c>
-      <c r="R33" t="inlineStr"/>
+          <t>TBD</t>
+        </is>
+      </c>
+      <c r="M33" t="inlineStr">
+        <is>
+          <t>not_yet_announced</t>
+        </is>
+      </c>
+      <c r="O33" t="inlineStr">
+        <is>
+          <t>2026-07-22 19:22 UTC</t>
+        </is>
+      </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
@@ -2971,76 +2483,45 @@
         </is>
       </c>
       <c r="D34" t="n">
-        <v>2026</v>
+        <v>2027</v>
       </c>
       <c r="E34" t="inlineStr">
         <is>
           <t>DS</t>
         </is>
       </c>
-      <c r="F34" t="inlineStr">
-        <is>
-          <t>Athens</t>
-        </is>
-      </c>
-      <c r="G34" t="inlineStr">
-        <is>
-          <t>Greece</t>
-        </is>
-      </c>
-      <c r="H34" t="inlineStr">
-        <is>
-          <t>Europe</t>
-        </is>
-      </c>
+      <c r="F34" t="inlineStr"/>
+      <c r="G34" t="inlineStr"/>
+      <c r="H34" t="inlineStr"/>
       <c r="I34" t="inlineStr">
         <is>
-          <t>October 31-November 4, 2026</t>
-        </is>
-      </c>
+          <t>TBD</t>
+        </is>
+      </c>
+      <c r="J34" t="inlineStr"/>
       <c r="K34" t="inlineStr">
         <is>
-          <t>https://microarch.org/micro59/</t>
-        </is>
-      </c>
-      <c r="L34" t="inlineStr">
-        <is>
-          <t>2026-04-07</t>
+          <t>TBD</t>
         </is>
       </c>
       <c r="M34" t="inlineStr">
         <is>
-          <t>May 22, 2026</t>
-        </is>
-      </c>
-      <c r="N34" t="inlineStr">
-        <is>
-          <t>confirmed</t>
+          <t>not_yet_announced</t>
         </is>
       </c>
       <c r="O34" t="inlineStr">
         <is>
-          <t>https://microarch.org/micro59/</t>
+          <t>2026-07-22 19:22 UTC</t>
         </is>
       </c>
       <c r="P34" t="inlineStr">
         <is>
-          <t>2026-07-22 19:07 UTC</t>
-        </is>
-      </c>
-      <c r="Q34" t="inlineStr">
-        <is>
-          <t>2026-07-22 18:58 UTC</t>
+          <t>2026-07-22 19:22 UTC</t>
         </is>
       </c>
       <c r="R34" t="inlineStr">
         <is>
-          <t>https://microarch.org/micro59/</t>
-        </is>
-      </c>
-      <c r="S34" t="inlineStr">
-        <is>
-          <t>extracted from official site</t>
+          <t>需要人工核实官网（未配置搜索API做兜底）</t>
         </is>
       </c>
     </row>
@@ -3061,54 +2542,37 @@
         </is>
       </c>
       <c r="D35" t="n">
-        <v>2026</v>
+        <v>2027</v>
       </c>
       <c r="E35" t="inlineStr">
         <is>
           <t>NW</t>
         </is>
       </c>
-      <c r="F35" t="inlineStr">
-        <is>
-          <t>Austin, Texas</t>
-        </is>
-      </c>
-      <c r="G35" t="inlineStr">
-        <is>
-          <t>USA</t>
-        </is>
-      </c>
-      <c r="H35" t="inlineStr">
-        <is>
-          <t>North America</t>
-        </is>
-      </c>
+      <c r="F35" t="inlineStr"/>
+      <c r="G35" t="inlineStr"/>
+      <c r="H35" t="inlineStr"/>
       <c r="I35" t="inlineStr">
         <is>
-          <t>November, 2026</t>
-        </is>
-      </c>
+          <t>TBD</t>
+        </is>
+      </c>
+      <c r="J35" t="inlineStr"/>
       <c r="K35" t="inlineStr">
         <is>
-          <t>https://sigmobile.org/mobicom/2026/</t>
-        </is>
-      </c>
-      <c r="L35" t="inlineStr">
-        <is>
-          <t>2025-09-03</t>
-        </is>
-      </c>
-      <c r="N35" t="inlineStr">
-        <is>
-          <t>not_yet_announced</t>
-        </is>
-      </c>
-      <c r="P35" t="inlineStr">
-        <is>
-          <t>2026-07-22 19:07 UTC</t>
-        </is>
-      </c>
-      <c r="R35" t="inlineStr"/>
+          <t>TBD</t>
+        </is>
+      </c>
+      <c r="M35" t="inlineStr">
+        <is>
+          <t>not_yet_announced</t>
+        </is>
+      </c>
+      <c r="O35" t="inlineStr">
+        <is>
+          <t>2026-07-22 19:22 UTC</t>
+        </is>
+      </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
@@ -3151,30 +2615,29 @@
       </c>
       <c r="I36" t="inlineStr">
         <is>
-          <t>March 22 - March 26, 2027</t>
+          <t>03.22-03.26</t>
+        </is>
+      </c>
+      <c r="J36" t="inlineStr">
+        <is>
+          <t>https://www.ndss-symposium.org/ndss2027/</t>
         </is>
       </c>
       <c r="K36" t="inlineStr">
         <is>
-          <t>https://www.ndss-symposium.org/ndss2027/</t>
-        </is>
-      </c>
-      <c r="L36" t="inlineStr">
-        <is>
           <t>2026-05-06</t>
         </is>
       </c>
-      <c r="N36" t="inlineStr">
-        <is>
-          <t>not_yet_announced</t>
-        </is>
-      </c>
-      <c r="P36" t="inlineStr">
-        <is>
-          <t>2026-07-22 19:07 UTC</t>
-        </is>
-      </c>
-      <c r="R36" t="inlineStr"/>
+      <c r="M36" t="inlineStr">
+        <is>
+          <t>not_yet_announced</t>
+        </is>
+      </c>
+      <c r="O36" t="inlineStr">
+        <is>
+          <t>2026-07-22 19:22 UTC</t>
+        </is>
+      </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
@@ -3193,76 +2656,45 @@
         </is>
       </c>
       <c r="D37" t="n">
-        <v>2026</v>
+        <v>2027</v>
       </c>
       <c r="E37" t="inlineStr">
         <is>
           <t>AI</t>
         </is>
       </c>
-      <c r="F37" t="inlineStr">
-        <is>
-          <t>Sydney</t>
-        </is>
-      </c>
-      <c r="G37" t="inlineStr">
-        <is>
-          <t>Australia</t>
-        </is>
-      </c>
-      <c r="H37" t="inlineStr">
-        <is>
-          <t>Other</t>
-        </is>
-      </c>
+      <c r="F37" t="inlineStr"/>
+      <c r="G37" t="inlineStr"/>
+      <c r="H37" t="inlineStr"/>
       <c r="I37" t="inlineStr">
         <is>
-          <t>December 6, 2026</t>
-        </is>
-      </c>
+          <t>TBD</t>
+        </is>
+      </c>
+      <c r="J37" t="inlineStr"/>
       <c r="K37" t="inlineStr">
         <is>
-          <t>https://neurips.cc/Conferences/2026</t>
-        </is>
-      </c>
-      <c r="L37" t="inlineStr">
-        <is>
-          <t>2026-05-07</t>
+          <t>TBD</t>
         </is>
       </c>
       <c r="M37" t="inlineStr">
         <is>
-          <t>June 06, 2026</t>
-        </is>
-      </c>
-      <c r="N37" t="inlineStr">
-        <is>
-          <t>confirmed</t>
+          <t>not_yet_announced</t>
         </is>
       </c>
       <c r="O37" t="inlineStr">
         <is>
-          <t>https://neurips.cc/Conferences/2026/CallForWorkshops</t>
+          <t>2026-07-22 19:22 UTC</t>
         </is>
       </c>
       <c r="P37" t="inlineStr">
         <is>
-          <t>2026-07-22 19:07 UTC</t>
-        </is>
-      </c>
-      <c r="Q37" t="inlineStr">
-        <is>
-          <t>2026-07-22 18:58 UTC</t>
+          <t>2026-07-22 19:22 UTC</t>
         </is>
       </c>
       <c r="R37" t="inlineStr">
         <is>
-          <t>https://neurips.cc/Conferences/2026/CallForWorkshops</t>
-        </is>
-      </c>
-      <c r="S37" t="inlineStr">
-        <is>
-          <t>extracted from official site</t>
+          <t>需要人工核实官网（未配置搜索API做兜底）</t>
         </is>
       </c>
     </row>
@@ -3307,30 +2739,29 @@
       </c>
       <c r="I38" t="inlineStr">
         <is>
-          <t>May 11-13, 2027</t>
+          <t>05.11-05.13</t>
+        </is>
+      </c>
+      <c r="J38" t="inlineStr">
+        <is>
+          <t>https://www.usenix.org/conference/nsdi27</t>
         </is>
       </c>
       <c r="K38" t="inlineStr">
         <is>
-          <t>https://www.usenix.org/conference/nsdi27</t>
-        </is>
-      </c>
-      <c r="L38" t="inlineStr">
-        <is>
           <t>2026-04-23</t>
         </is>
       </c>
-      <c r="N38" t="inlineStr">
-        <is>
-          <t>not_yet_announced</t>
-        </is>
-      </c>
-      <c r="P38" t="inlineStr">
-        <is>
-          <t>2026-07-22 19:07 UTC</t>
-        </is>
-      </c>
-      <c r="R38" t="inlineStr"/>
+      <c r="M38" t="inlineStr">
+        <is>
+          <t>not_yet_announced</t>
+        </is>
+      </c>
+      <c r="O38" t="inlineStr">
+        <is>
+          <t>2026-07-22 19:22 UTC</t>
+        </is>
+      </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
@@ -3349,76 +2780,45 @@
         </is>
       </c>
       <c r="D39" t="n">
-        <v>2026</v>
+        <v>2027</v>
       </c>
       <c r="E39" t="inlineStr">
         <is>
           <t>SE</t>
         </is>
       </c>
-      <c r="F39" t="inlineStr">
-        <is>
-          <t>Oakland, California</t>
-        </is>
-      </c>
-      <c r="G39" t="inlineStr">
-        <is>
-          <t>United States</t>
-        </is>
-      </c>
-      <c r="H39" t="inlineStr">
-        <is>
-          <t>North America</t>
-        </is>
-      </c>
+      <c r="F39" t="inlineStr"/>
+      <c r="G39" t="inlineStr"/>
+      <c r="H39" t="inlineStr"/>
       <c r="I39" t="inlineStr">
         <is>
-          <t>October 3-9, 2026</t>
-        </is>
-      </c>
+          <t>TBD</t>
+        </is>
+      </c>
+      <c r="J39" t="inlineStr"/>
       <c r="K39" t="inlineStr">
         <is>
-          <t>https://conf.researchr.org/track/splash-2026/oopsla-2026</t>
-        </is>
-      </c>
-      <c r="L39" t="inlineStr">
-        <is>
-          <t>2025-10-10</t>
+          <t>TBD</t>
         </is>
       </c>
       <c r="M39" t="inlineStr">
         <is>
-          <t>Sat 17 Jan 2026</t>
-        </is>
-      </c>
-      <c r="N39" t="inlineStr">
-        <is>
-          <t>confirmed</t>
+          <t>not_yet_announced</t>
         </is>
       </c>
       <c r="O39" t="inlineStr">
         <is>
-          <t>https://2026.splashcon.org/track/splash-issta-2026-workshops</t>
+          <t>2026-07-22 19:22 UTC</t>
         </is>
       </c>
       <c r="P39" t="inlineStr">
         <is>
-          <t>2026-07-22 19:07 UTC</t>
-        </is>
-      </c>
-      <c r="Q39" t="inlineStr">
-        <is>
-          <t>2026-07-22 18:58 UTC</t>
+          <t>2026-07-22 19:22 UTC</t>
         </is>
       </c>
       <c r="R39" t="inlineStr">
         <is>
-          <t>https://2026.splashcon.org/track/splash-issta-2026-workshops</t>
-        </is>
-      </c>
-      <c r="S39" t="inlineStr">
-        <is>
-          <t>extracted from official site</t>
+          <t>需要人工核实官网（未配置搜索API做兜底）</t>
         </is>
       </c>
     </row>
@@ -3463,30 +2863,29 @@
       </c>
       <c r="I40" t="inlineStr">
         <is>
-          <t>July 7-9, 2027</t>
+          <t>07.07-07.09</t>
+        </is>
+      </c>
+      <c r="J40" t="inlineStr">
+        <is>
+          <t>https://www.usenix.org/conference/osdi27</t>
         </is>
       </c>
       <c r="K40" t="inlineStr">
         <is>
-          <t>https://www.usenix.org/conference/osdi27</t>
-        </is>
-      </c>
-      <c r="L40" t="inlineStr">
-        <is>
           <t>2026-12-08</t>
         </is>
       </c>
-      <c r="N40" t="inlineStr">
-        <is>
-          <t>not_yet_announced</t>
-        </is>
-      </c>
-      <c r="P40" t="inlineStr">
-        <is>
-          <t>2026-07-22 19:07 UTC</t>
-        </is>
-      </c>
-      <c r="R40" t="inlineStr"/>
+      <c r="M40" t="inlineStr">
+        <is>
+          <t>not_yet_announced</t>
+        </is>
+      </c>
+      <c r="O40" t="inlineStr">
+        <is>
+          <t>2026-07-22 19:22 UTC</t>
+        </is>
+      </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
@@ -3505,76 +2904,45 @@
         </is>
       </c>
       <c r="D41" t="n">
-        <v>2026</v>
+        <v>2027</v>
       </c>
       <c r="E41" t="inlineStr">
         <is>
           <t>SE</t>
         </is>
       </c>
-      <c r="F41" t="inlineStr">
-        <is>
-          <t>Boulder, Colorado</t>
-        </is>
-      </c>
-      <c r="G41" t="inlineStr">
-        <is>
-          <t>United States</t>
-        </is>
-      </c>
-      <c r="H41" t="inlineStr">
-        <is>
-          <t>North America</t>
-        </is>
-      </c>
+      <c r="F41" t="inlineStr"/>
+      <c r="G41" t="inlineStr"/>
+      <c r="H41" t="inlineStr"/>
       <c r="I41" t="inlineStr">
         <is>
-          <t>June 15-19, 2026</t>
-        </is>
-      </c>
+          <t>TBD</t>
+        </is>
+      </c>
+      <c r="J41" t="inlineStr"/>
       <c r="K41" t="inlineStr">
         <is>
-          <t>https://pldi26.sigplan.org/</t>
-        </is>
-      </c>
-      <c r="L41" t="inlineStr">
-        <is>
-          <t>2025-11-13</t>
+          <t>TBD</t>
         </is>
       </c>
       <c r="M41" t="inlineStr">
         <is>
-          <t>Mon 24 Nov 2025</t>
-        </is>
-      </c>
-      <c r="N41" t="inlineStr">
-        <is>
-          <t>confirmed</t>
+          <t>not_yet_announced</t>
         </is>
       </c>
       <c r="O41" t="inlineStr">
         <is>
-          <t>https://pldi26.sigplan.org/track/pldi-2026-PLDI-Workshops</t>
+          <t>2026-07-22 19:22 UTC</t>
         </is>
       </c>
       <c r="P41" t="inlineStr">
         <is>
-          <t>2026-07-22 19:07 UTC</t>
-        </is>
-      </c>
-      <c r="Q41" t="inlineStr">
-        <is>
-          <t>2026-07-22 18:58 UTC</t>
+          <t>2026-07-22 19:22 UTC</t>
         </is>
       </c>
       <c r="R41" t="inlineStr">
         <is>
-          <t>https://pldi26.sigplan.org/track/pldi-2026-PLDI-Workshops</t>
-        </is>
-      </c>
-      <c r="S41" t="inlineStr">
-        <is>
-          <t>extracted from official site</t>
+          <t>需要人工核实官网（未配置搜索API做兜底）</t>
         </is>
       </c>
     </row>
@@ -3607,6 +2975,7 @@
           <t>Mexico City</t>
         </is>
       </c>
+      <c r="G42" t="inlineStr"/>
       <c r="H42" t="inlineStr">
         <is>
           <t>Other</t>
@@ -3614,50 +2983,50 @@
       </c>
       <c r="I42" t="inlineStr">
         <is>
-          <t>January 10-16, 2027</t>
+          <t>01.10-01.16</t>
+        </is>
+      </c>
+      <c r="J42" t="inlineStr">
+        <is>
+          <t>https://popl27.sigplan.org/</t>
         </is>
       </c>
       <c r="K42" t="inlineStr">
         <is>
-          <t>https://popl27.sigplan.org/</t>
+          <t>2026-07-09</t>
         </is>
       </c>
       <c r="L42" t="inlineStr">
         <is>
-          <t>2026-07-09</t>
+          <t>2026-07-24</t>
         </is>
       </c>
       <c r="M42" t="inlineStr">
         <is>
-          <t>24 July 2026</t>
+          <t>confirmed</t>
         </is>
       </c>
       <c r="N42" t="inlineStr">
         <is>
-          <t>confirmed</t>
+          <t>https://popl27.sigplan.org/track/POPL-2027-workshops-and-co-located-events</t>
         </is>
       </c>
       <c r="O42" t="inlineStr">
         <is>
+          <t>2026-07-22 19:22 UTC</t>
+        </is>
+      </c>
+      <c r="P42" t="inlineStr">
+        <is>
+          <t>2026-07-22 19:22 UTC</t>
+        </is>
+      </c>
+      <c r="Q42" t="inlineStr">
+        <is>
           <t>https://popl27.sigplan.org/track/POPL-2027-workshops-and-co-located-events</t>
         </is>
       </c>
-      <c r="P42" t="inlineStr">
-        <is>
-          <t>2026-07-22 19:07 UTC</t>
-        </is>
-      </c>
-      <c r="Q42" t="inlineStr">
-        <is>
-          <t>2026-07-22 18:58 UTC</t>
-        </is>
-      </c>
       <c r="R42" t="inlineStr">
-        <is>
-          <t>https://popl27.sigplan.org/track/POPL-2027-workshops-and-co-located-events</t>
-        </is>
-      </c>
-      <c r="S42" t="inlineStr">
         <is>
           <t>extracted from official site</t>
         </is>
@@ -3704,30 +3073,29 @@
       </c>
       <c r="I43" t="inlineStr">
         <is>
-          <t>Mar 20-24, 2027</t>
+          <t>03.20-03.24</t>
+        </is>
+      </c>
+      <c r="J43" t="inlineStr">
+        <is>
+          <t>https://ppopp27.sigplan.org/</t>
         </is>
       </c>
       <c r="K43" t="inlineStr">
         <is>
-          <t>https://ppopp27.sigplan.org/</t>
-        </is>
-      </c>
-      <c r="L43" t="inlineStr">
-        <is>
           <t>2026-08-03</t>
         </is>
       </c>
-      <c r="N43" t="inlineStr">
-        <is>
-          <t>not_yet_announced</t>
-        </is>
-      </c>
-      <c r="P43" t="inlineStr">
-        <is>
-          <t>2026-07-22 19:07 UTC</t>
-        </is>
-      </c>
-      <c r="R43" t="inlineStr"/>
+      <c r="M43" t="inlineStr">
+        <is>
+          <t>not_yet_announced</t>
+        </is>
+      </c>
+      <c r="O43" t="inlineStr">
+        <is>
+          <t>2026-07-22 19:22 UTC</t>
+        </is>
+      </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
@@ -3746,54 +3114,37 @@
         </is>
       </c>
       <c r="D44" t="n">
-        <v>2026</v>
+        <v>2027</v>
       </c>
       <c r="E44" t="inlineStr">
         <is>
           <t>MX</t>
         </is>
       </c>
-      <c r="F44" t="inlineStr">
-        <is>
-          <t>Yokohama</t>
-        </is>
-      </c>
-      <c r="G44" t="inlineStr">
-        <is>
-          <t>Japan</t>
-        </is>
-      </c>
-      <c r="H44" t="inlineStr">
-        <is>
-          <t>Asia</t>
-        </is>
-      </c>
+      <c r="F44" t="inlineStr"/>
+      <c r="G44" t="inlineStr"/>
+      <c r="H44" t="inlineStr"/>
       <c r="I44" t="inlineStr">
         <is>
-          <t>December 9-11, 2026</t>
-        </is>
-      </c>
+          <t>TBD</t>
+        </is>
+      </c>
+      <c r="J44" t="inlineStr"/>
       <c r="K44" t="inlineStr">
         <is>
-          <t>http://2026.rtss.org/</t>
-        </is>
-      </c>
-      <c r="L44" t="inlineStr">
-        <is>
-          <t>2026-05-21</t>
-        </is>
-      </c>
-      <c r="N44" t="inlineStr">
-        <is>
-          <t>not_yet_announced</t>
-        </is>
-      </c>
-      <c r="P44" t="inlineStr">
-        <is>
-          <t>2026-07-22 19:07 UTC</t>
-        </is>
-      </c>
-      <c r="R44" t="inlineStr"/>
+          <t>TBD</t>
+        </is>
+      </c>
+      <c r="M44" t="inlineStr">
+        <is>
+          <t>not_yet_announced</t>
+        </is>
+      </c>
+      <c r="O44" t="inlineStr">
+        <is>
+          <t>2026-07-22 19:22 UTC</t>
+        </is>
+      </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
@@ -3812,54 +3163,37 @@
         </is>
       </c>
       <c r="D45" t="n">
-        <v>2026</v>
+        <v>2027</v>
       </c>
       <c r="E45" t="inlineStr">
         <is>
           <t>DS</t>
         </is>
       </c>
-      <c r="F45" t="inlineStr">
-        <is>
-          <t>McCormick Place, Chicago, Illinois</t>
-        </is>
-      </c>
-      <c r="G45" t="inlineStr">
-        <is>
-          <t>USA</t>
-        </is>
-      </c>
-      <c r="H45" t="inlineStr">
-        <is>
-          <t>North America</t>
-        </is>
-      </c>
+      <c r="F45" t="inlineStr"/>
+      <c r="G45" t="inlineStr"/>
+      <c r="H45" t="inlineStr"/>
       <c r="I45" t="inlineStr">
         <is>
-          <t>November 15-20, 2026</t>
-        </is>
-      </c>
+          <t>TBD</t>
+        </is>
+      </c>
+      <c r="J45" t="inlineStr"/>
       <c r="K45" t="inlineStr">
         <is>
-          <t>https://sc26.supercomputing.org/</t>
-        </is>
-      </c>
-      <c r="L45" t="inlineStr">
-        <is>
-          <t>2026-04-08</t>
-        </is>
-      </c>
-      <c r="N45" t="inlineStr">
-        <is>
-          <t>not_yet_announced</t>
-        </is>
-      </c>
-      <c r="P45" t="inlineStr">
-        <is>
-          <t>2026-07-22 19:07 UTC</t>
-        </is>
-      </c>
-      <c r="R45" t="inlineStr"/>
+          <t>TBD</t>
+        </is>
+      </c>
+      <c r="M45" t="inlineStr">
+        <is>
+          <t>not_yet_announced</t>
+        </is>
+      </c>
+      <c r="O45" t="inlineStr">
+        <is>
+          <t>2026-07-22 19:22 UTC</t>
+        </is>
+      </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
@@ -3878,76 +3212,45 @@
         </is>
       </c>
       <c r="D46" t="n">
-        <v>2026</v>
+        <v>2027</v>
       </c>
       <c r="E46" t="inlineStr">
         <is>
           <t>NW</t>
         </is>
       </c>
-      <c r="F46" t="inlineStr">
-        <is>
-          <t>Denver, Colorado</t>
-        </is>
-      </c>
-      <c r="G46" t="inlineStr">
-        <is>
-          <t>USA</t>
-        </is>
-      </c>
-      <c r="H46" t="inlineStr">
-        <is>
-          <t>North America</t>
-        </is>
-      </c>
+      <c r="F46" t="inlineStr"/>
+      <c r="G46" t="inlineStr"/>
+      <c r="H46" t="inlineStr"/>
       <c r="I46" t="inlineStr">
         <is>
-          <t>August 17 - 21, 2026</t>
-        </is>
-      </c>
+          <t>TBD</t>
+        </is>
+      </c>
+      <c r="J46" t="inlineStr"/>
       <c r="K46" t="inlineStr">
         <is>
-          <t>https://conferences.sigcomm.org/sigcomm/2026/</t>
-        </is>
-      </c>
-      <c r="L46" t="inlineStr">
-        <is>
-          <t>2026-02-06</t>
+          <t>TBD</t>
         </is>
       </c>
       <c r="M46" t="inlineStr">
         <is>
-          <t>January 21, 2026</t>
-        </is>
-      </c>
-      <c r="N46" t="inlineStr">
-        <is>
-          <t>confirmed</t>
+          <t>not_yet_announced</t>
         </is>
       </c>
       <c r="O46" t="inlineStr">
         <is>
-          <t>https://conferences.sigcomm.org/sigcomm/2026/</t>
+          <t>2026-07-22 19:22 UTC</t>
         </is>
       </c>
       <c r="P46" t="inlineStr">
         <is>
-          <t>2026-07-22 19:07 UTC</t>
-        </is>
-      </c>
-      <c r="Q46" t="inlineStr">
-        <is>
-          <t>2026-07-22 18:58 UTC</t>
+          <t>2026-07-22 19:22 UTC</t>
         </is>
       </c>
       <c r="R46" t="inlineStr">
         <is>
-          <t>https://conferences.sigcomm.org/sigcomm/2026/</t>
-        </is>
-      </c>
-      <c r="S46" t="inlineStr">
-        <is>
-          <t>extracted from official site</t>
+          <t>需要人工核实官网（未配置搜索API做兜底）</t>
         </is>
       </c>
     </row>
@@ -3968,54 +3271,37 @@
         </is>
       </c>
       <c r="D47" t="n">
-        <v>2026</v>
+        <v>2027</v>
       </c>
       <c r="E47" t="inlineStr">
         <is>
           <t>DB</t>
         </is>
       </c>
-      <c r="F47" t="inlineStr">
-        <is>
-          <t>Melbourne</t>
-        </is>
-      </c>
-      <c r="G47" t="inlineStr">
-        <is>
-          <t>Australia</t>
-        </is>
-      </c>
-      <c r="H47" t="inlineStr">
-        <is>
-          <t>Other</t>
-        </is>
-      </c>
+      <c r="F47" t="inlineStr"/>
+      <c r="G47" t="inlineStr"/>
+      <c r="H47" t="inlineStr"/>
       <c r="I47" t="inlineStr">
         <is>
-          <t>July 20-24, 2026</t>
-        </is>
-      </c>
+          <t>TBD</t>
+        </is>
+      </c>
+      <c r="J47" t="inlineStr"/>
       <c r="K47" t="inlineStr">
         <is>
-          <t>https://sigir2026.org/en-AU</t>
-        </is>
-      </c>
-      <c r="L47" t="inlineStr">
-        <is>
-          <t>2026-01-22</t>
-        </is>
-      </c>
-      <c r="N47" t="inlineStr">
-        <is>
-          <t>not_yet_announced</t>
-        </is>
-      </c>
-      <c r="P47" t="inlineStr">
-        <is>
-          <t>2026-07-22 19:07 UTC</t>
-        </is>
-      </c>
-      <c r="R47" t="inlineStr"/>
+          <t>TBD</t>
+        </is>
+      </c>
+      <c r="M47" t="inlineStr">
+        <is>
+          <t>not_yet_announced</t>
+        </is>
+      </c>
+      <c r="O47" t="inlineStr">
+        <is>
+          <t>2026-07-22 19:22 UTC</t>
+        </is>
+      </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
@@ -4061,27 +3347,26 @@
           <t>August 2027 (exact dates TBD)</t>
         </is>
       </c>
+      <c r="J48" t="inlineStr">
+        <is>
+          <t>https://kdd2027.kdd.org/</t>
+        </is>
+      </c>
       <c r="K48" t="inlineStr">
         <is>
-          <t>https://kdd2027.kdd.org/</t>
-        </is>
-      </c>
-      <c r="L48" t="inlineStr">
-        <is>
           <t>2026-07-26</t>
         </is>
       </c>
-      <c r="N48" t="inlineStr">
-        <is>
-          <t>not_yet_announced</t>
-        </is>
-      </c>
-      <c r="P48" t="inlineStr">
-        <is>
-          <t>2026-07-22 19:07 UTC</t>
-        </is>
-      </c>
-      <c r="R48" t="inlineStr"/>
+      <c r="M48" t="inlineStr">
+        <is>
+          <t>not_yet_announced</t>
+        </is>
+      </c>
+      <c r="O48" t="inlineStr">
+        <is>
+          <t>2026-07-22 19:22 UTC</t>
+        </is>
+      </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
@@ -4124,30 +3409,29 @@
       </c>
       <c r="I49" t="inlineStr">
         <is>
-          <t>June 13-19, 2027</t>
+          <t>06.13-06.19</t>
+        </is>
+      </c>
+      <c r="J49" t="inlineStr">
+        <is>
+          <t>https://2027.sigmod.org/</t>
         </is>
       </c>
       <c r="K49" t="inlineStr">
         <is>
-          <t>https://2027.sigmod.org/</t>
-        </is>
-      </c>
-      <c r="L49" t="inlineStr">
-        <is>
           <t>2026-01-17</t>
         </is>
       </c>
-      <c r="N49" t="inlineStr">
-        <is>
-          <t>not_yet_announced</t>
-        </is>
-      </c>
-      <c r="P49" t="inlineStr">
-        <is>
-          <t>2026-07-22 19:07 UTC</t>
-        </is>
-      </c>
-      <c r="R49" t="inlineStr"/>
+      <c r="M49" t="inlineStr">
+        <is>
+          <t>not_yet_announced</t>
+        </is>
+      </c>
+      <c r="O49" t="inlineStr">
+        <is>
+          <t>2026-07-22 19:22 UTC</t>
+        </is>
+      </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
@@ -4166,76 +3450,45 @@
         </is>
       </c>
       <c r="D50" t="n">
-        <v>2026</v>
+        <v>2027</v>
       </c>
       <c r="E50" t="inlineStr">
         <is>
           <t>DS</t>
         </is>
       </c>
-      <c r="F50" t="inlineStr">
-        <is>
-          <t>Hyatt Hotel, Shatin, Hong Kong</t>
-        </is>
-      </c>
-      <c r="G50" t="inlineStr">
-        <is>
-          <t>China</t>
-        </is>
-      </c>
-      <c r="H50" t="inlineStr">
-        <is>
-          <t>Asia</t>
-        </is>
-      </c>
+      <c r="F50" t="inlineStr"/>
+      <c r="G50" t="inlineStr"/>
+      <c r="H50" t="inlineStr"/>
       <c r="I50" t="inlineStr">
         <is>
-          <t>November 15-18, 2026</t>
-        </is>
-      </c>
+          <t>TBD</t>
+        </is>
+      </c>
+      <c r="J50" t="inlineStr"/>
       <c r="K50" t="inlineStr">
         <is>
-          <t>https://sigops.org/s/conferences/atc/2026/index.html</t>
-        </is>
-      </c>
-      <c r="L50" t="inlineStr">
-        <is>
-          <t>2026-06-11</t>
+          <t>TBD</t>
         </is>
       </c>
       <c r="M50" t="inlineStr">
         <is>
-          <t>April 29, 2025</t>
-        </is>
-      </c>
-      <c r="N50" t="inlineStr">
-        <is>
-          <t>confirmed</t>
+          <t>not_yet_announced</t>
         </is>
       </c>
       <c r="O50" t="inlineStr">
         <is>
-          <t>https://sigops.org/s/conferences/atc/2026/index.html</t>
+          <t>2026-07-22 19:22 UTC</t>
         </is>
       </c>
       <c r="P50" t="inlineStr">
         <is>
-          <t>2026-07-22 19:07 UTC</t>
-        </is>
-      </c>
-      <c r="Q50" t="inlineStr">
-        <is>
-          <t>2026-07-22 19:04 UTC</t>
+          <t>2026-07-22 19:22 UTC</t>
         </is>
       </c>
       <c r="R50" t="inlineStr">
         <is>
-          <t>https://sigops.org/s/conferences/atc/2026/index.html</t>
-        </is>
-      </c>
-      <c r="S50" t="inlineStr">
-        <is>
-          <t>extracted from official site</t>
+          <t>需要人工核实官网（未配置搜索API做兜底）</t>
         </is>
       </c>
     </row>
@@ -4280,30 +3533,29 @@
       </c>
       <c r="I51" t="inlineStr">
         <is>
-          <t>January 24-27, 2027</t>
+          <t>01.24-01.27</t>
+        </is>
+      </c>
+      <c r="J51" t="inlineStr">
+        <is>
+          <t>https://www.siam.org/conferences-events/siam-conferences/soda27/</t>
         </is>
       </c>
       <c r="K51" t="inlineStr">
         <is>
-          <t>https://www.siam.org/conferences-events/siam-conferences/soda27/</t>
-        </is>
-      </c>
-      <c r="L51" t="inlineStr">
-        <is>
           <t>2026-07-09</t>
         </is>
       </c>
-      <c r="N51" t="inlineStr">
-        <is>
-          <t>not_yet_announced</t>
-        </is>
-      </c>
-      <c r="P51" t="inlineStr">
-        <is>
-          <t>2026-07-22 19:07 UTC</t>
-        </is>
-      </c>
-      <c r="R51" t="inlineStr"/>
+      <c r="M51" t="inlineStr">
+        <is>
+          <t>not_yet_announced</t>
+        </is>
+      </c>
+      <c r="O51" t="inlineStr">
+        <is>
+          <t>2026-07-22 19:22 UTC</t>
+        </is>
+      </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
@@ -4322,54 +3574,37 @@
         </is>
       </c>
       <c r="D52" t="n">
-        <v>2026</v>
+        <v>2027</v>
       </c>
       <c r="E52" t="inlineStr">
         <is>
           <t>SE</t>
         </is>
       </c>
-      <c r="F52" t="inlineStr">
-        <is>
-          <t>Clarion Congress Hotel Prague, Prague</t>
-        </is>
-      </c>
-      <c r="G52" t="inlineStr">
-        <is>
-          <t>Czechia</t>
-        </is>
-      </c>
-      <c r="H52" t="inlineStr">
-        <is>
-          <t>Europe</t>
-        </is>
-      </c>
+      <c r="F52" t="inlineStr"/>
+      <c r="G52" t="inlineStr"/>
+      <c r="H52" t="inlineStr"/>
       <c r="I52" t="inlineStr">
         <is>
-          <t>September 29 - October 2, 2026</t>
-        </is>
-      </c>
+          <t>TBD</t>
+        </is>
+      </c>
+      <c r="J52" t="inlineStr"/>
       <c r="K52" t="inlineStr">
         <is>
-          <t>https://sigops.org/s/conferences/sosp/2026/index.html</t>
-        </is>
-      </c>
-      <c r="L52" t="inlineStr">
-        <is>
-          <t>2026-04-01</t>
-        </is>
-      </c>
-      <c r="N52" t="inlineStr">
-        <is>
-          <t>not_yet_announced</t>
-        </is>
-      </c>
-      <c r="P52" t="inlineStr">
-        <is>
-          <t>2026-07-22 19:07 UTC</t>
-        </is>
-      </c>
-      <c r="R52" t="inlineStr"/>
+          <t>TBD</t>
+        </is>
+      </c>
+      <c r="M52" t="inlineStr">
+        <is>
+          <t>not_yet_announced</t>
+        </is>
+      </c>
+      <c r="O52" t="inlineStr">
+        <is>
+          <t>2026-07-22 19:22 UTC</t>
+        </is>
+      </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
@@ -4415,27 +3650,26 @@
           <t>TBD</t>
         </is>
       </c>
+      <c r="J53" t="inlineStr">
+        <is>
+          <t>https://sp2027.ieee-security.org/index.html</t>
+        </is>
+      </c>
       <c r="K53" t="inlineStr">
         <is>
-          <t>https://sp2027.ieee-security.org/index.html</t>
-        </is>
-      </c>
-      <c r="L53" t="inlineStr">
-        <is>
           <t>2026-06-11</t>
         </is>
       </c>
-      <c r="N53" t="inlineStr">
-        <is>
-          <t>not_yet_announced</t>
-        </is>
-      </c>
-      <c r="P53" t="inlineStr">
-        <is>
-          <t>2026-07-22 19:07 UTC</t>
-        </is>
-      </c>
-      <c r="R53" t="inlineStr"/>
+      <c r="M53" t="inlineStr">
+        <is>
+          <t>not_yet_announced</t>
+        </is>
+      </c>
+      <c r="O53" t="inlineStr">
+        <is>
+          <t>2026-07-22 19:22 UTC</t>
+        </is>
+      </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
@@ -4454,53 +3688,37 @@
         </is>
       </c>
       <c r="D54" t="n">
-        <v>2026</v>
+        <v>2027</v>
       </c>
       <c r="E54" t="inlineStr">
         <is>
           <t>CT</t>
         </is>
       </c>
-      <c r="F54" t="inlineStr">
-        <is>
-          <t>Salt Lake City, Utah</t>
-        </is>
-      </c>
-      <c r="G54" t="inlineStr">
-        <is>
-          <t>USA</t>
-        </is>
-      </c>
-      <c r="H54" t="inlineStr">
-        <is>
-          <t>North America</t>
-        </is>
-      </c>
+      <c r="F54" t="inlineStr"/>
+      <c r="G54" t="inlineStr"/>
+      <c r="H54" t="inlineStr"/>
       <c r="I54" t="inlineStr">
         <is>
-          <t>June 22-26, 2026</t>
-        </is>
-      </c>
+          <t>TBD</t>
+        </is>
+      </c>
+      <c r="J54" t="inlineStr"/>
       <c r="K54" t="inlineStr">
         <is>
-          <t>https://acm-stoc.org/stoc2026/</t>
-        </is>
-      </c>
-      <c r="L54" t="inlineStr">
-        <is>
-          <t>2025-11-04</t>
-        </is>
-      </c>
-      <c r="N54" t="inlineStr">
-        <is>
-          <t>not_yet_announced</t>
-        </is>
-      </c>
-      <c r="P54" t="inlineStr">
-        <is>
-          <t>2026-07-22 19:07 UTC</t>
-        </is>
-      </c>
+          <t>TBD</t>
+        </is>
+      </c>
+      <c r="L54" t="inlineStr"/>
+      <c r="M54" t="inlineStr">
+        <is>
+          <t>not_yet_announced</t>
+        </is>
+      </c>
+      <c r="N54" t="inlineStr"/>
+      <c r="O54" t="inlineStr"/>
+      <c r="P54" t="inlineStr"/>
+      <c r="Q54" t="inlineStr"/>
       <c r="R54" t="inlineStr"/>
     </row>
     <row r="55">
@@ -4520,76 +3738,45 @@
         </is>
       </c>
       <c r="D55" t="n">
-        <v>2026</v>
+        <v>2027</v>
       </c>
       <c r="E55" t="inlineStr">
         <is>
           <t>HI</t>
         </is>
       </c>
-      <c r="F55" t="inlineStr">
-        <is>
-          <t>Shanghai</t>
-        </is>
-      </c>
-      <c r="G55" t="inlineStr">
-        <is>
-          <t>China</t>
-        </is>
-      </c>
-      <c r="H55" t="inlineStr">
-        <is>
-          <t>Asia</t>
-        </is>
-      </c>
+      <c r="F55" t="inlineStr"/>
+      <c r="G55" t="inlineStr"/>
+      <c r="H55" t="inlineStr"/>
       <c r="I55" t="inlineStr">
         <is>
-          <t>October 11-15, 2026</t>
-        </is>
-      </c>
+          <t>TBD</t>
+        </is>
+      </c>
+      <c r="J55" t="inlineStr"/>
       <c r="K55" t="inlineStr">
         <is>
-          <t>https://www.ubicomp.org/ubicomp-iswc-2026</t>
-        </is>
-      </c>
-      <c r="L55" t="inlineStr">
-        <is>
-          <t>2026-02-01</t>
+          <t>TBD</t>
         </is>
       </c>
       <c r="M55" t="inlineStr">
         <is>
-          <t>2026-03-07</t>
-        </is>
-      </c>
-      <c r="N55" t="inlineStr">
-        <is>
-          <t>confirmed</t>
+          <t>not_yet_announced</t>
         </is>
       </c>
       <c r="O55" t="inlineStr">
         <is>
-          <t>https://www.ubicomp.org/ubicomp-iswc-2026/workshop-cfp/</t>
+          <t>2026-07-22 19:22 UTC</t>
         </is>
       </c>
       <c r="P55" t="inlineStr">
         <is>
-          <t>2026-07-22 19:07 UTC</t>
-        </is>
-      </c>
-      <c r="Q55" t="inlineStr">
-        <is>
-          <t>2026-07-22 18:58 UTC</t>
+          <t>2026-07-22 19:22 UTC</t>
         </is>
       </c>
       <c r="R55" t="inlineStr">
         <is>
-          <t>https://www.ubicomp.org/ubicomp-iswc-2026/workshop-cfp/</t>
-        </is>
-      </c>
-      <c r="S55" t="inlineStr">
-        <is>
-          <t>extracted from official site</t>
+          <t>需要人工核实官网（未配置搜索API做兜底）</t>
         </is>
       </c>
     </row>
@@ -4610,76 +3797,45 @@
         </is>
       </c>
       <c r="D56" t="n">
-        <v>2026</v>
+        <v>2027</v>
       </c>
       <c r="E56" t="inlineStr">
         <is>
           <t>HI</t>
         </is>
       </c>
-      <c r="F56" t="inlineStr">
-        <is>
-          <t>GM Renaissance Center, Detroit, MI</t>
-        </is>
-      </c>
-      <c r="G56" t="inlineStr">
-        <is>
-          <t>USA</t>
-        </is>
-      </c>
-      <c r="H56" t="inlineStr">
-        <is>
-          <t>North America</t>
-        </is>
-      </c>
+      <c r="F56" t="inlineStr"/>
+      <c r="G56" t="inlineStr"/>
+      <c r="H56" t="inlineStr"/>
       <c r="I56" t="inlineStr">
         <is>
-          <t>November 2 - 5, 2026</t>
-        </is>
-      </c>
+          <t>TBD</t>
+        </is>
+      </c>
+      <c r="J56" t="inlineStr"/>
       <c r="K56" t="inlineStr">
         <is>
-          <t>https://uist.acm.org/2026/</t>
-        </is>
-      </c>
-      <c r="L56" t="inlineStr">
-        <is>
-          <t>2026-03-31</t>
+          <t>TBD</t>
         </is>
       </c>
       <c r="M56" t="inlineStr">
         <is>
-          <t>Jul 10, 2026</t>
-        </is>
-      </c>
-      <c r="N56" t="inlineStr">
-        <is>
-          <t>confirmed</t>
+          <t>not_yet_announced</t>
         </is>
       </c>
       <c r="O56" t="inlineStr">
         <is>
-          <t>https://uist.acm.org/2026/</t>
+          <t>2026-07-22 19:22 UTC</t>
         </is>
       </c>
       <c r="P56" t="inlineStr">
         <is>
-          <t>2026-07-22 19:07 UTC</t>
-        </is>
-      </c>
-      <c r="Q56" t="inlineStr">
-        <is>
-          <t>2026-07-22 18:58 UTC</t>
+          <t>2026-07-22 19:22 UTC</t>
         </is>
       </c>
       <c r="R56" t="inlineStr">
         <is>
-          <t>https://uist.acm.org/2026/</t>
-        </is>
-      </c>
-      <c r="S56" t="inlineStr">
-        <is>
-          <t>extracted from official site</t>
+          <t>需要人工核实官网（未配置搜索API做兜底）</t>
         </is>
       </c>
     </row>
@@ -4724,30 +3880,29 @@
       </c>
       <c r="I57" t="inlineStr">
         <is>
-          <t>August 11-13, 2027</t>
+          <t>08.11-08.13</t>
+        </is>
+      </c>
+      <c r="J57" t="inlineStr">
+        <is>
+          <t>https://www.usenix.org/conference/usenixsecurity27</t>
         </is>
       </c>
       <c r="K57" t="inlineStr">
         <is>
-          <t>https://www.usenix.org/conference/usenixsecurity27</t>
-        </is>
-      </c>
-      <c r="L57" t="inlineStr">
-        <is>
           <t>2026-08-25</t>
         </is>
       </c>
-      <c r="N57" t="inlineStr">
-        <is>
-          <t>not_yet_announced</t>
-        </is>
-      </c>
-      <c r="P57" t="inlineStr">
-        <is>
-          <t>2026-07-22 19:07 UTC</t>
-        </is>
-      </c>
-      <c r="R57" t="inlineStr"/>
+      <c r="M57" t="inlineStr">
+        <is>
+          <t>not_yet_announced</t>
+        </is>
+      </c>
+      <c r="O57" t="inlineStr">
+        <is>
+          <t>2026-07-22 19:22 UTC</t>
+        </is>
+      </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
@@ -4790,30 +3945,29 @@
       </c>
       <c r="I58" t="inlineStr">
         <is>
-          <t>August 23 - August 27, 2027</t>
+          <t>08.23-08.27</t>
+        </is>
+      </c>
+      <c r="J58" t="inlineStr">
+        <is>
+          <t>https://www.vldb.org/2027/</t>
         </is>
       </c>
       <c r="K58" t="inlineStr">
         <is>
-          <t>https://www.vldb.org/2027/</t>
-        </is>
-      </c>
-      <c r="L58" t="inlineStr">
-        <is>
           <t>2026-04-01</t>
         </is>
       </c>
-      <c r="N58" t="inlineStr">
-        <is>
-          <t>not_yet_announced</t>
-        </is>
-      </c>
-      <c r="P58" t="inlineStr">
-        <is>
-          <t>2026-07-22 19:07 UTC</t>
-        </is>
-      </c>
-      <c r="R58" t="inlineStr"/>
+      <c r="M58" t="inlineStr">
+        <is>
+          <t>not_yet_announced</t>
+        </is>
+      </c>
+      <c r="O58" t="inlineStr">
+        <is>
+          <t>2026-07-22 19:22 UTC</t>
+        </is>
+      </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
@@ -4856,30 +4010,29 @@
       </c>
       <c r="I59" t="inlineStr">
         <is>
-          <t>May 10 - 14, 2027</t>
+          <t>05.10-05.14</t>
+        </is>
+      </c>
+      <c r="J59" t="inlineStr">
+        <is>
+          <t>https://acmweb2027.org/</t>
         </is>
       </c>
       <c r="K59" t="inlineStr">
         <is>
-          <t>https://acmweb2027.org/</t>
-        </is>
-      </c>
-      <c r="L59" t="inlineStr">
-        <is>
           <t>2026-10-18</t>
         </is>
       </c>
-      <c r="N59" t="inlineStr">
-        <is>
-          <t>not_yet_announced</t>
-        </is>
-      </c>
-      <c r="P59" t="inlineStr">
-        <is>
-          <t>2026-07-22 19:07 UTC</t>
-        </is>
-      </c>
-      <c r="R59" t="inlineStr"/>
+      <c r="M59" t="inlineStr">
+        <is>
+          <t>not_yet_announced</t>
+        </is>
+      </c>
+      <c r="O59" t="inlineStr">
+        <is>
+          <t>2026-07-22 19:22 UTC</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -4892,7 +4045,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E46"/>
+  <dimension ref="A1:E87"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -6027,6 +5180,1018 @@
         </is>
       </c>
     </row>
+    <row r="47">
+      <c r="A47" t="inlineStr">
+        <is>
+          <t>chi</t>
+        </is>
+      </c>
+      <c r="B47" t="inlineStr">
+        <is>
+          <t>workshop_proposal_deadline</t>
+        </is>
+      </c>
+      <c r="C47" t="inlineStr">
+        <is>
+          <t>September 28, 2026</t>
+        </is>
+      </c>
+      <c r="D47" t="inlineStr">
+        <is>
+          <t>2026-09-28</t>
+        </is>
+      </c>
+      <c r="E47" t="inlineStr">
+        <is>
+          <t>2026-07-22 19:22 UTC</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" t="inlineStr">
+        <is>
+          <t>cscw</t>
+        </is>
+      </c>
+      <c r="B48" t="inlineStr">
+        <is>
+          <t>workshop_proposal_deadline</t>
+        </is>
+      </c>
+      <c r="C48" t="inlineStr">
+        <is>
+          <t>April 10, 2026</t>
+        </is>
+      </c>
+      <c r="E48" t="inlineStr">
+        <is>
+          <t>2026-07-22 19:22 UTC</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" t="inlineStr">
+        <is>
+          <t>cscw</t>
+        </is>
+      </c>
+      <c r="B49" t="inlineStr">
+        <is>
+          <t>workshop_proposal_status</t>
+        </is>
+      </c>
+      <c r="C49" t="inlineStr">
+        <is>
+          <t>confirmed</t>
+        </is>
+      </c>
+      <c r="D49" t="inlineStr">
+        <is>
+          <t>not_yet_announced</t>
+        </is>
+      </c>
+      <c r="E49" t="inlineStr">
+        <is>
+          <t>2026-07-22 19:22 UTC</t>
+        </is>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" t="inlineStr">
+        <is>
+          <t>cvpr</t>
+        </is>
+      </c>
+      <c r="B50" t="inlineStr">
+        <is>
+          <t>workshop_proposal_deadline</t>
+        </is>
+      </c>
+      <c r="C50" t="inlineStr">
+        <is>
+          <t>Nov 03, 2025</t>
+        </is>
+      </c>
+      <c r="E50" t="inlineStr">
+        <is>
+          <t>2026-07-22 19:22 UTC</t>
+        </is>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" t="inlineStr">
+        <is>
+          <t>cvpr</t>
+        </is>
+      </c>
+      <c r="B51" t="inlineStr">
+        <is>
+          <t>workshop_proposal_status</t>
+        </is>
+      </c>
+      <c r="C51" t="inlineStr">
+        <is>
+          <t>confirmed</t>
+        </is>
+      </c>
+      <c r="D51" t="inlineStr">
+        <is>
+          <t>not_yet_announced</t>
+        </is>
+      </c>
+      <c r="E51" t="inlineStr">
+        <is>
+          <t>2026-07-22 19:22 UTC</t>
+        </is>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" t="inlineStr">
+        <is>
+          <t>dac</t>
+        </is>
+      </c>
+      <c r="B52" t="inlineStr">
+        <is>
+          <t>workshop_proposal_deadline</t>
+        </is>
+      </c>
+      <c r="C52" t="inlineStr">
+        <is>
+          <t>Apr 29, 2026</t>
+        </is>
+      </c>
+      <c r="E52" t="inlineStr">
+        <is>
+          <t>2026-07-22 19:22 UTC</t>
+        </is>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" t="inlineStr">
+        <is>
+          <t>dac</t>
+        </is>
+      </c>
+      <c r="B53" t="inlineStr">
+        <is>
+          <t>workshop_proposal_status</t>
+        </is>
+      </c>
+      <c r="C53" t="inlineStr">
+        <is>
+          <t>confirmed</t>
+        </is>
+      </c>
+      <c r="D53" t="inlineStr">
+        <is>
+          <t>not_yet_announced</t>
+        </is>
+      </c>
+      <c r="E53" t="inlineStr">
+        <is>
+          <t>2026-07-22 19:22 UTC</t>
+        </is>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" t="inlineStr">
+        <is>
+          <t>fm</t>
+        </is>
+      </c>
+      <c r="B54" t="inlineStr">
+        <is>
+          <t>workshop_proposal_deadline</t>
+        </is>
+      </c>
+      <c r="C54" t="inlineStr">
+        <is>
+          <t>November 10, 2025</t>
+        </is>
+      </c>
+      <c r="E54" t="inlineStr">
+        <is>
+          <t>2026-07-22 19:22 UTC</t>
+        </is>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" t="inlineStr">
+        <is>
+          <t>fm</t>
+        </is>
+      </c>
+      <c r="B55" t="inlineStr">
+        <is>
+          <t>workshop_proposal_status</t>
+        </is>
+      </c>
+      <c r="C55" t="inlineStr">
+        <is>
+          <t>confirmed</t>
+        </is>
+      </c>
+      <c r="D55" t="inlineStr">
+        <is>
+          <t>not_yet_announced</t>
+        </is>
+      </c>
+      <c r="E55" t="inlineStr">
+        <is>
+          <t>2026-07-22 19:22 UTC</t>
+        </is>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" t="inlineStr">
+        <is>
+          <t>hpdc</t>
+        </is>
+      </c>
+      <c r="B56" t="inlineStr">
+        <is>
+          <t>workshop_proposal_deadline</t>
+        </is>
+      </c>
+      <c r="C56" t="inlineStr">
+        <is>
+          <t>December 5, 2025</t>
+        </is>
+      </c>
+      <c r="E56" t="inlineStr">
+        <is>
+          <t>2026-07-22 19:22 UTC</t>
+        </is>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" t="inlineStr">
+        <is>
+          <t>hpdc</t>
+        </is>
+      </c>
+      <c r="B57" t="inlineStr">
+        <is>
+          <t>workshop_proposal_status</t>
+        </is>
+      </c>
+      <c r="C57" t="inlineStr">
+        <is>
+          <t>confirmed</t>
+        </is>
+      </c>
+      <c r="D57" t="inlineStr">
+        <is>
+          <t>not_yet_announced</t>
+        </is>
+      </c>
+      <c r="E57" t="inlineStr">
+        <is>
+          <t>2026-07-22 19:22 UTC</t>
+        </is>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" t="inlineStr">
+        <is>
+          <t>iccv</t>
+        </is>
+      </c>
+      <c r="B58" t="inlineStr">
+        <is>
+          <t>workshop_proposal_deadline</t>
+        </is>
+      </c>
+      <c r="C58" t="inlineStr">
+        <is>
+          <t>Mar 13, 2025</t>
+        </is>
+      </c>
+      <c r="E58" t="inlineStr">
+        <is>
+          <t>2026-07-22 19:22 UTC</t>
+        </is>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" t="inlineStr">
+        <is>
+          <t>iccv</t>
+        </is>
+      </c>
+      <c r="B59" t="inlineStr">
+        <is>
+          <t>workshop_proposal_status</t>
+        </is>
+      </c>
+      <c r="C59" t="inlineStr">
+        <is>
+          <t>confirmed</t>
+        </is>
+      </c>
+      <c r="D59" t="inlineStr">
+        <is>
+          <t>not_yet_announced</t>
+        </is>
+      </c>
+      <c r="E59" t="inlineStr">
+        <is>
+          <t>2026-07-22 19:22 UTC</t>
+        </is>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" t="inlineStr">
+        <is>
+          <t>iclr</t>
+        </is>
+      </c>
+      <c r="B60" t="inlineStr">
+        <is>
+          <t>workshop_proposal_deadline</t>
+        </is>
+      </c>
+      <c r="C60" t="inlineStr">
+        <is>
+          <t>10 October 2025</t>
+        </is>
+      </c>
+      <c r="E60" t="inlineStr">
+        <is>
+          <t>2026-07-22 19:22 UTC</t>
+        </is>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" t="inlineStr">
+        <is>
+          <t>iclr</t>
+        </is>
+      </c>
+      <c r="B61" t="inlineStr">
+        <is>
+          <t>workshop_proposal_status</t>
+        </is>
+      </c>
+      <c r="C61" t="inlineStr">
+        <is>
+          <t>confirmed</t>
+        </is>
+      </c>
+      <c r="D61" t="inlineStr">
+        <is>
+          <t>not_yet_announced</t>
+        </is>
+      </c>
+      <c r="E61" t="inlineStr">
+        <is>
+          <t>2026-07-22 19:22 UTC</t>
+        </is>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" t="inlineStr">
+        <is>
+          <t>icml</t>
+        </is>
+      </c>
+      <c r="B62" t="inlineStr">
+        <is>
+          <t>workshop_proposal_deadline</t>
+        </is>
+      </c>
+      <c r="C62" t="inlineStr">
+        <is>
+          <t>February 13, 2026</t>
+        </is>
+      </c>
+      <c r="E62" t="inlineStr">
+        <is>
+          <t>2026-07-22 19:22 UTC</t>
+        </is>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" t="inlineStr">
+        <is>
+          <t>icml</t>
+        </is>
+      </c>
+      <c r="B63" t="inlineStr">
+        <is>
+          <t>workshop_proposal_status</t>
+        </is>
+      </c>
+      <c r="C63" t="inlineStr">
+        <is>
+          <t>confirmed</t>
+        </is>
+      </c>
+      <c r="D63" t="inlineStr">
+        <is>
+          <t>not_yet_announced</t>
+        </is>
+      </c>
+      <c r="E63" t="inlineStr">
+        <is>
+          <t>2026-07-22 19:22 UTC</t>
+        </is>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" t="inlineStr">
+        <is>
+          <t>icse</t>
+        </is>
+      </c>
+      <c r="B64" t="inlineStr">
+        <is>
+          <t>workshop_proposal_deadline</t>
+        </is>
+      </c>
+      <c r="C64" t="inlineStr">
+        <is>
+          <t>4 July 2026</t>
+        </is>
+      </c>
+      <c r="D64" t="inlineStr">
+        <is>
+          <t>2026-07-04</t>
+        </is>
+      </c>
+      <c r="E64" t="inlineStr">
+        <is>
+          <t>2026-07-22 19:22 UTC</t>
+        </is>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" t="inlineStr">
+        <is>
+          <t>ieeevis</t>
+        </is>
+      </c>
+      <c r="B65" t="inlineStr">
+        <is>
+          <t>workshop_proposal_deadline</t>
+        </is>
+      </c>
+      <c r="C65" t="inlineStr">
+        <is>
+          <t>July 30, 2026</t>
+        </is>
+      </c>
+      <c r="E65" t="inlineStr">
+        <is>
+          <t>2026-07-22 19:22 UTC</t>
+        </is>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" t="inlineStr">
+        <is>
+          <t>ieeevis</t>
+        </is>
+      </c>
+      <c r="B66" t="inlineStr">
+        <is>
+          <t>workshop_proposal_status</t>
+        </is>
+      </c>
+      <c r="C66" t="inlineStr">
+        <is>
+          <t>confirmed</t>
+        </is>
+      </c>
+      <c r="D66" t="inlineStr">
+        <is>
+          <t>not_yet_announced</t>
+        </is>
+      </c>
+      <c r="E66" t="inlineStr">
+        <is>
+          <t>2026-07-22 19:22 UTC</t>
+        </is>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" t="inlineStr">
+        <is>
+          <t>isca</t>
+        </is>
+      </c>
+      <c r="B67" t="inlineStr">
+        <is>
+          <t>workshop_proposal_deadline</t>
+        </is>
+      </c>
+      <c r="C67" t="inlineStr">
+        <is>
+          <t>Jan 9, 2026</t>
+        </is>
+      </c>
+      <c r="E67" t="inlineStr">
+        <is>
+          <t>2026-07-22 19:22 UTC</t>
+        </is>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" t="inlineStr">
+        <is>
+          <t>isca</t>
+        </is>
+      </c>
+      <c r="B68" t="inlineStr">
+        <is>
+          <t>workshop_proposal_status</t>
+        </is>
+      </c>
+      <c r="C68" t="inlineStr">
+        <is>
+          <t>confirmed</t>
+        </is>
+      </c>
+      <c r="D68" t="inlineStr">
+        <is>
+          <t>not_yet_announced</t>
+        </is>
+      </c>
+      <c r="E68" t="inlineStr">
+        <is>
+          <t>2026-07-22 19:22 UTC</t>
+        </is>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" t="inlineStr">
+        <is>
+          <t>issta</t>
+        </is>
+      </c>
+      <c r="B69" t="inlineStr">
+        <is>
+          <t>workshop_proposal_deadline</t>
+        </is>
+      </c>
+      <c r="C69" t="inlineStr">
+        <is>
+          <t>Sat 17 Jan 2026</t>
+        </is>
+      </c>
+      <c r="E69" t="inlineStr">
+        <is>
+          <t>2026-07-22 19:22 UTC</t>
+        </is>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" t="inlineStr">
+        <is>
+          <t>issta</t>
+        </is>
+      </c>
+      <c r="B70" t="inlineStr">
+        <is>
+          <t>workshop_proposal_status</t>
+        </is>
+      </c>
+      <c r="C70" t="inlineStr">
+        <is>
+          <t>confirmed</t>
+        </is>
+      </c>
+      <c r="D70" t="inlineStr">
+        <is>
+          <t>not_yet_announced</t>
+        </is>
+      </c>
+      <c r="E70" t="inlineStr">
+        <is>
+          <t>2026-07-22 19:22 UTC</t>
+        </is>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" t="inlineStr">
+        <is>
+          <t>micro</t>
+        </is>
+      </c>
+      <c r="B71" t="inlineStr">
+        <is>
+          <t>workshop_proposal_deadline</t>
+        </is>
+      </c>
+      <c r="C71" t="inlineStr">
+        <is>
+          <t>May 22, 2026</t>
+        </is>
+      </c>
+      <c r="E71" t="inlineStr">
+        <is>
+          <t>2026-07-22 19:22 UTC</t>
+        </is>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72" t="inlineStr">
+        <is>
+          <t>micro</t>
+        </is>
+      </c>
+      <c r="B72" t="inlineStr">
+        <is>
+          <t>workshop_proposal_status</t>
+        </is>
+      </c>
+      <c r="C72" t="inlineStr">
+        <is>
+          <t>confirmed</t>
+        </is>
+      </c>
+      <c r="D72" t="inlineStr">
+        <is>
+          <t>not_yet_announced</t>
+        </is>
+      </c>
+      <c r="E72" t="inlineStr">
+        <is>
+          <t>2026-07-22 19:22 UTC</t>
+        </is>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" t="inlineStr">
+        <is>
+          <t>neurips</t>
+        </is>
+      </c>
+      <c r="B73" t="inlineStr">
+        <is>
+          <t>workshop_proposal_deadline</t>
+        </is>
+      </c>
+      <c r="C73" t="inlineStr">
+        <is>
+          <t>June 06, 2026</t>
+        </is>
+      </c>
+      <c r="E73" t="inlineStr">
+        <is>
+          <t>2026-07-22 19:22 UTC</t>
+        </is>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74" t="inlineStr">
+        <is>
+          <t>neurips</t>
+        </is>
+      </c>
+      <c r="B74" t="inlineStr">
+        <is>
+          <t>workshop_proposal_status</t>
+        </is>
+      </c>
+      <c r="C74" t="inlineStr">
+        <is>
+          <t>confirmed</t>
+        </is>
+      </c>
+      <c r="D74" t="inlineStr">
+        <is>
+          <t>not_yet_announced</t>
+        </is>
+      </c>
+      <c r="E74" t="inlineStr">
+        <is>
+          <t>2026-07-22 19:22 UTC</t>
+        </is>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" t="inlineStr">
+        <is>
+          <t>oopsla</t>
+        </is>
+      </c>
+      <c r="B75" t="inlineStr">
+        <is>
+          <t>workshop_proposal_deadline</t>
+        </is>
+      </c>
+      <c r="C75" t="inlineStr">
+        <is>
+          <t>Sat 17 Jan 2026</t>
+        </is>
+      </c>
+      <c r="E75" t="inlineStr">
+        <is>
+          <t>2026-07-22 19:22 UTC</t>
+        </is>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76" t="inlineStr">
+        <is>
+          <t>oopsla</t>
+        </is>
+      </c>
+      <c r="B76" t="inlineStr">
+        <is>
+          <t>workshop_proposal_status</t>
+        </is>
+      </c>
+      <c r="C76" t="inlineStr">
+        <is>
+          <t>confirmed</t>
+        </is>
+      </c>
+      <c r="D76" t="inlineStr">
+        <is>
+          <t>not_yet_announced</t>
+        </is>
+      </c>
+      <c r="E76" t="inlineStr">
+        <is>
+          <t>2026-07-22 19:22 UTC</t>
+        </is>
+      </c>
+    </row>
+    <row r="77">
+      <c r="A77" t="inlineStr">
+        <is>
+          <t>pldi</t>
+        </is>
+      </c>
+      <c r="B77" t="inlineStr">
+        <is>
+          <t>workshop_proposal_deadline</t>
+        </is>
+      </c>
+      <c r="C77" t="inlineStr">
+        <is>
+          <t>Mon 24 Nov 2025</t>
+        </is>
+      </c>
+      <c r="E77" t="inlineStr">
+        <is>
+          <t>2026-07-22 19:22 UTC</t>
+        </is>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78" t="inlineStr">
+        <is>
+          <t>pldi</t>
+        </is>
+      </c>
+      <c r="B78" t="inlineStr">
+        <is>
+          <t>workshop_proposal_status</t>
+        </is>
+      </c>
+      <c r="C78" t="inlineStr">
+        <is>
+          <t>confirmed</t>
+        </is>
+      </c>
+      <c r="D78" t="inlineStr">
+        <is>
+          <t>not_yet_announced</t>
+        </is>
+      </c>
+      <c r="E78" t="inlineStr">
+        <is>
+          <t>2026-07-22 19:22 UTC</t>
+        </is>
+      </c>
+    </row>
+    <row r="79">
+      <c r="A79" t="inlineStr">
+        <is>
+          <t>popl</t>
+        </is>
+      </c>
+      <c r="B79" t="inlineStr">
+        <is>
+          <t>workshop_proposal_deadline</t>
+        </is>
+      </c>
+      <c r="C79" t="inlineStr">
+        <is>
+          <t>24 July 2026</t>
+        </is>
+      </c>
+      <c r="D79" t="inlineStr">
+        <is>
+          <t>2026-07-24</t>
+        </is>
+      </c>
+      <c r="E79" t="inlineStr">
+        <is>
+          <t>2026-07-22 19:22 UTC</t>
+        </is>
+      </c>
+    </row>
+    <row r="80">
+      <c r="A80" t="inlineStr">
+        <is>
+          <t>sigcomm</t>
+        </is>
+      </c>
+      <c r="B80" t="inlineStr">
+        <is>
+          <t>workshop_proposal_deadline</t>
+        </is>
+      </c>
+      <c r="C80" t="inlineStr">
+        <is>
+          <t>January 21, 2026</t>
+        </is>
+      </c>
+      <c r="E80" t="inlineStr">
+        <is>
+          <t>2026-07-22 19:22 UTC</t>
+        </is>
+      </c>
+    </row>
+    <row r="81">
+      <c r="A81" t="inlineStr">
+        <is>
+          <t>sigcomm</t>
+        </is>
+      </c>
+      <c r="B81" t="inlineStr">
+        <is>
+          <t>workshop_proposal_status</t>
+        </is>
+      </c>
+      <c r="C81" t="inlineStr">
+        <is>
+          <t>confirmed</t>
+        </is>
+      </c>
+      <c r="D81" t="inlineStr">
+        <is>
+          <t>not_yet_announced</t>
+        </is>
+      </c>
+      <c r="E81" t="inlineStr">
+        <is>
+          <t>2026-07-22 19:22 UTC</t>
+        </is>
+      </c>
+    </row>
+    <row r="82">
+      <c r="A82" t="inlineStr">
+        <is>
+          <t>sigopsatc</t>
+        </is>
+      </c>
+      <c r="B82" t="inlineStr">
+        <is>
+          <t>workshop_proposal_deadline</t>
+        </is>
+      </c>
+      <c r="C82" t="inlineStr">
+        <is>
+          <t>April 29, 2025</t>
+        </is>
+      </c>
+      <c r="E82" t="inlineStr">
+        <is>
+          <t>2026-07-22 19:22 UTC</t>
+        </is>
+      </c>
+    </row>
+    <row r="83">
+      <c r="A83" t="inlineStr">
+        <is>
+          <t>sigopsatc</t>
+        </is>
+      </c>
+      <c r="B83" t="inlineStr">
+        <is>
+          <t>workshop_proposal_status</t>
+        </is>
+      </c>
+      <c r="C83" t="inlineStr">
+        <is>
+          <t>confirmed</t>
+        </is>
+      </c>
+      <c r="D83" t="inlineStr">
+        <is>
+          <t>not_yet_announced</t>
+        </is>
+      </c>
+      <c r="E83" t="inlineStr">
+        <is>
+          <t>2026-07-22 19:22 UTC</t>
+        </is>
+      </c>
+    </row>
+    <row r="84">
+      <c r="A84" t="inlineStr">
+        <is>
+          <t>ubicompiswc</t>
+        </is>
+      </c>
+      <c r="B84" t="inlineStr">
+        <is>
+          <t>workshop_proposal_deadline</t>
+        </is>
+      </c>
+      <c r="C84" t="inlineStr">
+        <is>
+          <t>2026-03-07</t>
+        </is>
+      </c>
+      <c r="E84" t="inlineStr">
+        <is>
+          <t>2026-07-22 19:22 UTC</t>
+        </is>
+      </c>
+    </row>
+    <row r="85">
+      <c r="A85" t="inlineStr">
+        <is>
+          <t>ubicompiswc</t>
+        </is>
+      </c>
+      <c r="B85" t="inlineStr">
+        <is>
+          <t>workshop_proposal_status</t>
+        </is>
+      </c>
+      <c r="C85" t="inlineStr">
+        <is>
+          <t>confirmed</t>
+        </is>
+      </c>
+      <c r="D85" t="inlineStr">
+        <is>
+          <t>not_yet_announced</t>
+        </is>
+      </c>
+      <c r="E85" t="inlineStr">
+        <is>
+          <t>2026-07-22 19:22 UTC</t>
+        </is>
+      </c>
+    </row>
+    <row r="86">
+      <c r="A86" t="inlineStr">
+        <is>
+          <t>uist</t>
+        </is>
+      </c>
+      <c r="B86" t="inlineStr">
+        <is>
+          <t>workshop_proposal_deadline</t>
+        </is>
+      </c>
+      <c r="C86" t="inlineStr">
+        <is>
+          <t>Jul 10, 2026</t>
+        </is>
+      </c>
+      <c r="E86" t="inlineStr">
+        <is>
+          <t>2026-07-22 19:22 UTC</t>
+        </is>
+      </c>
+    </row>
+    <row r="87">
+      <c r="A87" t="inlineStr">
+        <is>
+          <t>uist</t>
+        </is>
+      </c>
+      <c r="B87" t="inlineStr">
+        <is>
+          <t>workshop_proposal_status</t>
+        </is>
+      </c>
+      <c r="C87" t="inlineStr">
+        <is>
+          <t>confirmed</t>
+        </is>
+      </c>
+      <c r="D87" t="inlineStr">
+        <is>
+          <t>not_yet_announced</t>
+        </is>
+      </c>
+      <c r="E87" t="inlineStr">
+        <is>
+          <t>2026-07-22 19:22 UTC</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/conferences.xlsx
+++ b/data/conferences.xlsx
@@ -683,15 +683,11 @@
           <t>CG</t>
         </is>
       </c>
-      <c r="F4" t="inlineStr"/>
-      <c r="G4" t="inlineStr"/>
-      <c r="H4" t="inlineStr"/>
       <c r="I4" t="inlineStr">
         <is>
           <t>TBD</t>
         </is>
       </c>
-      <c r="J4" t="inlineStr"/>
       <c r="K4" t="inlineStr">
         <is>
           <t>TBD</t>
@@ -732,15 +728,11 @@
           <t>CG</t>
         </is>
       </c>
-      <c r="F5" t="inlineStr"/>
-      <c r="G5" t="inlineStr"/>
-      <c r="H5" t="inlineStr"/>
       <c r="I5" t="inlineStr">
         <is>
           <t>TBD</t>
         </is>
       </c>
-      <c r="J5" t="inlineStr"/>
       <c r="K5" t="inlineStr">
         <is>
           <t>TBD</t>
@@ -781,15 +773,11 @@
           <t>SE</t>
         </is>
       </c>
-      <c r="F6" t="inlineStr"/>
-      <c r="G6" t="inlineStr"/>
-      <c r="H6" t="inlineStr"/>
       <c r="I6" t="inlineStr">
         <is>
           <t>TBD</t>
         </is>
       </c>
-      <c r="J6" t="inlineStr"/>
       <c r="K6" t="inlineStr">
         <is>
           <t>TBD</t>
@@ -895,15 +883,11 @@
           <t>CT</t>
         </is>
       </c>
-      <c r="F8" t="inlineStr"/>
-      <c r="G8" t="inlineStr"/>
-      <c r="H8" t="inlineStr"/>
       <c r="I8" t="inlineStr">
         <is>
           <t>TBD</t>
         </is>
       </c>
-      <c r="J8" t="inlineStr"/>
       <c r="K8" t="inlineStr">
         <is>
           <t>TBD</t>
@@ -944,15 +928,11 @@
           <t>SC</t>
         </is>
       </c>
-      <c r="F9" t="inlineStr"/>
-      <c r="G9" t="inlineStr"/>
-      <c r="H9" t="inlineStr"/>
       <c r="I9" t="inlineStr">
         <is>
           <t>TBD</t>
         </is>
       </c>
-      <c r="J9" t="inlineStr"/>
       <c r="K9" t="inlineStr">
         <is>
           <t>TBD</t>
@@ -1083,15 +1063,11 @@
           <t>SC</t>
         </is>
       </c>
-      <c r="F11" t="inlineStr"/>
-      <c r="G11" t="inlineStr"/>
-      <c r="H11" t="inlineStr"/>
       <c r="I11" t="inlineStr">
         <is>
           <t>TBD</t>
         </is>
       </c>
-      <c r="J11" t="inlineStr"/>
       <c r="K11" t="inlineStr">
         <is>
           <t>TBD</t>
@@ -1132,15 +1108,11 @@
           <t>HI</t>
         </is>
       </c>
-      <c r="F12" t="inlineStr"/>
-      <c r="G12" t="inlineStr"/>
-      <c r="H12" t="inlineStr"/>
       <c r="I12" t="inlineStr">
         <is>
           <t>TBD</t>
         </is>
       </c>
-      <c r="J12" t="inlineStr"/>
       <c r="K12" t="inlineStr">
         <is>
           <t>TBD</t>
@@ -1191,15 +1163,11 @@
           <t>AI</t>
         </is>
       </c>
-      <c r="F13" t="inlineStr"/>
-      <c r="G13" t="inlineStr"/>
-      <c r="H13" t="inlineStr"/>
       <c r="I13" t="inlineStr">
         <is>
           <t>TBD</t>
         </is>
       </c>
-      <c r="J13" t="inlineStr"/>
       <c r="K13" t="inlineStr">
         <is>
           <t>TBD</t>
@@ -1250,15 +1218,11 @@
           <t>DS</t>
         </is>
       </c>
-      <c r="F14" t="inlineStr"/>
-      <c r="G14" t="inlineStr"/>
-      <c r="H14" t="inlineStr"/>
       <c r="I14" t="inlineStr">
         <is>
           <t>TBD</t>
         </is>
       </c>
-      <c r="J14" t="inlineStr"/>
       <c r="K14" t="inlineStr">
         <is>
           <t>TBD</t>
@@ -1504,15 +1468,11 @@
           <t>SE</t>
         </is>
       </c>
-      <c r="F18" t="inlineStr"/>
-      <c r="G18" t="inlineStr"/>
-      <c r="H18" t="inlineStr"/>
       <c r="I18" t="inlineStr">
         <is>
           <t>TBD</t>
         </is>
       </c>
-      <c r="J18" t="inlineStr"/>
       <c r="K18" t="inlineStr">
         <is>
           <t>TBD</t>
@@ -1563,31 +1523,21 @@
           <t>CT</t>
         </is>
       </c>
-      <c r="F19" t="inlineStr"/>
-      <c r="G19" t="inlineStr"/>
-      <c r="H19" t="inlineStr"/>
       <c r="I19" t="inlineStr">
         <is>
           <t>TBD</t>
         </is>
       </c>
-      <c r="J19" t="inlineStr"/>
       <c r="K19" t="inlineStr">
         <is>
           <t>TBD</t>
         </is>
       </c>
-      <c r="L19" t="inlineStr"/>
       <c r="M19" t="inlineStr">
         <is>
           <t>not_yet_announced</t>
         </is>
       </c>
-      <c r="N19" t="inlineStr"/>
-      <c r="O19" t="inlineStr"/>
-      <c r="P19" t="inlineStr"/>
-      <c r="Q19" t="inlineStr"/>
-      <c r="R19" t="inlineStr"/>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
@@ -1743,15 +1693,11 @@
           <t>DS</t>
         </is>
       </c>
-      <c r="F22" t="inlineStr"/>
-      <c r="G22" t="inlineStr"/>
-      <c r="H22" t="inlineStr"/>
       <c r="I22" t="inlineStr">
         <is>
           <t>TBD</t>
         </is>
       </c>
-      <c r="J22" t="inlineStr"/>
       <c r="K22" t="inlineStr">
         <is>
           <t>TBD</t>
@@ -1802,15 +1748,11 @@
           <t>AI</t>
         </is>
       </c>
-      <c r="F23" t="inlineStr"/>
-      <c r="G23" t="inlineStr"/>
-      <c r="H23" t="inlineStr"/>
       <c r="I23" t="inlineStr">
         <is>
           <t>TBD</t>
         </is>
       </c>
-      <c r="J23" t="inlineStr"/>
       <c r="K23" t="inlineStr">
         <is>
           <t>TBD</t>
@@ -1926,15 +1868,11 @@
           <t>AI</t>
         </is>
       </c>
-      <c r="F25" t="inlineStr"/>
-      <c r="G25" t="inlineStr"/>
-      <c r="H25" t="inlineStr"/>
       <c r="I25" t="inlineStr">
         <is>
           <t>TBD</t>
         </is>
       </c>
-      <c r="J25" t="inlineStr"/>
       <c r="K25" t="inlineStr">
         <is>
           <t>TBD</t>
@@ -1985,15 +1923,11 @@
           <t>AI</t>
         </is>
       </c>
-      <c r="F26" t="inlineStr"/>
-      <c r="G26" t="inlineStr"/>
-      <c r="H26" t="inlineStr"/>
       <c r="I26" t="inlineStr">
         <is>
           <t>TBD</t>
         </is>
       </c>
-      <c r="J26" t="inlineStr"/>
       <c r="K26" t="inlineStr">
         <is>
           <t>TBD</t>
@@ -2134,15 +2068,11 @@
           <t>CG</t>
         </is>
       </c>
-      <c r="F28" t="inlineStr"/>
-      <c r="G28" t="inlineStr"/>
-      <c r="H28" t="inlineStr"/>
       <c r="I28" t="inlineStr">
         <is>
           <t>TBD</t>
         </is>
       </c>
-      <c r="J28" t="inlineStr"/>
       <c r="K28" t="inlineStr">
         <is>
           <t>TBD</t>
@@ -2323,15 +2253,11 @@
           <t>DS</t>
         </is>
       </c>
-      <c r="F31" t="inlineStr"/>
-      <c r="G31" t="inlineStr"/>
-      <c r="H31" t="inlineStr"/>
       <c r="I31" t="inlineStr">
         <is>
           <t>TBD</t>
         </is>
       </c>
-      <c r="J31" t="inlineStr"/>
       <c r="K31" t="inlineStr">
         <is>
           <t>TBD</t>
@@ -2382,15 +2308,11 @@
           <t>SE</t>
         </is>
       </c>
-      <c r="F32" t="inlineStr"/>
-      <c r="G32" t="inlineStr"/>
-      <c r="H32" t="inlineStr"/>
       <c r="I32" t="inlineStr">
         <is>
           <t>TBD</t>
         </is>
       </c>
-      <c r="J32" t="inlineStr"/>
       <c r="K32" t="inlineStr">
         <is>
           <t>TBD</t>
@@ -2441,15 +2363,11 @@
           <t>CT</t>
         </is>
       </c>
-      <c r="F33" t="inlineStr"/>
-      <c r="G33" t="inlineStr"/>
-      <c r="H33" t="inlineStr"/>
       <c r="I33" t="inlineStr">
         <is>
           <t>TBD</t>
         </is>
       </c>
-      <c r="J33" t="inlineStr"/>
       <c r="K33" t="inlineStr">
         <is>
           <t>TBD</t>
@@ -2490,15 +2408,11 @@
           <t>DS</t>
         </is>
       </c>
-      <c r="F34" t="inlineStr"/>
-      <c r="G34" t="inlineStr"/>
-      <c r="H34" t="inlineStr"/>
       <c r="I34" t="inlineStr">
         <is>
           <t>TBD</t>
         </is>
       </c>
-      <c r="J34" t="inlineStr"/>
       <c r="K34" t="inlineStr">
         <is>
           <t>TBD</t>
@@ -2549,15 +2463,11 @@
           <t>NW</t>
         </is>
       </c>
-      <c r="F35" t="inlineStr"/>
-      <c r="G35" t="inlineStr"/>
-      <c r="H35" t="inlineStr"/>
       <c r="I35" t="inlineStr">
         <is>
           <t>TBD</t>
         </is>
       </c>
-      <c r="J35" t="inlineStr"/>
       <c r="K35" t="inlineStr">
         <is>
           <t>TBD</t>
@@ -2663,15 +2573,11 @@
           <t>AI</t>
         </is>
       </c>
-      <c r="F37" t="inlineStr"/>
-      <c r="G37" t="inlineStr"/>
-      <c r="H37" t="inlineStr"/>
       <c r="I37" t="inlineStr">
         <is>
           <t>TBD</t>
         </is>
       </c>
-      <c r="J37" t="inlineStr"/>
       <c r="K37" t="inlineStr">
         <is>
           <t>TBD</t>
@@ -2787,15 +2693,11 @@
           <t>SE</t>
         </is>
       </c>
-      <c r="F39" t="inlineStr"/>
-      <c r="G39" t="inlineStr"/>
-      <c r="H39" t="inlineStr"/>
       <c r="I39" t="inlineStr">
         <is>
           <t>TBD</t>
         </is>
       </c>
-      <c r="J39" t="inlineStr"/>
       <c r="K39" t="inlineStr">
         <is>
           <t>TBD</t>
@@ -2911,15 +2813,11 @@
           <t>SE</t>
         </is>
       </c>
-      <c r="F41" t="inlineStr"/>
-      <c r="G41" t="inlineStr"/>
-      <c r="H41" t="inlineStr"/>
       <c r="I41" t="inlineStr">
         <is>
           <t>TBD</t>
         </is>
       </c>
-      <c r="J41" t="inlineStr"/>
       <c r="K41" t="inlineStr">
         <is>
           <t>TBD</t>
@@ -2975,7 +2873,6 @@
           <t>Mexico City</t>
         </is>
       </c>
-      <c r="G42" t="inlineStr"/>
       <c r="H42" t="inlineStr">
         <is>
           <t>Other</t>
@@ -3091,9 +2988,16 @@
           <t>not_yet_announced</t>
         </is>
       </c>
+      <c r="N43" t="inlineStr"/>
       <c r="O43" t="inlineStr">
         <is>
-          <t>2026-07-22 19:22 UTC</t>
+          <t>2026-07-22 19:32 UTC</t>
+        </is>
+      </c>
+      <c r="Q43" t="inlineStr"/>
+      <c r="R43" t="inlineStr">
+        <is>
+          <t>需要人工核实官网（未配置搜索API做兜底）</t>
         </is>
       </c>
     </row>
@@ -3121,15 +3025,11 @@
           <t>MX</t>
         </is>
       </c>
-      <c r="F44" t="inlineStr"/>
-      <c r="G44" t="inlineStr"/>
-      <c r="H44" t="inlineStr"/>
       <c r="I44" t="inlineStr">
         <is>
           <t>TBD</t>
         </is>
       </c>
-      <c r="J44" t="inlineStr"/>
       <c r="K44" t="inlineStr">
         <is>
           <t>TBD</t>
@@ -3170,15 +3070,11 @@
           <t>DS</t>
         </is>
       </c>
-      <c r="F45" t="inlineStr"/>
-      <c r="G45" t="inlineStr"/>
-      <c r="H45" t="inlineStr"/>
       <c r="I45" t="inlineStr">
         <is>
           <t>TBD</t>
         </is>
       </c>
-      <c r="J45" t="inlineStr"/>
       <c r="K45" t="inlineStr">
         <is>
           <t>TBD</t>
@@ -3219,15 +3115,11 @@
           <t>NW</t>
         </is>
       </c>
-      <c r="F46" t="inlineStr"/>
-      <c r="G46" t="inlineStr"/>
-      <c r="H46" t="inlineStr"/>
       <c r="I46" t="inlineStr">
         <is>
           <t>TBD</t>
         </is>
       </c>
-      <c r="J46" t="inlineStr"/>
       <c r="K46" t="inlineStr">
         <is>
           <t>TBD</t>
@@ -3278,15 +3170,11 @@
           <t>DB</t>
         </is>
       </c>
-      <c r="F47" t="inlineStr"/>
-      <c r="G47" t="inlineStr"/>
-      <c r="H47" t="inlineStr"/>
       <c r="I47" t="inlineStr">
         <is>
           <t>TBD</t>
         </is>
       </c>
-      <c r="J47" t="inlineStr"/>
       <c r="K47" t="inlineStr">
         <is>
           <t>TBD</t>
@@ -3457,15 +3345,11 @@
           <t>DS</t>
         </is>
       </c>
-      <c r="F50" t="inlineStr"/>
-      <c r="G50" t="inlineStr"/>
-      <c r="H50" t="inlineStr"/>
       <c r="I50" t="inlineStr">
         <is>
           <t>TBD</t>
         </is>
       </c>
-      <c r="J50" t="inlineStr"/>
       <c r="K50" t="inlineStr">
         <is>
           <t>TBD</t>
@@ -3581,15 +3465,11 @@
           <t>SE</t>
         </is>
       </c>
-      <c r="F52" t="inlineStr"/>
-      <c r="G52" t="inlineStr"/>
-      <c r="H52" t="inlineStr"/>
       <c r="I52" t="inlineStr">
         <is>
           <t>TBD</t>
         </is>
       </c>
-      <c r="J52" t="inlineStr"/>
       <c r="K52" t="inlineStr">
         <is>
           <t>TBD</t>
@@ -3695,31 +3575,21 @@
           <t>CT</t>
         </is>
       </c>
-      <c r="F54" t="inlineStr"/>
-      <c r="G54" t="inlineStr"/>
-      <c r="H54" t="inlineStr"/>
       <c r="I54" t="inlineStr">
         <is>
           <t>TBD</t>
         </is>
       </c>
-      <c r="J54" t="inlineStr"/>
       <c r="K54" t="inlineStr">
         <is>
           <t>TBD</t>
         </is>
       </c>
-      <c r="L54" t="inlineStr"/>
       <c r="M54" t="inlineStr">
         <is>
           <t>not_yet_announced</t>
         </is>
       </c>
-      <c r="N54" t="inlineStr"/>
-      <c r="O54" t="inlineStr"/>
-      <c r="P54" t="inlineStr"/>
-      <c r="Q54" t="inlineStr"/>
-      <c r="R54" t="inlineStr"/>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
@@ -3745,15 +3615,11 @@
           <t>HI</t>
         </is>
       </c>
-      <c r="F55" t="inlineStr"/>
-      <c r="G55" t="inlineStr"/>
-      <c r="H55" t="inlineStr"/>
       <c r="I55" t="inlineStr">
         <is>
           <t>TBD</t>
         </is>
       </c>
-      <c r="J55" t="inlineStr"/>
       <c r="K55" t="inlineStr">
         <is>
           <t>TBD</t>
@@ -3804,15 +3670,11 @@
           <t>HI</t>
         </is>
       </c>
-      <c r="F56" t="inlineStr"/>
-      <c r="G56" t="inlineStr"/>
-      <c r="H56" t="inlineStr"/>
       <c r="I56" t="inlineStr">
         <is>
           <t>TBD</t>
         </is>
       </c>
-      <c r="J56" t="inlineStr"/>
       <c r="K56" t="inlineStr">
         <is>
           <t>TBD</t>
